--- a/startup/standards/standards.xlsx
+++ b/startup/standards/standards.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Ti" sheetId="1" state="visible" r:id="rId2"/>
@@ -1700,7 +1700,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3282" uniqueCount="595">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3282" uniqueCount="596">
   <si>
     <t xml:space="preserve">Double wheel</t>
   </si>
@@ -2578,172 +2578,175 @@
     <t xml:space="preserve">Babingtonite</t>
   </si>
   <si>
+    <t xml:space="preserve">fluorescence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ca2Fe0.75Mn0.25FeSi5O14(OH)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Babingtonite, CM14452; Lane's Quarry, Westfield, Hampden County, Massachusetts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-200 -30 -10 25 560</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 2 2 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Axinite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ca2MnAl2BSi4O15(OH)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Axinite, CM17413; Luning, Mineral County, Nevada, USA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mnfoil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mn foil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">metal powder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">reference wheel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LaMnO3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Co</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CoO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CoO, cobalt monoxide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Co2O3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Co3O4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CoAlO3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CoAlO3, cobalt aluminate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LaCoO3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ni</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NiO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NiO, nickel oxide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NiHydroxide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ni(OH)2, nickel hydroxide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NiBO3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NiBO3.xH2O, nickel borate hydrate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NiAl2O4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NiAl2O4, nickel aluminate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LaNiO3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LaNiO3, lanthanum nickelate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cufoil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cu metal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">reference metal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">reference foil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CuO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cu2O</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dioptase</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CuSi2(OH)2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Covellite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CuS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CuCl2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CuCl2, eriochalcite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sample coutesy Ankita Mohanty and Karen Chen-Wiegart, Stony Brook</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Znfoil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zn metal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZnO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hemimorphite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zn4Si2O7(OH)2·H2O</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Willemite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zn2SiO4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zincite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petedunnite</t>
+  </si>
+  <si>
     <t xml:space="preserve">both</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ca2Fe0.75Mn0.25FeSi5O14(OH)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Babingtonite, CM14452; Lane's Quarry, Westfield, Hampden County, Massachusetts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-200 -30 -10 25 560</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 2 2 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Axinite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ca2MnAl2BSi4O15(OH)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Axinite, CM17413; Luning, Mineral County, Nevada, USA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mnfoil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mn foil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">metal powder</t>
-  </si>
-  <si>
-    <t xml:space="preserve">reference wheel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LaMnO3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Co</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CoO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CoO, cobalt monoxide</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Co2O3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Co3O4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CoAlO3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CoAlO3, cobalt aluminate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LaCoO3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ni</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NiO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NiO, nickel oxide</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NiHydroxide</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ni(OH)2, nickel hydroxide</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NiBO3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NiBO3.xH2O, nickel borate hydrate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NiAl2O4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NiAl2O4, nickel aluminate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LaNiO3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LaNiO3, lanthanum nickelate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cufoil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cu metal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">reference metal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">reference foil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CuO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cu2O</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dioptase</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CuSi2(OH)2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Covellite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CuS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CuCl2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CuCl2, eriochalcite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sample coutesy Ankita Mohanty and Karen Chen-Wiegart, Stony Brook</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Znfoil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zn metal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ZnO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hemimorphite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zn4Si2O7(OH)2·H2O</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Willemite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zn2SiO4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zincite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petedunnite</t>
   </si>
   <si>
     <t xml:space="preserve">Ca(Zn,Mn,Fe,Mg)Si2O6</t>
@@ -3847,7 +3850,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="111">
+  <cellXfs count="110">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -4156,10 +4159,6 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -4375,9 +4374,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>40680</xdr:colOff>
+      <xdr:colOff>40320</xdr:colOff>
       <xdr:row>65</xdr:row>
-      <xdr:rowOff>66960</xdr:rowOff>
+      <xdr:rowOff>66600</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4390,8 +4389,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1656000" y="11943000"/>
-          <a:ext cx="3207240" cy="1822680"/>
+          <a:off x="1656360" y="11943000"/>
+          <a:ext cx="3207240" cy="1822320"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4417,9 +4416,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>856080</xdr:colOff>
+      <xdr:colOff>855720</xdr:colOff>
       <xdr:row>43</xdr:row>
-      <xdr:rowOff>162360</xdr:rowOff>
+      <xdr:rowOff>162000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4432,8 +4431,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2072880" y="7088040"/>
-          <a:ext cx="3605760" cy="2246760"/>
+          <a:off x="2073600" y="7088040"/>
+          <a:ext cx="3605400" cy="2246400"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4459,9 +4458,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>856080</xdr:colOff>
+      <xdr:colOff>855720</xdr:colOff>
       <xdr:row>43</xdr:row>
-      <xdr:rowOff>162720</xdr:rowOff>
+      <xdr:rowOff>162360</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4474,8 +4473,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2072880" y="5591880"/>
-          <a:ext cx="3605760" cy="2247120"/>
+          <a:off x="2073600" y="5591880"/>
+          <a:ext cx="3605400" cy="2246760"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4496,7 +4495,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B1:AE54"/>
-  <sheetFormatPr defaultColWidth="9.01953125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.03125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="1" min="1" style="0" width="11.52"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="10.01"/>
@@ -6710,7 +6709,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B1:AE30"/>
-  <sheetFormatPr defaultColWidth="9.01953125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.03125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="1" min="1" style="0" width="11.52"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="10.01"/>
@@ -6989,7 +6988,7 @@
         <v>48</v>
       </c>
       <c r="I6" s="34" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="J6" s="35" t="s">
         <v>50</v>
@@ -7052,10 +7051,10 @@
       <c r="B7" s="69" t="n">
         <v>11</v>
       </c>
-      <c r="C7" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D7" s="80" t="s">
+      <c r="C7" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D7" s="79" t="s">
         <v>62</v>
       </c>
       <c r="E7" s="65"/>
@@ -7086,14 +7085,14 @@
       <c r="B8" s="69" t="n">
         <v>12</v>
       </c>
-      <c r="C8" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D8" s="80" t="s">
+      <c r="C8" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D8" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E8" s="65" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F8" s="66"/>
       <c r="G8" s="66"/>
@@ -7101,12 +7100,12 @@
       <c r="I8" s="67"/>
       <c r="J8" s="68"/>
       <c r="K8" s="69"/>
-      <c r="L8" s="87" t="s">
-        <v>353</v>
+      <c r="L8" s="86" t="s">
+        <v>354</v>
       </c>
       <c r="M8" s="71"/>
       <c r="N8" s="73" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="O8" s="64"/>
       <c r="P8" s="29"/>
@@ -7126,14 +7125,14 @@
       <c r="B9" s="69" t="n">
         <v>13</v>
       </c>
-      <c r="C9" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D9" s="80" t="s">
+      <c r="C9" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D9" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E9" s="65" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="F9" s="66"/>
       <c r="G9" s="66"/>
@@ -7142,11 +7141,11 @@
       <c r="J9" s="68"/>
       <c r="K9" s="69"/>
       <c r="L9" s="70" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="M9" s="71"/>
       <c r="N9" s="73" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="O9" s="64"/>
       <c r="P9" s="29"/>
@@ -7166,21 +7165,21 @@
       <c r="B10" s="69" t="n">
         <v>14</v>
       </c>
-      <c r="C10" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D10" s="80" t="s">
+      <c r="C10" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D10" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E10" s="0" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="I10" s="67"/>
       <c r="L10" s="0" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="N10" s="73" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="O10" s="64"/>
       <c r="P10" s="29"/>
@@ -7200,21 +7199,21 @@
       <c r="B11" s="69" t="n">
         <v>15</v>
       </c>
-      <c r="C11" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D11" s="80" t="s">
+      <c r="C11" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D11" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E11" s="0" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="I11" s="67"/>
-      <c r="L11" s="87" t="s">
-        <v>360</v>
+      <c r="L11" s="86" t="s">
+        <v>361</v>
       </c>
       <c r="N11" s="73" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="O11" s="64"/>
       <c r="P11" s="29"/>
@@ -7234,21 +7233,21 @@
       <c r="B12" s="69" t="n">
         <v>16</v>
       </c>
-      <c r="C12" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D12" s="80" t="s">
+      <c r="C12" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D12" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E12" s="0" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="I12" s="67"/>
-      <c r="L12" s="87" t="s">
-        <v>362</v>
+      <c r="L12" s="86" t="s">
+        <v>363</v>
       </c>
       <c r="N12" s="73" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="O12" s="64"/>
       <c r="P12" s="29"/>
@@ -7268,21 +7267,21 @@
       <c r="B13" s="69" t="n">
         <v>17</v>
       </c>
-      <c r="C13" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D13" s="80" t="s">
+      <c r="C13" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D13" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E13" s="0" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="I13" s="67"/>
       <c r="L13" s="0" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="N13" s="73" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="O13" s="64"/>
       <c r="P13" s="29"/>
@@ -7302,14 +7301,14 @@
       <c r="B14" s="69" t="n">
         <v>18</v>
       </c>
-      <c r="C14" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D14" s="80" t="s">
+      <c r="C14" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D14" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E14" s="65" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F14" s="66"/>
       <c r="G14" s="66"/>
@@ -7318,11 +7317,11 @@
       <c r="J14" s="68"/>
       <c r="K14" s="69"/>
       <c r="L14" s="70" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="M14" s="71"/>
       <c r="N14" s="73" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="O14" s="64"/>
       <c r="P14" s="29"/>
@@ -7342,14 +7341,14 @@
       <c r="B15" s="69" t="n">
         <v>19</v>
       </c>
-      <c r="C15" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D15" s="80" t="s">
+      <c r="C15" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D15" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E15" s="65" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="F15" s="66"/>
       <c r="G15" s="66"/>
@@ -7357,12 +7356,12 @@
       <c r="I15" s="67"/>
       <c r="J15" s="68"/>
       <c r="K15" s="69"/>
-      <c r="L15" s="87" t="s">
-        <v>369</v>
+      <c r="L15" s="86" t="s">
+        <v>370</v>
       </c>
       <c r="M15" s="71"/>
       <c r="N15" s="73" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="O15" s="64"/>
       <c r="P15" s="29"/>
@@ -7382,14 +7381,14 @@
       <c r="B16" s="69" t="n">
         <v>20</v>
       </c>
-      <c r="C16" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D16" s="80" t="s">
+      <c r="C16" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D16" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E16" s="65" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F16" s="66"/>
       <c r="G16" s="66"/>
@@ -7398,11 +7397,11 @@
       <c r="J16" s="68"/>
       <c r="K16" s="69"/>
       <c r="L16" s="65" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="M16" s="71"/>
       <c r="N16" s="73" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="O16" s="64"/>
       <c r="P16" s="29"/>
@@ -7422,14 +7421,14 @@
       <c r="B17" s="69" t="n">
         <v>21</v>
       </c>
-      <c r="C17" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D17" s="80" t="s">
+      <c r="C17" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D17" s="79" t="s">
         <v>62</v>
       </c>
       <c r="E17" s="65" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F17" s="66"/>
       <c r="G17" s="66"/>
@@ -7438,7 +7437,7 @@
       <c r="J17" s="68"/>
       <c r="K17" s="69"/>
       <c r="L17" s="70" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="M17" s="71"/>
       <c r="N17" s="72"/>
@@ -7460,10 +7459,10 @@
       <c r="B18" s="69" t="n">
         <v>22</v>
       </c>
-      <c r="C18" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D18" s="80" t="s">
+      <c r="C18" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D18" s="79" t="s">
         <v>62</v>
       </c>
       <c r="E18" s="65"/>
@@ -7494,10 +7493,10 @@
       <c r="B19" s="69" t="n">
         <v>11</v>
       </c>
-      <c r="C19" s="79" t="s">
+      <c r="C19" s="78" t="s">
         <v>86</v>
       </c>
-      <c r="D19" s="80" t="s">
+      <c r="D19" s="79" t="s">
         <v>62</v>
       </c>
       <c r="E19" s="65"/>
@@ -7528,25 +7527,25 @@
       <c r="B20" s="69" t="n">
         <v>12</v>
       </c>
-      <c r="C20" s="79" t="s">
+      <c r="C20" s="78" t="s">
         <v>86</v>
       </c>
-      <c r="D20" s="80" t="s">
-        <v>3</v>
-      </c>
-      <c r="E20" s="82" t="s">
-        <v>374</v>
+      <c r="D20" s="79" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20" s="81" t="s">
+        <v>375</v>
       </c>
       <c r="F20" s="66"/>
       <c r="G20" s="66"/>
       <c r="H20" s="66"/>
       <c r="I20" s="67" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="J20" s="68"/>
       <c r="K20" s="69"/>
       <c r="L20" s="65" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="M20" s="71"/>
       <c r="N20" s="73" t="s">
@@ -7570,10 +7569,10 @@
       <c r="B21" s="69" t="n">
         <v>13</v>
       </c>
-      <c r="C21" s="79" t="s">
+      <c r="C21" s="78" t="s">
         <v>86</v>
       </c>
-      <c r="D21" s="80" t="s">
+      <c r="D21" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E21" s="29"/>
@@ -7604,10 +7603,10 @@
       <c r="B22" s="69" t="n">
         <v>14</v>
       </c>
-      <c r="C22" s="79" t="s">
+      <c r="C22" s="78" t="s">
         <v>86</v>
       </c>
-      <c r="D22" s="80" t="s">
+      <c r="D22" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E22" s="29"/>
@@ -7637,10 +7636,10 @@
       <c r="B23" s="69" t="n">
         <v>15</v>
       </c>
-      <c r="C23" s="79" t="s">
+      <c r="C23" s="78" t="s">
         <v>86</v>
       </c>
-      <c r="D23" s="80" t="s">
+      <c r="D23" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E23" s="29"/>
@@ -7671,10 +7670,10 @@
       <c r="B24" s="69" t="n">
         <v>16</v>
       </c>
-      <c r="C24" s="79" t="s">
+      <c r="C24" s="78" t="s">
         <v>86</v>
       </c>
-      <c r="D24" s="80" t="s">
+      <c r="D24" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E24" s="29"/>
@@ -7705,10 +7704,10 @@
       <c r="B25" s="69" t="n">
         <v>17</v>
       </c>
-      <c r="C25" s="79" t="s">
+      <c r="C25" s="78" t="s">
         <v>86</v>
       </c>
-      <c r="D25" s="80" t="s">
+      <c r="D25" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E25" s="29"/>
@@ -7739,10 +7738,10 @@
       <c r="B26" s="69" t="n">
         <v>18</v>
       </c>
-      <c r="C26" s="79" t="s">
+      <c r="C26" s="78" t="s">
         <v>86</v>
       </c>
-      <c r="D26" s="80" t="s">
+      <c r="D26" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E26" s="29"/>
@@ -7773,10 +7772,10 @@
       <c r="B27" s="69" t="n">
         <v>19</v>
       </c>
-      <c r="C27" s="79" t="s">
+      <c r="C27" s="78" t="s">
         <v>86</v>
       </c>
-      <c r="D27" s="80" t="s">
+      <c r="D27" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E27" s="29"/>
@@ -7807,10 +7806,10 @@
       <c r="B28" s="69" t="n">
         <v>20</v>
       </c>
-      <c r="C28" s="79" t="s">
+      <c r="C28" s="78" t="s">
         <v>86</v>
       </c>
-      <c r="D28" s="80" t="s">
+      <c r="D28" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E28" s="29"/>
@@ -7841,10 +7840,10 @@
       <c r="B29" s="69" t="n">
         <v>21</v>
       </c>
-      <c r="C29" s="79" t="s">
+      <c r="C29" s="78" t="s">
         <v>86</v>
       </c>
-      <c r="D29" s="80" t="s">
+      <c r="D29" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E29" s="29"/>
@@ -7875,10 +7874,10 @@
       <c r="B30" s="69" t="n">
         <v>22</v>
       </c>
-      <c r="C30" s="79" t="s">
+      <c r="C30" s="78" t="s">
         <v>86</v>
       </c>
-      <c r="D30" s="80" t="s">
+      <c r="D30" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E30" s="29"/>
@@ -8054,7 +8053,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B1:AE30"/>
-  <sheetFormatPr defaultColWidth="9.01953125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.03125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="1" min="1" style="0" width="11.52"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="10.01"/>
@@ -8332,7 +8331,7 @@
         <v>48</v>
       </c>
       <c r="I6" s="34" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="J6" s="35" t="s">
         <v>50</v>
@@ -8395,14 +8394,14 @@
       <c r="B7" s="69" t="n">
         <v>1</v>
       </c>
-      <c r="C7" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D7" s="80" t="s">
+      <c r="C7" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D7" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E7" s="71" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="F7" s="66"/>
       <c r="G7" s="66"/>
@@ -8411,11 +8410,11 @@
       <c r="J7" s="68"/>
       <c r="K7" s="69"/>
       <c r="L7" s="71" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="M7" s="71"/>
       <c r="N7" s="73" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="O7" s="56"/>
       <c r="P7" s="29"/>
@@ -8435,14 +8434,14 @@
       <c r="B8" s="69" t="n">
         <v>2</v>
       </c>
-      <c r="C8" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D8" s="80" t="s">
+      <c r="C8" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D8" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E8" s="71" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F8" s="66"/>
       <c r="G8" s="66"/>
@@ -8451,11 +8450,11 @@
       <c r="J8" s="68"/>
       <c r="K8" s="69"/>
       <c r="L8" s="71" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="M8" s="71"/>
       <c r="N8" s="73" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="O8" s="56"/>
       <c r="P8" s="29"/>
@@ -8475,14 +8474,14 @@
       <c r="B9" s="69" t="n">
         <v>3</v>
       </c>
-      <c r="C9" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D9" s="80" t="s">
+      <c r="C9" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D9" s="79" t="s">
         <v>62</v>
       </c>
       <c r="E9" s="65" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="F9" s="66"/>
       <c r="G9" s="66"/>
@@ -8491,11 +8490,11 @@
       <c r="J9" s="68"/>
       <c r="K9" s="69"/>
       <c r="L9" s="65" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="M9" s="71"/>
       <c r="N9" s="73" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="O9" s="56"/>
       <c r="P9" s="29"/>
@@ -8515,14 +8514,14 @@
       <c r="B10" s="69" t="n">
         <v>4</v>
       </c>
-      <c r="C10" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D10" s="80" t="s">
+      <c r="C10" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D10" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E10" s="65" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="F10" s="66"/>
       <c r="G10" s="66"/>
@@ -8531,11 +8530,11 @@
       <c r="J10" s="68"/>
       <c r="K10" s="69"/>
       <c r="L10" s="65" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="M10" s="71"/>
       <c r="N10" s="73" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="O10" s="56"/>
       <c r="P10" s="29"/>
@@ -8555,22 +8554,22 @@
       <c r="B11" s="69" t="n">
         <v>5</v>
       </c>
-      <c r="C11" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D11" s="80" t="s">
-        <v>3</v>
-      </c>
-      <c r="E11" s="82"/>
-      <c r="F11" s="82"/>
-      <c r="G11" s="82"/>
-      <c r="H11" s="82"/>
-      <c r="I11" s="82"/>
-      <c r="J11" s="82"/>
-      <c r="K11" s="82"/>
-      <c r="L11" s="82"/>
+      <c r="C11" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D11" s="79" t="s">
+        <v>3</v>
+      </c>
+      <c r="E11" s="81"/>
+      <c r="F11" s="81"/>
+      <c r="G11" s="81"/>
+      <c r="H11" s="81"/>
+      <c r="I11" s="81"/>
+      <c r="J11" s="81"/>
+      <c r="K11" s="81"/>
+      <c r="L11" s="81"/>
       <c r="M11" s="71"/>
-      <c r="N11" s="82"/>
+      <c r="N11" s="81"/>
       <c r="O11" s="56"/>
       <c r="P11" s="29"/>
       <c r="Q11" s="57"/>
@@ -8589,10 +8588,10 @@
       <c r="B12" s="69" t="n">
         <v>6</v>
       </c>
-      <c r="C12" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D12" s="80" t="s">
+      <c r="C12" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D12" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E12" s="65"/>
@@ -8633,7 +8632,7 @@
       <c r="F13" s="13"/>
       <c r="G13" s="13"/>
       <c r="H13" s="13"/>
-      <c r="I13" s="78"/>
+      <c r="I13" s="77"/>
       <c r="J13" s="55"/>
       <c r="K13" s="50"/>
       <c r="L13" s="56"/>
@@ -8667,7 +8666,7 @@
       <c r="F14" s="13"/>
       <c r="G14" s="13"/>
       <c r="H14" s="13"/>
-      <c r="I14" s="78"/>
+      <c r="I14" s="77"/>
       <c r="J14" s="55"/>
       <c r="K14" s="50"/>
       <c r="L14" s="56"/>
@@ -8701,7 +8700,7 @@
       <c r="F15" s="13"/>
       <c r="G15" s="13"/>
       <c r="H15" s="13"/>
-      <c r="I15" s="78"/>
+      <c r="I15" s="77"/>
       <c r="J15" s="55"/>
       <c r="K15" s="50"/>
       <c r="L15" s="56"/>
@@ -8735,7 +8734,7 @@
       <c r="F16" s="13"/>
       <c r="G16" s="13"/>
       <c r="H16" s="13"/>
-      <c r="I16" s="78"/>
+      <c r="I16" s="77"/>
       <c r="J16" s="55"/>
       <c r="K16" s="50"/>
       <c r="L16" s="56"/>
@@ -8769,7 +8768,7 @@
       <c r="F17" s="13"/>
       <c r="G17" s="13"/>
       <c r="H17" s="13"/>
-      <c r="I17" s="78"/>
+      <c r="I17" s="77"/>
       <c r="J17" s="55"/>
       <c r="K17" s="50"/>
       <c r="L17" s="56"/>
@@ -8803,7 +8802,7 @@
       <c r="F18" s="13"/>
       <c r="G18" s="13"/>
       <c r="H18" s="13"/>
-      <c r="I18" s="78"/>
+      <c r="I18" s="77"/>
       <c r="J18" s="55"/>
       <c r="K18" s="50"/>
       <c r="L18" s="56"/>
@@ -8837,7 +8836,7 @@
       <c r="F19" s="13"/>
       <c r="G19" s="13"/>
       <c r="H19" s="13"/>
-      <c r="I19" s="78"/>
+      <c r="I19" s="77"/>
       <c r="J19" s="55"/>
       <c r="K19" s="50"/>
       <c r="L19" s="53"/>
@@ -8871,7 +8870,7 @@
       <c r="F20" s="13"/>
       <c r="G20" s="13"/>
       <c r="H20" s="13"/>
-      <c r="I20" s="78"/>
+      <c r="I20" s="77"/>
       <c r="J20" s="55"/>
       <c r="K20" s="50"/>
       <c r="L20" s="53"/>
@@ -8905,7 +8904,7 @@
       <c r="F21" s="13"/>
       <c r="G21" s="13"/>
       <c r="H21" s="13"/>
-      <c r="I21" s="78"/>
+      <c r="I21" s="77"/>
       <c r="J21" s="55"/>
       <c r="K21" s="50"/>
       <c r="L21" s="29"/>
@@ -8939,7 +8938,7 @@
       <c r="F22" s="13"/>
       <c r="G22" s="13"/>
       <c r="H22" s="13"/>
-      <c r="I22" s="78"/>
+      <c r="I22" s="77"/>
       <c r="J22" s="55"/>
       <c r="K22" s="50"/>
       <c r="L22" s="29"/>
@@ -9380,7 +9379,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B1:AE54"/>
-  <sheetFormatPr defaultColWidth="9.01953125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.03125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="1" min="1" style="0" width="11.52"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="10.01"/>
@@ -9659,7 +9658,7 @@
         <v>48</v>
       </c>
       <c r="I6" s="34" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="J6" s="35" t="s">
         <v>50</v>
@@ -9722,10 +9721,10 @@
       <c r="B7" s="69" t="n">
         <v>1</v>
       </c>
-      <c r="C7" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D7" s="80" t="s">
+      <c r="C7" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D7" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E7" s="71"/>
@@ -9756,25 +9755,25 @@
       <c r="B8" s="69" t="n">
         <v>2</v>
       </c>
-      <c r="C8" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D8" s="80" t="s">
+      <c r="C8" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D8" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E8" s="71" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="F8" s="66"/>
       <c r="G8" s="66"/>
       <c r="H8" s="66"/>
       <c r="I8" s="67" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="J8" s="68"/>
       <c r="K8" s="69"/>
       <c r="L8" s="70" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="M8" s="71"/>
       <c r="N8" s="73" t="s">
@@ -9798,25 +9797,25 @@
       <c r="B9" s="69" t="n">
         <v>3</v>
       </c>
-      <c r="C9" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D9" s="80" t="s">
+      <c r="C9" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D9" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E9" s="65" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F9" s="66"/>
       <c r="G9" s="66"/>
       <c r="H9" s="66"/>
       <c r="I9" s="67" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="J9" s="68"/>
       <c r="K9" s="69"/>
       <c r="L9" s="70" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="M9" s="71"/>
       <c r="N9" s="73" t="s">
@@ -9840,25 +9839,25 @@
       <c r="B10" s="69" t="n">
         <v>4</v>
       </c>
-      <c r="C10" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D10" s="80" t="s">
+      <c r="C10" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D10" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E10" s="65" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="F10" s="66"/>
       <c r="G10" s="66"/>
       <c r="H10" s="66"/>
       <c r="I10" s="67" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="J10" s="68"/>
       <c r="K10" s="69"/>
       <c r="L10" s="70" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="M10" s="71"/>
       <c r="N10" s="73" t="s">
@@ -9882,26 +9881,26 @@
       <c r="B11" s="69" t="n">
         <v>5</v>
       </c>
-      <c r="C11" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D11" s="80" t="s">
+      <c r="C11" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D11" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E11" s="0" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="I11" s="67" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="L11" s="70" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="M11" s="71" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="N11" s="73" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="O11" s="64"/>
       <c r="P11" s="29"/>
@@ -9921,10 +9920,10 @@
       <c r="B12" s="69" t="n">
         <v>6</v>
       </c>
-      <c r="C12" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D12" s="80" t="s">
+      <c r="C12" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D12" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E12" s="65"/>
@@ -9955,10 +9954,10 @@
       <c r="B13" s="69" t="n">
         <v>7</v>
       </c>
-      <c r="C13" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D13" s="80" t="s">
+      <c r="C13" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D13" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E13" s="65"/>
@@ -9989,10 +9988,10 @@
       <c r="B14" s="69" t="n">
         <v>8</v>
       </c>
-      <c r="C14" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D14" s="80" t="s">
+      <c r="C14" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D14" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E14" s="65"/>
@@ -10023,13 +10022,13 @@
       <c r="B15" s="69" t="n">
         <v>9</v>
       </c>
-      <c r="C15" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D15" s="80" t="s">
-        <v>3</v>
-      </c>
-      <c r="E15" s="85"/>
+      <c r="C15" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D15" s="79" t="s">
+        <v>3</v>
+      </c>
+      <c r="E15" s="84"/>
       <c r="F15" s="66"/>
       <c r="G15" s="66"/>
       <c r="H15" s="66"/>
@@ -10057,10 +10056,10 @@
       <c r="B16" s="69" t="n">
         <v>10</v>
       </c>
-      <c r="C16" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D16" s="80" t="s">
+      <c r="C16" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D16" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E16" s="65"/>
@@ -10072,7 +10071,7 @@
       <c r="K16" s="69"/>
       <c r="L16" s="70"/>
       <c r="M16" s="71"/>
-      <c r="N16" s="86"/>
+      <c r="N16" s="85"/>
       <c r="O16" s="64"/>
       <c r="P16" s="29"/>
       <c r="Q16" s="57"/>
@@ -10091,10 +10090,10 @@
       <c r="B17" s="69" t="n">
         <v>11</v>
       </c>
-      <c r="C17" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D17" s="80" t="s">
+      <c r="C17" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D17" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E17" s="65"/>
@@ -10125,10 +10124,10 @@
       <c r="B18" s="69" t="n">
         <v>12</v>
       </c>
-      <c r="C18" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D18" s="80" t="s">
+      <c r="C18" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D18" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E18" s="65"/>
@@ -10159,10 +10158,10 @@
       <c r="B19" s="69" t="n">
         <v>13</v>
       </c>
-      <c r="C19" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D19" s="80" t="s">
+      <c r="C19" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D19" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E19" s="65"/>
@@ -10193,10 +10192,10 @@
       <c r="B20" s="69" t="n">
         <v>14</v>
       </c>
-      <c r="C20" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D20" s="80" t="s">
+      <c r="C20" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D20" s="79" t="s">
         <v>3</v>
       </c>
       <c r="I20" s="67"/>
@@ -10219,14 +10218,14 @@
       <c r="B21" s="69" t="n">
         <v>15</v>
       </c>
-      <c r="C21" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D21" s="80" t="s">
+      <c r="C21" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D21" s="79" t="s">
         <v>3</v>
       </c>
       <c r="I21" s="67"/>
-      <c r="L21" s="87"/>
+      <c r="L21" s="86"/>
       <c r="N21" s="73"/>
       <c r="O21" s="64"/>
       <c r="P21" s="29"/>
@@ -10246,14 +10245,14 @@
       <c r="B22" s="69" t="n">
         <v>16</v>
       </c>
-      <c r="C22" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D22" s="80" t="s">
+      <c r="C22" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D22" s="79" t="s">
         <v>3</v>
       </c>
       <c r="I22" s="67"/>
-      <c r="L22" s="87"/>
+      <c r="L22" s="86"/>
       <c r="N22" s="73"/>
       <c r="O22" s="64"/>
       <c r="P22" s="29"/>
@@ -10273,10 +10272,10 @@
       <c r="B23" s="69" t="n">
         <v>17</v>
       </c>
-      <c r="C23" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D23" s="80" t="s">
+      <c r="C23" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D23" s="79" t="s">
         <v>3</v>
       </c>
       <c r="I23" s="67"/>
@@ -10299,10 +10298,10 @@
       <c r="B24" s="69" t="n">
         <v>18</v>
       </c>
-      <c r="C24" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D24" s="80" t="s">
+      <c r="C24" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D24" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E24" s="65"/>
@@ -10333,10 +10332,10 @@
       <c r="B25" s="69" t="n">
         <v>19</v>
       </c>
-      <c r="C25" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D25" s="80" t="s">
+      <c r="C25" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D25" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E25" s="65"/>
@@ -10346,7 +10345,7 @@
       <c r="I25" s="67"/>
       <c r="J25" s="68"/>
       <c r="K25" s="69"/>
-      <c r="L25" s="87"/>
+      <c r="L25" s="86"/>
       <c r="M25" s="71"/>
       <c r="N25" s="73"/>
       <c r="O25" s="64"/>
@@ -10367,31 +10366,31 @@
       <c r="B26" s="69" t="n">
         <v>20</v>
       </c>
-      <c r="C26" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D26" s="80" t="s">
+      <c r="C26" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D26" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E26" s="65" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="F26" s="66"/>
       <c r="G26" s="66"/>
       <c r="H26" s="66"/>
       <c r="I26" s="67" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="J26" s="68"/>
       <c r="K26" s="69"/>
       <c r="L26" s="65" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="M26" s="71" t="s">
         <v>78</v>
       </c>
       <c r="N26" s="73" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="O26" s="64"/>
       <c r="P26" s="29"/>
@@ -10411,25 +10410,25 @@
       <c r="B27" s="69" t="n">
         <v>21</v>
       </c>
-      <c r="C27" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D27" s="80" t="s">
+      <c r="C27" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D27" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E27" s="65" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="F27" s="66"/>
       <c r="G27" s="66"/>
       <c r="H27" s="66"/>
       <c r="I27" s="67" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="J27" s="68"/>
       <c r="K27" s="69"/>
       <c r="L27" s="70" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="M27" s="71"/>
       <c r="N27" s="73" t="s">
@@ -10453,25 +10452,25 @@
       <c r="B28" s="69" t="n">
         <v>22</v>
       </c>
-      <c r="C28" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D28" s="80" t="s">
+      <c r="C28" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D28" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E28" s="65" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="F28" s="66"/>
       <c r="G28" s="66"/>
       <c r="H28" s="66"/>
       <c r="I28" s="67" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="J28" s="68"/>
       <c r="K28" s="69"/>
       <c r="L28" s="70" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="M28" s="71"/>
       <c r="N28" s="73" t="s">
@@ -10495,25 +10494,25 @@
       <c r="B29" s="69" t="n">
         <v>23</v>
       </c>
-      <c r="C29" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D29" s="80" t="s">
+      <c r="C29" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D29" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E29" s="65" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F29" s="66"/>
       <c r="G29" s="66"/>
       <c r="H29" s="66"/>
       <c r="I29" s="67" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="J29" s="68"/>
       <c r="K29" s="69"/>
       <c r="L29" s="70" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="M29" s="65"/>
       <c r="N29" s="73" t="s">
@@ -10537,25 +10536,25 @@
       <c r="B30" s="69" t="n">
         <v>24</v>
       </c>
-      <c r="C30" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D30" s="80" t="s">
+      <c r="C30" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D30" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E30" s="65" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="F30" s="66"/>
       <c r="G30" s="66"/>
       <c r="H30" s="66"/>
       <c r="I30" s="67" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="J30" s="68"/>
       <c r="K30" s="69"/>
       <c r="L30" s="70" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="M30" s="65"/>
       <c r="N30" s="73" t="s">
@@ -10579,10 +10578,10 @@
       <c r="B31" s="69" t="n">
         <v>1</v>
       </c>
-      <c r="C31" s="79" t="s">
+      <c r="C31" s="78" t="s">
         <v>86</v>
       </c>
-      <c r="D31" s="80" t="s">
+      <c r="D31" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E31" s="71"/>
@@ -10613,10 +10612,10 @@
       <c r="B32" s="69" t="n">
         <v>2</v>
       </c>
-      <c r="C32" s="79" t="s">
+      <c r="C32" s="78" t="s">
         <v>86</v>
       </c>
-      <c r="D32" s="80" t="s">
+      <c r="D32" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E32" s="71"/>
@@ -10647,25 +10646,25 @@
       <c r="B33" s="69" t="n">
         <v>3</v>
       </c>
-      <c r="C33" s="79" t="s">
+      <c r="C33" s="78" t="s">
         <v>86</v>
       </c>
-      <c r="D33" s="80" t="s">
+      <c r="D33" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E33" s="65" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="F33" s="66"/>
       <c r="G33" s="66"/>
       <c r="H33" s="66"/>
       <c r="I33" s="67" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="J33" s="68"/>
       <c r="K33" s="69"/>
       <c r="L33" s="70" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="M33" s="71"/>
       <c r="N33" s="73" t="s">
@@ -10689,25 +10688,25 @@
       <c r="B34" s="69" t="n">
         <v>4</v>
       </c>
-      <c r="C34" s="79" t="s">
+      <c r="C34" s="78" t="s">
         <v>86</v>
       </c>
-      <c r="D34" s="80" t="s">
+      <c r="D34" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E34" s="65" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="F34" s="66"/>
       <c r="G34" s="66"/>
       <c r="H34" s="66"/>
       <c r="I34" s="67" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="J34" s="68"/>
       <c r="K34" s="69"/>
       <c r="L34" s="70" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="M34" s="71"/>
       <c r="N34" s="73" t="s">
@@ -10731,10 +10730,10 @@
       <c r="B35" s="69" t="n">
         <v>5</v>
       </c>
-      <c r="C35" s="79" t="s">
+      <c r="C35" s="78" t="s">
         <v>86</v>
       </c>
-      <c r="D35" s="80" t="s">
+      <c r="D35" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E35" s="65"/>
@@ -10765,10 +10764,10 @@
       <c r="B36" s="69" t="n">
         <v>6</v>
       </c>
-      <c r="C36" s="79" t="s">
+      <c r="C36" s="78" t="s">
         <v>86</v>
       </c>
-      <c r="D36" s="80" t="s">
+      <c r="D36" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E36" s="65"/>
@@ -10799,10 +10798,10 @@
       <c r="B37" s="69" t="n">
         <v>7</v>
       </c>
-      <c r="C37" s="79" t="s">
+      <c r="C37" s="78" t="s">
         <v>86</v>
       </c>
-      <c r="D37" s="80" t="s">
+      <c r="D37" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E37" s="65"/>
@@ -10833,13 +10832,13 @@
       <c r="B38" s="69" t="n">
         <v>8</v>
       </c>
-      <c r="C38" s="79" t="s">
+      <c r="C38" s="78" t="s">
         <v>86</v>
       </c>
-      <c r="D38" s="80" t="s">
-        <v>3</v>
-      </c>
-      <c r="E38" s="82"/>
+      <c r="D38" s="79" t="s">
+        <v>3</v>
+      </c>
+      <c r="E38" s="81"/>
       <c r="F38" s="66"/>
       <c r="G38" s="66"/>
       <c r="H38" s="66"/>
@@ -10867,10 +10866,10 @@
       <c r="B39" s="69" t="n">
         <v>9</v>
       </c>
-      <c r="C39" s="79" t="s">
+      <c r="C39" s="78" t="s">
         <v>86</v>
       </c>
-      <c r="D39" s="80" t="s">
+      <c r="D39" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E39" s="65"/>
@@ -10901,10 +10900,10 @@
       <c r="B40" s="69" t="n">
         <v>10</v>
       </c>
-      <c r="C40" s="79" t="s">
+      <c r="C40" s="78" t="s">
         <v>86</v>
       </c>
-      <c r="D40" s="80" t="s">
+      <c r="D40" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E40" s="65"/>
@@ -10935,10 +10934,10 @@
       <c r="B41" s="69" t="n">
         <v>11</v>
       </c>
-      <c r="C41" s="79" t="s">
+      <c r="C41" s="78" t="s">
         <v>86</v>
       </c>
-      <c r="D41" s="80" t="s">
+      <c r="D41" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E41" s="65"/>
@@ -10969,13 +10968,13 @@
       <c r="B42" s="69" t="n">
         <v>12</v>
       </c>
-      <c r="C42" s="79" t="s">
+      <c r="C42" s="78" t="s">
         <v>86</v>
       </c>
-      <c r="D42" s="80" t="s">
-        <v>3</v>
-      </c>
-      <c r="E42" s="82"/>
+      <c r="D42" s="79" t="s">
+        <v>3</v>
+      </c>
+      <c r="E42" s="81"/>
       <c r="F42" s="66"/>
       <c r="G42" s="66"/>
       <c r="H42" s="66"/>
@@ -11003,10 +11002,10 @@
       <c r="B43" s="69" t="n">
         <v>13</v>
       </c>
-      <c r="C43" s="79" t="s">
+      <c r="C43" s="78" t="s">
         <v>86</v>
       </c>
-      <c r="D43" s="80" t="s">
+      <c r="D43" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E43" s="65"/>
@@ -11037,10 +11036,10 @@
       <c r="B44" s="69" t="n">
         <v>14</v>
       </c>
-      <c r="C44" s="79" t="s">
+      <c r="C44" s="78" t="s">
         <v>86</v>
       </c>
-      <c r="D44" s="80" t="s">
+      <c r="D44" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E44" s="65"/>
@@ -11071,10 +11070,10 @@
       <c r="B45" s="69" t="n">
         <v>15</v>
       </c>
-      <c r="C45" s="79" t="s">
+      <c r="C45" s="78" t="s">
         <v>86</v>
       </c>
-      <c r="D45" s="80" t="s">
+      <c r="D45" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E45" s="65"/>
@@ -11105,10 +11104,10 @@
       <c r="B46" s="69" t="n">
         <v>16</v>
       </c>
-      <c r="C46" s="79" t="s">
+      <c r="C46" s="78" t="s">
         <v>86</v>
       </c>
-      <c r="D46" s="80" t="s">
+      <c r="D46" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E46" s="65"/>
@@ -11139,10 +11138,10 @@
       <c r="B47" s="69" t="n">
         <v>17</v>
       </c>
-      <c r="C47" s="79" t="s">
+      <c r="C47" s="78" t="s">
         <v>86</v>
       </c>
-      <c r="D47" s="80" t="s">
+      <c r="D47" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E47" s="65"/>
@@ -11173,10 +11172,10 @@
       <c r="B48" s="69" t="n">
         <v>18</v>
       </c>
-      <c r="C48" s="79" t="s">
+      <c r="C48" s="78" t="s">
         <v>86</v>
       </c>
-      <c r="D48" s="80" t="s">
+      <c r="D48" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E48" s="65"/>
@@ -11207,10 +11206,10 @@
       <c r="B49" s="69" t="n">
         <v>19</v>
       </c>
-      <c r="C49" s="79" t="s">
+      <c r="C49" s="78" t="s">
         <v>86</v>
       </c>
-      <c r="D49" s="80" t="s">
+      <c r="D49" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E49" s="65"/>
@@ -11241,25 +11240,25 @@
       <c r="B50" s="69" t="n">
         <v>20</v>
       </c>
-      <c r="C50" s="79" t="s">
+      <c r="C50" s="78" t="s">
         <v>86</v>
       </c>
-      <c r="D50" s="80" t="s">
+      <c r="D50" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E50" s="65" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="F50" s="66"/>
       <c r="G50" s="66"/>
       <c r="H50" s="66"/>
       <c r="I50" s="67" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="J50" s="68"/>
       <c r="K50" s="69"/>
       <c r="L50" s="70" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="M50" s="71"/>
       <c r="N50" s="73" t="s">
@@ -11283,31 +11282,31 @@
       <c r="B51" s="69" t="n">
         <v>21</v>
       </c>
-      <c r="C51" s="79" t="s">
+      <c r="C51" s="78" t="s">
         <v>86</v>
       </c>
-      <c r="D51" s="80" t="s">
+      <c r="D51" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E51" s="65" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="F51" s="66"/>
       <c r="G51" s="66"/>
       <c r="H51" s="66"/>
       <c r="I51" s="67" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="J51" s="68"/>
       <c r="K51" s="69"/>
       <c r="L51" s="70" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="M51" s="71" t="s">
         <v>53</v>
       </c>
       <c r="N51" s="72" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="O51" s="64"/>
       <c r="P51" s="29"/>
@@ -11327,31 +11326,31 @@
       <c r="B52" s="69" t="n">
         <v>22</v>
       </c>
-      <c r="C52" s="79" t="s">
+      <c r="C52" s="78" t="s">
         <v>86</v>
       </c>
-      <c r="D52" s="80" t="s">
+      <c r="D52" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E52" s="65" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="F52" s="66"/>
       <c r="G52" s="66"/>
       <c r="H52" s="66"/>
       <c r="I52" s="67" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="J52" s="68"/>
       <c r="K52" s="69"/>
       <c r="L52" s="70" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="M52" s="71" t="s">
         <v>53</v>
       </c>
       <c r="N52" s="72" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="O52" s="64"/>
       <c r="P52" s="29"/>
@@ -11371,25 +11370,25 @@
       <c r="B53" s="69" t="n">
         <v>23</v>
       </c>
-      <c r="C53" s="79" t="s">
+      <c r="C53" s="78" t="s">
         <v>86</v>
       </c>
-      <c r="D53" s="80" t="s">
+      <c r="D53" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E53" s="65" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="F53" s="66"/>
       <c r="G53" s="66"/>
       <c r="H53" s="66"/>
       <c r="I53" s="67" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="J53" s="68"/>
       <c r="K53" s="69"/>
       <c r="L53" s="70" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="M53" s="65"/>
       <c r="N53" s="73" t="s">
@@ -11413,31 +11412,31 @@
       <c r="B54" s="69" t="n">
         <v>24</v>
       </c>
-      <c r="C54" s="79" t="s">
+      <c r="C54" s="78" t="s">
         <v>86</v>
       </c>
-      <c r="D54" s="80" t="s">
+      <c r="D54" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E54" s="65" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="F54" s="66"/>
       <c r="G54" s="66"/>
       <c r="H54" s="66"/>
       <c r="I54" s="67" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="J54" s="68"/>
       <c r="K54" s="69"/>
       <c r="L54" s="70" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="M54" s="71" t="s">
         <v>53</v>
       </c>
       <c r="N54" s="73" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="O54" s="64"/>
       <c r="P54" s="29"/>
@@ -11570,7 +11569,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B1:AE54"/>
-  <sheetFormatPr defaultColWidth="9.01953125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.03125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="1" min="1" style="0" width="11.52"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="10.01"/>
@@ -11849,7 +11848,7 @@
         <v>48</v>
       </c>
       <c r="I6" s="34" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="J6" s="35" t="s">
         <v>164</v>
@@ -11912,10 +11911,10 @@
       <c r="B7" s="69" t="n">
         <v>1</v>
       </c>
-      <c r="C7" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D7" s="80" t="s">
+      <c r="C7" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D7" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E7" s="71"/>
@@ -11946,33 +11945,33 @@
       <c r="B8" s="69" t="n">
         <v>2</v>
       </c>
-      <c r="C8" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D8" s="80" t="s">
+      <c r="C8" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D8" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E8" s="71" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="F8" s="66"/>
       <c r="G8" s="66"/>
       <c r="H8" s="66"/>
       <c r="I8" s="67" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="J8" s="68" t="s">
         <v>164</v>
       </c>
       <c r="K8" s="69"/>
       <c r="L8" s="71" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="M8" s="71" t="s">
         <v>53</v>
       </c>
       <c r="N8" s="73" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="O8" s="64"/>
       <c r="P8" s="29"/>
@@ -11992,27 +11991,27 @@
       <c r="B9" s="69" t="n">
         <v>3</v>
       </c>
-      <c r="C9" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D9" s="80" t="s">
+      <c r="C9" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D9" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E9" s="65" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="F9" s="66"/>
       <c r="G9" s="66"/>
       <c r="H9" s="66"/>
       <c r="I9" s="67" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="J9" s="68" t="s">
         <v>164</v>
       </c>
       <c r="K9" s="69"/>
       <c r="L9" s="65" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="M9" s="71"/>
       <c r="N9" s="73" t="s">
@@ -12036,33 +12035,33 @@
       <c r="B10" s="69" t="n">
         <v>4</v>
       </c>
-      <c r="C10" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D10" s="80" t="s">
+      <c r="C10" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D10" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E10" s="65" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="F10" s="66"/>
       <c r="G10" s="66"/>
       <c r="H10" s="66"/>
       <c r="I10" s="67" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="J10" s="68" t="s">
         <v>164</v>
       </c>
       <c r="K10" s="69"/>
       <c r="L10" s="65" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="M10" s="71" t="s">
         <v>53</v>
       </c>
       <c r="N10" s="73" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="O10" s="64"/>
       <c r="P10" s="29"/>
@@ -12082,29 +12081,29 @@
       <c r="B11" s="69" t="n">
         <v>5</v>
       </c>
-      <c r="C11" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D11" s="80" t="s">
+      <c r="C11" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D11" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E11" s="0" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="I11" s="67" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="J11" s="68" t="s">
         <v>164</v>
       </c>
       <c r="L11" s="0" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="M11" s="71" t="s">
         <v>53</v>
       </c>
       <c r="N11" s="73" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="O11" s="64"/>
       <c r="P11" s="29"/>
@@ -12124,33 +12123,33 @@
       <c r="B12" s="69" t="n">
         <v>6</v>
       </c>
-      <c r="C12" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D12" s="80" t="s">
+      <c r="C12" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D12" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E12" s="65" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="F12" s="66"/>
       <c r="G12" s="66"/>
       <c r="H12" s="66"/>
       <c r="I12" s="67" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="J12" s="68" t="s">
         <v>164</v>
       </c>
       <c r="K12" s="69"/>
       <c r="L12" s="70" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="M12" s="71" t="s">
         <v>53</v>
       </c>
       <c r="N12" s="73" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="O12" s="64"/>
       <c r="P12" s="29"/>
@@ -12170,33 +12169,33 @@
       <c r="B13" s="69" t="n">
         <v>7</v>
       </c>
-      <c r="C13" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D13" s="80" t="s">
+      <c r="C13" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D13" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E13" s="65" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="F13" s="66"/>
       <c r="G13" s="66"/>
       <c r="H13" s="66"/>
       <c r="I13" s="67" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="J13" s="68" t="s">
         <v>164</v>
       </c>
       <c r="K13" s="69"/>
       <c r="L13" s="70" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="M13" s="71" t="s">
         <v>53</v>
       </c>
       <c r="N13" s="73" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="O13" s="64"/>
       <c r="P13" s="29"/>
@@ -12216,10 +12215,10 @@
       <c r="B14" s="69" t="n">
         <v>8</v>
       </c>
-      <c r="C14" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D14" s="80" t="s">
+      <c r="C14" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D14" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E14" s="65"/>
@@ -12250,13 +12249,13 @@
       <c r="B15" s="69" t="n">
         <v>9</v>
       </c>
-      <c r="C15" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D15" s="80" t="s">
-        <v>3</v>
-      </c>
-      <c r="E15" s="85"/>
+      <c r="C15" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D15" s="79" t="s">
+        <v>3</v>
+      </c>
+      <c r="E15" s="84"/>
       <c r="F15" s="66"/>
       <c r="G15" s="66"/>
       <c r="H15" s="66"/>
@@ -12284,10 +12283,10 @@
       <c r="B16" s="69" t="n">
         <v>10</v>
       </c>
-      <c r="C16" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D16" s="80" t="s">
+      <c r="C16" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D16" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E16" s="65"/>
@@ -12299,7 +12298,7 @@
       <c r="K16" s="69"/>
       <c r="L16" s="70"/>
       <c r="M16" s="71"/>
-      <c r="N16" s="86"/>
+      <c r="N16" s="85"/>
       <c r="O16" s="64"/>
       <c r="P16" s="29"/>
       <c r="Q16" s="57"/>
@@ -12318,10 +12317,10 @@
       <c r="B17" s="69" t="n">
         <v>11</v>
       </c>
-      <c r="C17" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D17" s="80" t="s">
+      <c r="C17" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D17" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E17" s="65"/>
@@ -12352,10 +12351,10 @@
       <c r="B18" s="69" t="n">
         <v>12</v>
       </c>
-      <c r="C18" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D18" s="80" t="s">
+      <c r="C18" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D18" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E18" s="65"/>
@@ -12386,10 +12385,10 @@
       <c r="B19" s="69" t="n">
         <v>13</v>
       </c>
-      <c r="C19" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D19" s="80" t="s">
+      <c r="C19" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D19" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E19" s="65"/>
@@ -12420,10 +12419,10 @@
       <c r="B20" s="69" t="n">
         <v>14</v>
       </c>
-      <c r="C20" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D20" s="80" t="s">
+      <c r="C20" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D20" s="79" t="s">
         <v>3</v>
       </c>
       <c r="I20" s="67"/>
@@ -12446,14 +12445,14 @@
       <c r="B21" s="69" t="n">
         <v>15</v>
       </c>
-      <c r="C21" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D21" s="80" t="s">
+      <c r="C21" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D21" s="79" t="s">
         <v>3</v>
       </c>
       <c r="I21" s="67"/>
-      <c r="L21" s="87"/>
+      <c r="L21" s="86"/>
       <c r="N21" s="73"/>
       <c r="O21" s="64"/>
       <c r="P21" s="29"/>
@@ -12473,14 +12472,14 @@
       <c r="B22" s="69" t="n">
         <v>16</v>
       </c>
-      <c r="C22" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D22" s="80" t="s">
+      <c r="C22" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D22" s="79" t="s">
         <v>3</v>
       </c>
       <c r="I22" s="67"/>
-      <c r="L22" s="87"/>
+      <c r="L22" s="86"/>
       <c r="N22" s="73"/>
       <c r="O22" s="64"/>
       <c r="P22" s="29"/>
@@ -12500,10 +12499,10 @@
       <c r="B23" s="69" t="n">
         <v>17</v>
       </c>
-      <c r="C23" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D23" s="80" t="s">
+      <c r="C23" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D23" s="79" t="s">
         <v>3</v>
       </c>
       <c r="I23" s="67"/>
@@ -12526,10 +12525,10 @@
       <c r="B24" s="69" t="n">
         <v>18</v>
       </c>
-      <c r="C24" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D24" s="80" t="s">
+      <c r="C24" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D24" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E24" s="65"/>
@@ -12560,10 +12559,10 @@
       <c r="B25" s="69" t="n">
         <v>19</v>
       </c>
-      <c r="C25" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D25" s="80" t="s">
+      <c r="C25" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D25" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E25" s="65"/>
@@ -12573,7 +12572,7 @@
       <c r="I25" s="67"/>
       <c r="J25" s="68"/>
       <c r="K25" s="69"/>
-      <c r="L25" s="87"/>
+      <c r="L25" s="86"/>
       <c r="M25" s="71"/>
       <c r="N25" s="73"/>
       <c r="O25" s="64"/>
@@ -12594,10 +12593,10 @@
       <c r="B26" s="69" t="n">
         <v>20</v>
       </c>
-      <c r="C26" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D26" s="80" t="s">
+      <c r="C26" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D26" s="79" t="s">
         <v>3</v>
       </c>
       <c r="O26" s="64"/>
@@ -12618,29 +12617,29 @@
       <c r="B27" s="69" t="n">
         <v>21</v>
       </c>
-      <c r="C27" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D27" s="80" t="s">
+      <c r="C27" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D27" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E27" s="0" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="I27" s="67" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="J27" s="68" t="s">
         <v>164</v>
       </c>
       <c r="L27" s="0" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="M27" s="71" t="s">
         <v>53</v>
       </c>
       <c r="N27" s="73" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="O27" s="64"/>
       <c r="P27" s="29"/>
@@ -12660,33 +12659,33 @@
       <c r="B28" s="69" t="n">
         <v>22</v>
       </c>
-      <c r="C28" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D28" s="80" t="s">
+      <c r="C28" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D28" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E28" s="65" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="F28" s="66"/>
       <c r="G28" s="66"/>
       <c r="H28" s="66"/>
       <c r="I28" s="67" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="J28" s="68" t="s">
         <v>164</v>
       </c>
       <c r="K28" s="69"/>
-      <c r="L28" s="87" t="s">
-        <v>438</v>
+      <c r="L28" s="86" t="s">
+        <v>439</v>
       </c>
       <c r="M28" s="71" t="s">
         <v>53</v>
       </c>
       <c r="N28" s="72" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="O28" s="64"/>
       <c r="P28" s="29"/>
@@ -12706,33 +12705,33 @@
       <c r="B29" s="69" t="n">
         <v>23</v>
       </c>
-      <c r="C29" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D29" s="80" t="s">
+      <c r="C29" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D29" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E29" s="65" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="F29" s="66"/>
       <c r="G29" s="66"/>
       <c r="H29" s="66"/>
       <c r="I29" s="67" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="J29" s="68" t="s">
         <v>164</v>
       </c>
       <c r="K29" s="69"/>
       <c r="L29" s="70" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="M29" s="71" t="s">
         <v>53</v>
       </c>
       <c r="N29" s="72" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="O29" s="64"/>
       <c r="P29" s="29"/>
@@ -12752,33 +12751,33 @@
       <c r="B30" s="69" t="n">
         <v>24</v>
       </c>
-      <c r="C30" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D30" s="80" t="s">
+      <c r="C30" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D30" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E30" s="65" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="F30" s="66"/>
       <c r="G30" s="66"/>
       <c r="H30" s="66"/>
       <c r="I30" s="67" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="J30" s="68" t="s">
         <v>164</v>
       </c>
       <c r="K30" s="69"/>
       <c r="L30" s="65" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="M30" s="71" t="s">
         <v>53</v>
       </c>
       <c r="N30" s="72" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="O30" s="64"/>
       <c r="P30" s="29"/>
@@ -12798,10 +12797,10 @@
       <c r="B31" s="69" t="n">
         <v>1</v>
       </c>
-      <c r="C31" s="79" t="s">
+      <c r="C31" s="78" t="s">
         <v>86</v>
       </c>
-      <c r="D31" s="80" t="s">
+      <c r="D31" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E31" s="71"/>
@@ -12832,27 +12831,27 @@
       <c r="B32" s="69" t="n">
         <v>3</v>
       </c>
-      <c r="C32" s="79" t="s">
+      <c r="C32" s="78" t="s">
         <v>86</v>
       </c>
-      <c r="D32" s="80" t="s">
+      <c r="D32" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E32" s="71" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="F32" s="66"/>
       <c r="G32" s="66"/>
       <c r="H32" s="66"/>
       <c r="I32" s="67" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="J32" s="68" t="s">
         <v>164</v>
       </c>
       <c r="K32" s="69"/>
       <c r="L32" s="70" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="M32" s="71"/>
       <c r="N32" s="73" t="s">
@@ -12876,27 +12875,27 @@
       <c r="B33" s="69" t="n">
         <v>4</v>
       </c>
-      <c r="C33" s="79" t="s">
+      <c r="C33" s="78" t="s">
         <v>86</v>
       </c>
-      <c r="D33" s="80" t="s">
+      <c r="D33" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E33" s="65" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="F33" s="66"/>
       <c r="G33" s="66"/>
       <c r="H33" s="66"/>
       <c r="I33" s="67" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="J33" s="68" t="s">
         <v>164</v>
       </c>
       <c r="K33" s="69"/>
       <c r="L33" s="70" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="M33" s="71" t="s">
         <v>53</v>
@@ -12922,10 +12921,10 @@
       <c r="B34" s="69" t="n">
         <v>4</v>
       </c>
-      <c r="C34" s="79" t="s">
+      <c r="C34" s="78" t="s">
         <v>86</v>
       </c>
-      <c r="D34" s="80" t="s">
+      <c r="D34" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E34" s="65"/>
@@ -12956,10 +12955,10 @@
       <c r="B35" s="69" t="n">
         <v>5</v>
       </c>
-      <c r="C35" s="79" t="s">
+      <c r="C35" s="78" t="s">
         <v>86</v>
       </c>
-      <c r="D35" s="80" t="s">
+      <c r="D35" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E35" s="65"/>
@@ -12990,10 +12989,10 @@
       <c r="B36" s="69" t="n">
         <v>6</v>
       </c>
-      <c r="C36" s="79" t="s">
+      <c r="C36" s="78" t="s">
         <v>86</v>
       </c>
-      <c r="D36" s="80" t="s">
+      <c r="D36" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E36" s="65"/>
@@ -13024,10 +13023,10 @@
       <c r="B37" s="69" t="n">
         <v>7</v>
       </c>
-      <c r="C37" s="79" t="s">
+      <c r="C37" s="78" t="s">
         <v>86</v>
       </c>
-      <c r="D37" s="80" t="s">
+      <c r="D37" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E37" s="65"/>
@@ -13058,13 +13057,13 @@
       <c r="B38" s="69" t="n">
         <v>8</v>
       </c>
-      <c r="C38" s="79" t="s">
+      <c r="C38" s="78" t="s">
         <v>86</v>
       </c>
-      <c r="D38" s="80" t="s">
-        <v>3</v>
-      </c>
-      <c r="E38" s="82"/>
+      <c r="D38" s="79" t="s">
+        <v>3</v>
+      </c>
+      <c r="E38" s="81"/>
       <c r="F38" s="66"/>
       <c r="G38" s="66"/>
       <c r="H38" s="66"/>
@@ -13092,10 +13091,10 @@
       <c r="B39" s="69" t="n">
         <v>9</v>
       </c>
-      <c r="C39" s="79" t="s">
+      <c r="C39" s="78" t="s">
         <v>86</v>
       </c>
-      <c r="D39" s="80" t="s">
+      <c r="D39" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E39" s="65"/>
@@ -13126,27 +13125,27 @@
       <c r="B40" s="69" t="n">
         <v>10</v>
       </c>
-      <c r="C40" s="79" t="s">
+      <c r="C40" s="78" t="s">
         <v>86</v>
       </c>
-      <c r="D40" s="80" t="s">
+      <c r="D40" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E40" s="65" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="F40" s="66"/>
       <c r="G40" s="66"/>
       <c r="H40" s="66"/>
       <c r="I40" s="67" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="J40" s="68" t="s">
         <v>164</v>
       </c>
       <c r="K40" s="69"/>
       <c r="L40" s="70" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="M40" s="71" t="s">
         <v>53</v>
@@ -13170,27 +13169,27 @@
       <c r="B41" s="69" t="n">
         <v>11</v>
       </c>
-      <c r="C41" s="79" t="s">
+      <c r="C41" s="78" t="s">
         <v>86</v>
       </c>
-      <c r="D41" s="80" t="s">
+      <c r="D41" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E41" s="65" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="F41" s="66"/>
       <c r="G41" s="66"/>
       <c r="H41" s="66"/>
       <c r="I41" s="67" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="J41" s="68" t="s">
         <v>164</v>
       </c>
       <c r="K41" s="69"/>
       <c r="L41" s="70" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="M41" s="71" t="s">
         <v>53</v>
@@ -13214,27 +13213,27 @@
       <c r="B42" s="69" t="n">
         <v>12</v>
       </c>
-      <c r="C42" s="79" t="s">
+      <c r="C42" s="78" t="s">
         <v>86</v>
       </c>
-      <c r="D42" s="80" t="s">
+      <c r="D42" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E42" s="65" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="F42" s="66"/>
       <c r="G42" s="66"/>
       <c r="H42" s="66"/>
       <c r="I42" s="67" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="J42" s="68" t="s">
         <v>164</v>
       </c>
       <c r="K42" s="69"/>
       <c r="L42" s="70" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="M42" s="71" t="s">
         <v>53</v>
@@ -13258,27 +13257,27 @@
       <c r="B43" s="69" t="n">
         <v>13</v>
       </c>
-      <c r="C43" s="79" t="s">
+      <c r="C43" s="78" t="s">
         <v>86</v>
       </c>
-      <c r="D43" s="80" t="s">
+      <c r="D43" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E43" s="65" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="F43" s="66"/>
       <c r="G43" s="66"/>
       <c r="H43" s="66"/>
       <c r="I43" s="67" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="J43" s="68" t="s">
         <v>164</v>
       </c>
       <c r="K43" s="69"/>
       <c r="L43" s="70" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="M43" s="71" t="s">
         <v>53</v>
@@ -13302,10 +13301,10 @@
       <c r="B44" s="69" t="n">
         <v>14</v>
       </c>
-      <c r="C44" s="79" t="s">
+      <c r="C44" s="78" t="s">
         <v>86</v>
       </c>
-      <c r="D44" s="80" t="s">
+      <c r="D44" s="79" t="s">
         <v>3</v>
       </c>
       <c r="N44" s="72"/>
@@ -13327,10 +13326,10 @@
       <c r="B45" s="69" t="n">
         <v>15</v>
       </c>
-      <c r="C45" s="79" t="s">
+      <c r="C45" s="78" t="s">
         <v>86</v>
       </c>
-      <c r="D45" s="80" t="s">
+      <c r="D45" s="79" t="s">
         <v>3</v>
       </c>
       <c r="N45" s="72"/>
@@ -13352,10 +13351,10 @@
       <c r="B46" s="69" t="n">
         <v>16</v>
       </c>
-      <c r="C46" s="79" t="s">
+      <c r="C46" s="78" t="s">
         <v>86</v>
       </c>
-      <c r="D46" s="80" t="s">
+      <c r="D46" s="79" t="s">
         <v>3</v>
       </c>
       <c r="N46" s="72"/>
@@ -13377,27 +13376,27 @@
       <c r="B47" s="69" t="n">
         <v>17</v>
       </c>
-      <c r="C47" s="79" t="s">
+      <c r="C47" s="78" t="s">
         <v>86</v>
       </c>
-      <c r="D47" s="80" t="s">
+      <c r="D47" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E47" s="65" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="F47" s="66"/>
       <c r="G47" s="66"/>
       <c r="H47" s="66"/>
       <c r="I47" s="67" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="J47" s="68" t="s">
         <v>164</v>
       </c>
       <c r="K47" s="69"/>
       <c r="L47" s="70" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="M47" s="71" t="s">
         <v>53</v>
@@ -13421,30 +13420,30 @@
       <c r="B48" s="69" t="n">
         <v>18</v>
       </c>
-      <c r="C48" s="79" t="s">
+      <c r="C48" s="78" t="s">
         <v>86</v>
       </c>
-      <c r="D48" s="80" t="s">
+      <c r="D48" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E48" s="65" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="F48" s="66"/>
       <c r="G48" s="66"/>
       <c r="H48" s="66"/>
       <c r="I48" s="67" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="J48" s="68" t="s">
         <v>164</v>
       </c>
       <c r="K48" s="69"/>
-      <c r="L48" s="87" t="s">
-        <v>461</v>
+      <c r="L48" s="86" t="s">
+        <v>462</v>
       </c>
       <c r="M48" s="71" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="N48" s="72"/>
       <c r="O48" s="64"/>
@@ -13465,10 +13464,10 @@
       <c r="B49" s="69" t="n">
         <v>19</v>
       </c>
-      <c r="C49" s="79" t="s">
+      <c r="C49" s="78" t="s">
         <v>86</v>
       </c>
-      <c r="D49" s="80" t="s">
+      <c r="D49" s="79" t="s">
         <v>62</v>
       </c>
       <c r="E49" s="65"/>
@@ -13499,30 +13498,30 @@
       <c r="B50" s="69" t="n">
         <v>20</v>
       </c>
-      <c r="C50" s="79" t="s">
+      <c r="C50" s="78" t="s">
         <v>86</v>
       </c>
-      <c r="D50" s="80" t="s">
+      <c r="D50" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E50" s="65" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="F50" s="66"/>
       <c r="G50" s="66"/>
       <c r="H50" s="66"/>
       <c r="I50" s="67" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="J50" s="68" t="s">
         <v>164</v>
       </c>
       <c r="K50" s="69"/>
       <c r="L50" s="70" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="M50" s="71" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="N50" s="72"/>
       <c r="O50" s="64"/>
@@ -13543,30 +13542,30 @@
       <c r="B51" s="69" t="n">
         <v>21</v>
       </c>
-      <c r="C51" s="79" t="s">
+      <c r="C51" s="78" t="s">
         <v>86</v>
       </c>
-      <c r="D51" s="80" t="s">
+      <c r="D51" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E51" s="65" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="F51" s="66"/>
       <c r="G51" s="66"/>
       <c r="H51" s="66"/>
       <c r="I51" s="67" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="J51" s="68" t="s">
         <v>164</v>
       </c>
       <c r="K51" s="69"/>
       <c r="L51" s="70" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="M51" s="71" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="N51" s="72"/>
       <c r="O51" s="64"/>
@@ -13587,31 +13586,31 @@
       <c r="B52" s="69" t="n">
         <v>22</v>
       </c>
-      <c r="C52" s="79" t="s">
+      <c r="C52" s="78" t="s">
         <v>86</v>
       </c>
-      <c r="D52" s="80" t="s">
+      <c r="D52" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E52" s="65" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="F52" s="66"/>
       <c r="G52" s="66"/>
       <c r="H52" s="66"/>
       <c r="I52" s="67" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="J52" s="68" t="s">
         <v>164</v>
       </c>
       <c r="K52" s="69"/>
       <c r="L52" s="65" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="M52" s="71"/>
       <c r="N52" s="73" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="O52" s="64"/>
       <c r="P52" s="29"/>
@@ -13631,27 +13630,27 @@
       <c r="B53" s="69" t="n">
         <v>23</v>
       </c>
-      <c r="C53" s="79" t="s">
+      <c r="C53" s="78" t="s">
         <v>86</v>
       </c>
-      <c r="D53" s="80" t="s">
+      <c r="D53" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E53" s="65" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="F53" s="66"/>
       <c r="G53" s="66"/>
       <c r="H53" s="66"/>
       <c r="I53" s="67" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="J53" s="68" t="s">
         <v>164</v>
       </c>
       <c r="K53" s="69"/>
       <c r="L53" s="70" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="M53" s="65"/>
       <c r="N53" s="73" t="s">
@@ -13675,27 +13674,27 @@
       <c r="B54" s="69" t="n">
         <v>24</v>
       </c>
-      <c r="C54" s="79" t="s">
+      <c r="C54" s="78" t="s">
         <v>86</v>
       </c>
-      <c r="D54" s="80" t="s">
+      <c r="D54" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E54" s="65" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="F54" s="66"/>
       <c r="G54" s="66"/>
       <c r="H54" s="66"/>
       <c r="I54" s="67" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="J54" s="68" t="s">
         <v>164</v>
       </c>
       <c r="K54" s="69"/>
       <c r="L54" s="70" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="M54" s="71"/>
       <c r="N54" s="73" t="s">
@@ -13832,7 +13831,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B1:AE79"/>
-  <sheetFormatPr defaultColWidth="9.01953125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.03125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="1" min="1" style="0" width="11.52"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="10.01"/>
@@ -14181,26 +14180,26 @@
         <v>3</v>
       </c>
       <c r="E7" s="53" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="F7" s="13"/>
       <c r="G7" s="13"/>
       <c r="H7" s="13"/>
-      <c r="I7" s="88" t="s">
+      <c r="I7" s="87" t="s">
         <v>49</v>
       </c>
-      <c r="J7" s="89" t="s">
+      <c r="J7" s="88" t="s">
         <v>50</v>
       </c>
       <c r="K7" s="50"/>
       <c r="L7" s="56" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="M7" s="53" t="s">
         <v>329</v>
       </c>
-      <c r="N7" s="87" t="s">
-        <v>474</v>
+      <c r="N7" s="86" t="s">
+        <v>475</v>
       </c>
       <c r="O7" s="56"/>
       <c r="P7" s="29"/>
@@ -14227,20 +14226,20 @@
         <v>3</v>
       </c>
       <c r="E8" s="53" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F8" s="13"/>
       <c r="G8" s="13"/>
       <c r="H8" s="13"/>
-      <c r="I8" s="88" t="s">
-        <v>476</v>
-      </c>
-      <c r="J8" s="89" t="s">
+      <c r="I8" s="87" t="s">
+        <v>477</v>
+      </c>
+      <c r="J8" s="88" t="s">
         <v>164</v>
       </c>
       <c r="K8" s="50"/>
       <c r="L8" s="56" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="M8" s="53" t="s">
         <v>108</v>
@@ -14249,7 +14248,7 @@
         <v>167</v>
       </c>
       <c r="O8" s="75" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="P8" s="29"/>
       <c r="Q8" s="57"/>
@@ -14265,36 +14264,36 @@
       <c r="AC8" s="63"/>
     </row>
     <row r="9" customFormat="false" ht="20.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="90" t="n">
+      <c r="B9" s="89" t="n">
         <v>1</v>
       </c>
-      <c r="C9" s="91" t="s">
-        <v>45</v>
-      </c>
-      <c r="D9" s="92" t="s">
+      <c r="C9" s="90" t="s">
+        <v>45</v>
+      </c>
+      <c r="D9" s="91" t="s">
         <v>62</v>
       </c>
-      <c r="E9" s="93" t="s">
-        <v>479</v>
-      </c>
-      <c r="F9" s="90"/>
-      <c r="G9" s="90"/>
-      <c r="H9" s="90"/>
-      <c r="I9" s="94" t="s">
+      <c r="E9" s="92" t="s">
         <v>480</v>
       </c>
-      <c r="J9" s="95" t="s">
+      <c r="F9" s="89"/>
+      <c r="G9" s="89"/>
+      <c r="H9" s="89"/>
+      <c r="I9" s="93" t="s">
+        <v>481</v>
+      </c>
+      <c r="J9" s="94" t="s">
         <v>164</v>
       </c>
-      <c r="K9" s="90"/>
-      <c r="L9" s="96" t="s">
-        <v>481</v>
-      </c>
-      <c r="M9" s="93"/>
-      <c r="N9" s="97"/>
-      <c r="O9" s="96"/>
-      <c r="P9" s="98"/>
-      <c r="Q9" s="96"/>
+      <c r="K9" s="89"/>
+      <c r="L9" s="95" t="s">
+        <v>482</v>
+      </c>
+      <c r="M9" s="92"/>
+      <c r="N9" s="96"/>
+      <c r="O9" s="95"/>
+      <c r="P9" s="97"/>
+      <c r="Q9" s="95"/>
       <c r="R9" s="58"/>
       <c r="U9" s="12"/>
       <c r="V9" s="59"/>
@@ -14317,15 +14316,15 @@
         <v>3</v>
       </c>
       <c r="E10" s="53" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="F10" s="13"/>
       <c r="G10" s="13"/>
       <c r="H10" s="13"/>
-      <c r="I10" s="88" t="s">
+      <c r="I10" s="87" t="s">
         <v>243</v>
       </c>
-      <c r="J10" s="89" t="s">
+      <c r="J10" s="88" t="s">
         <v>50</v>
       </c>
       <c r="K10" s="50"/>
@@ -14335,8 +14334,8 @@
       <c r="M10" s="53" t="s">
         <v>329</v>
       </c>
-      <c r="N10" s="87" t="s">
-        <v>474</v>
+      <c r="N10" s="86" t="s">
+        <v>475</v>
       </c>
       <c r="O10" s="56"/>
       <c r="P10" s="29"/>
@@ -14363,20 +14362,20 @@
         <v>3</v>
       </c>
       <c r="E11" s="53" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="F11" s="13"/>
       <c r="G11" s="13"/>
       <c r="H11" s="13"/>
-      <c r="I11" s="88" t="s">
+      <c r="I11" s="87" t="s">
         <v>176</v>
       </c>
-      <c r="J11" s="89" t="s">
+      <c r="J11" s="88" t="s">
         <v>164</v>
       </c>
       <c r="K11" s="50"/>
       <c r="L11" s="56" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="M11" s="53" t="s">
         <v>108</v>
@@ -14385,7 +14384,7 @@
         <v>167</v>
       </c>
       <c r="O11" s="75" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="P11" s="29"/>
       <c r="Q11" s="57"/>
@@ -14411,20 +14410,20 @@
         <v>3</v>
       </c>
       <c r="E12" s="53" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F12" s="13"/>
       <c r="G12" s="13"/>
       <c r="H12" s="13"/>
-      <c r="I12" s="88" t="s">
-        <v>476</v>
-      </c>
-      <c r="J12" s="89" t="s">
-        <v>486</v>
+      <c r="I12" s="87" t="s">
+        <v>477</v>
+      </c>
+      <c r="J12" s="88" t="s">
+        <v>487</v>
       </c>
       <c r="K12" s="50"/>
       <c r="L12" s="56" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="M12" s="53" t="s">
         <v>108</v>
@@ -14457,15 +14456,15 @@
         <v>3</v>
       </c>
       <c r="E13" s="53" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="F13" s="13"/>
       <c r="G13" s="13"/>
       <c r="H13" s="13"/>
-      <c r="I13" s="88" t="s">
+      <c r="I13" s="87" t="s">
         <v>163</v>
       </c>
-      <c r="J13" s="89" t="s">
+      <c r="J13" s="88" t="s">
         <v>164</v>
       </c>
       <c r="K13" s="50"/>
@@ -14479,7 +14478,7 @@
         <v>167</v>
       </c>
       <c r="O13" s="75" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="P13" s="29"/>
       <c r="Q13" s="57"/>
@@ -14505,20 +14504,20 @@
         <v>3</v>
       </c>
       <c r="E14" s="53" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="F14" s="13"/>
       <c r="G14" s="13"/>
       <c r="H14" s="13"/>
-      <c r="I14" s="88" t="s">
+      <c r="I14" s="87" t="s">
         <v>200</v>
       </c>
-      <c r="J14" s="89" t="s">
+      <c r="J14" s="88" t="s">
         <v>164</v>
       </c>
       <c r="K14" s="50"/>
       <c r="L14" s="56" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="M14" s="53" t="s">
         <v>108</v>
@@ -14553,26 +14552,26 @@
         <v>3</v>
       </c>
       <c r="E15" s="53" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="F15" s="13"/>
       <c r="G15" s="13"/>
       <c r="H15" s="13"/>
-      <c r="I15" s="88" t="s">
-        <v>492</v>
-      </c>
-      <c r="J15" s="89" t="s">
+      <c r="I15" s="87" t="s">
+        <v>493</v>
+      </c>
+      <c r="J15" s="88" t="s">
         <v>50</v>
       </c>
       <c r="K15" s="50"/>
       <c r="L15" s="56" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="M15" s="53" t="s">
         <v>329</v>
       </c>
-      <c r="N15" s="87" t="s">
-        <v>474</v>
+      <c r="N15" s="86" t="s">
+        <v>475</v>
       </c>
       <c r="O15" s="56"/>
       <c r="P15" s="29"/>
@@ -14589,36 +14588,36 @@
       <c r="AC15" s="63"/>
     </row>
     <row r="16" customFormat="false" ht="20.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="90" t="n">
+      <c r="B16" s="89" t="n">
         <v>1</v>
       </c>
-      <c r="C16" s="91" t="s">
-        <v>45</v>
-      </c>
-      <c r="D16" s="92" t="s">
+      <c r="C16" s="90" t="s">
+        <v>45</v>
+      </c>
+      <c r="D16" s="91" t="s">
         <v>62</v>
       </c>
-      <c r="E16" s="93" t="s">
-        <v>479</v>
-      </c>
-      <c r="F16" s="90"/>
-      <c r="G16" s="90"/>
-      <c r="H16" s="90"/>
-      <c r="I16" s="94" t="s">
+      <c r="E16" s="92" t="s">
         <v>480</v>
       </c>
-      <c r="J16" s="95" t="s">
-        <v>486</v>
-      </c>
-      <c r="K16" s="90"/>
-      <c r="L16" s="96" t="s">
+      <c r="F16" s="89"/>
+      <c r="G16" s="89"/>
+      <c r="H16" s="89"/>
+      <c r="I16" s="93" t="s">
         <v>481</v>
       </c>
-      <c r="M16" s="93"/>
-      <c r="N16" s="97"/>
-      <c r="O16" s="96"/>
-      <c r="P16" s="98"/>
-      <c r="Q16" s="96"/>
+      <c r="J16" s="94" t="s">
+        <v>487</v>
+      </c>
+      <c r="K16" s="89"/>
+      <c r="L16" s="95" t="s">
+        <v>482</v>
+      </c>
+      <c r="M16" s="92"/>
+      <c r="N16" s="96"/>
+      <c r="O16" s="95"/>
+      <c r="P16" s="97"/>
+      <c r="Q16" s="95"/>
       <c r="R16" s="58"/>
       <c r="U16" s="12"/>
       <c r="V16" s="59"/>
@@ -14641,20 +14640,20 @@
         <v>3</v>
       </c>
       <c r="E17" s="53" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="F17" s="13"/>
       <c r="G17" s="13"/>
       <c r="H17" s="13"/>
-      <c r="I17" s="88" t="s">
+      <c r="I17" s="87" t="s">
         <v>205</v>
       </c>
-      <c r="J17" s="89" t="s">
+      <c r="J17" s="88" t="s">
         <v>164</v>
       </c>
       <c r="K17" s="50"/>
       <c r="L17" s="56" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="M17" s="53" t="s">
         <v>108</v>
@@ -14689,20 +14688,20 @@
         <v>3</v>
       </c>
       <c r="E18" s="53" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="F18" s="13"/>
       <c r="G18" s="13"/>
       <c r="H18" s="13"/>
-      <c r="I18" s="88" t="s">
+      <c r="I18" s="87" t="s">
         <v>176</v>
       </c>
-      <c r="J18" s="89" t="s">
-        <v>486</v>
+      <c r="J18" s="88" t="s">
+        <v>487</v>
       </c>
       <c r="K18" s="50"/>
       <c r="L18" s="56" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="M18" s="53" t="s">
         <v>108</v>
@@ -14735,26 +14734,26 @@
         <v>3</v>
       </c>
       <c r="E19" s="53" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="F19" s="13"/>
       <c r="G19" s="13"/>
       <c r="H19" s="13"/>
-      <c r="I19" s="88" t="s">
+      <c r="I19" s="87" t="s">
         <v>271</v>
       </c>
-      <c r="J19" s="89" t="s">
+      <c r="J19" s="88" t="s">
         <v>50</v>
       </c>
       <c r="K19" s="50"/>
       <c r="L19" s="56" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="M19" s="53" t="s">
         <v>255</v>
       </c>
-      <c r="N19" s="87" t="s">
-        <v>498</v>
+      <c r="N19" s="86" t="s">
+        <v>499</v>
       </c>
       <c r="O19" s="56"/>
       <c r="P19" s="29"/>
@@ -14781,16 +14780,16 @@
         <v>3</v>
       </c>
       <c r="E20" s="53" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="F20" s="13"/>
       <c r="G20" s="13"/>
       <c r="H20" s="13"/>
-      <c r="I20" s="88" t="s">
+      <c r="I20" s="87" t="s">
         <v>163</v>
       </c>
-      <c r="J20" s="89" t="s">
-        <v>486</v>
+      <c r="J20" s="88" t="s">
+        <v>487</v>
       </c>
       <c r="K20" s="50"/>
       <c r="L20" s="56" t="s">
@@ -14827,20 +14826,20 @@
         <v>3</v>
       </c>
       <c r="E21" s="53" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="F21" s="13"/>
       <c r="G21" s="13"/>
       <c r="H21" s="13"/>
-      <c r="I21" s="88" t="s">
+      <c r="I21" s="87" t="s">
         <v>179</v>
       </c>
-      <c r="J21" s="89" t="s">
+      <c r="J21" s="88" t="s">
         <v>164</v>
       </c>
       <c r="K21" s="50"/>
       <c r="L21" s="56" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="M21" s="53" t="s">
         <v>108</v>
@@ -14875,20 +14874,20 @@
         <v>3</v>
       </c>
       <c r="E22" s="53" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="F22" s="13"/>
       <c r="G22" s="13"/>
       <c r="H22" s="13"/>
-      <c r="I22" s="88" t="s">
+      <c r="I22" s="87" t="s">
         <v>200</v>
       </c>
-      <c r="J22" s="89" t="s">
-        <v>486</v>
+      <c r="J22" s="88" t="s">
+        <v>487</v>
       </c>
       <c r="K22" s="50"/>
       <c r="L22" s="56" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="M22" s="53" t="s">
         <v>108</v>
@@ -14921,20 +14920,20 @@
         <v>3</v>
       </c>
       <c r="E23" s="53" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F23" s="13"/>
       <c r="G23" s="13"/>
       <c r="H23" s="13"/>
-      <c r="I23" s="88" t="s">
+      <c r="I23" s="87" t="s">
         <v>183</v>
       </c>
-      <c r="J23" s="89" t="s">
+      <c r="J23" s="88" t="s">
         <v>164</v>
       </c>
       <c r="K23" s="50"/>
       <c r="L23" s="56" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="M23" s="53" t="s">
         <v>108</v>
@@ -14969,26 +14968,26 @@
         <v>3</v>
       </c>
       <c r="E24" s="53" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="F24" s="13"/>
       <c r="G24" s="13"/>
       <c r="H24" s="13"/>
-      <c r="I24" s="88" t="s">
+      <c r="I24" s="87" t="s">
         <v>89</v>
       </c>
-      <c r="J24" s="89" t="s">
+      <c r="J24" s="88" t="s">
         <v>50</v>
       </c>
       <c r="K24" s="50"/>
       <c r="L24" s="56" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="M24" s="53" t="s">
         <v>329</v>
       </c>
-      <c r="N24" s="87" t="s">
-        <v>474</v>
+      <c r="N24" s="86" t="s">
+        <v>475</v>
       </c>
       <c r="O24" s="56"/>
       <c r="P24" s="29"/>
@@ -15015,20 +15014,20 @@
         <v>3</v>
       </c>
       <c r="E25" s="53" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="F25" s="13"/>
       <c r="G25" s="13"/>
       <c r="H25" s="13"/>
-      <c r="I25" s="88" t="s">
+      <c r="I25" s="87" t="s">
         <v>205</v>
       </c>
-      <c r="J25" s="89" t="s">
-        <v>486</v>
+      <c r="J25" s="88" t="s">
+        <v>487</v>
       </c>
       <c r="K25" s="50"/>
       <c r="L25" s="56" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="M25" s="53" t="s">
         <v>108</v>
@@ -15061,20 +15060,20 @@
         <v>3</v>
       </c>
       <c r="E26" s="53" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F26" s="13"/>
       <c r="G26" s="13"/>
       <c r="H26" s="13"/>
-      <c r="I26" s="88" t="s">
+      <c r="I26" s="87" t="s">
         <v>195</v>
       </c>
-      <c r="J26" s="89" t="s">
+      <c r="J26" s="88" t="s">
         <v>164</v>
       </c>
       <c r="K26" s="50"/>
       <c r="L26" s="56" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="M26" s="53" t="s">
         <v>108</v>
@@ -15109,20 +15108,20 @@
         <v>3</v>
       </c>
       <c r="E27" s="53" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="F27" s="13"/>
       <c r="G27" s="13"/>
       <c r="H27" s="13"/>
-      <c r="I27" s="88" t="s">
+      <c r="I27" s="87" t="s">
         <v>219</v>
       </c>
-      <c r="J27" s="89" t="s">
+      <c r="J27" s="88" t="s">
         <v>164</v>
       </c>
       <c r="K27" s="50"/>
       <c r="L27" s="56" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="M27" s="53" t="s">
         <v>108</v>
@@ -15157,26 +15156,26 @@
         <v>3</v>
       </c>
       <c r="E28" s="53" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="F28" s="13"/>
       <c r="G28" s="13"/>
       <c r="H28" s="13"/>
-      <c r="I28" s="88" t="s">
+      <c r="I28" s="87" t="s">
         <v>305</v>
       </c>
-      <c r="J28" s="89" t="s">
+      <c r="J28" s="88" t="s">
         <v>50</v>
       </c>
       <c r="K28" s="50"/>
       <c r="L28" s="56" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="M28" s="53" t="s">
         <v>329</v>
       </c>
-      <c r="N28" s="87" t="s">
-        <v>474</v>
+      <c r="N28" s="86" t="s">
+        <v>475</v>
       </c>
       <c r="O28" s="56"/>
       <c r="P28" s="29"/>
@@ -15203,20 +15202,20 @@
         <v>3</v>
       </c>
       <c r="E29" s="53" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="F29" s="13"/>
       <c r="G29" s="13"/>
       <c r="H29" s="13"/>
-      <c r="I29" s="88" t="s">
+      <c r="I29" s="87" t="s">
         <v>179</v>
       </c>
-      <c r="J29" s="89" t="s">
-        <v>486</v>
+      <c r="J29" s="88" t="s">
+        <v>487</v>
       </c>
       <c r="K29" s="50"/>
       <c r="L29" s="56" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="M29" s="53" t="s">
         <v>108</v>
@@ -15249,20 +15248,20 @@
         <v>3</v>
       </c>
       <c r="E30" s="53" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="F30" s="13"/>
       <c r="G30" s="13"/>
       <c r="H30" s="13"/>
-      <c r="I30" s="88" t="s">
+      <c r="I30" s="87" t="s">
         <v>222</v>
       </c>
-      <c r="J30" s="89" t="s">
+      <c r="J30" s="88" t="s">
         <v>164</v>
       </c>
       <c r="K30" s="50"/>
       <c r="L30" s="56" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="M30" s="53" t="s">
         <v>108</v>
@@ -15297,20 +15296,20 @@
         <v>3</v>
       </c>
       <c r="E31" s="53" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F31" s="13"/>
       <c r="G31" s="13"/>
       <c r="H31" s="13"/>
-      <c r="I31" s="88" t="s">
+      <c r="I31" s="87" t="s">
         <v>183</v>
       </c>
-      <c r="J31" s="89" t="s">
-        <v>486</v>
+      <c r="J31" s="88" t="s">
+        <v>487</v>
       </c>
       <c r="K31" s="50"/>
       <c r="L31" s="56" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="M31" s="53" t="s">
         <v>108</v>
@@ -15343,20 +15342,20 @@
         <v>3</v>
       </c>
       <c r="E32" s="53" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="F32" s="13"/>
       <c r="G32" s="13"/>
       <c r="H32" s="13"/>
-      <c r="I32" s="88" t="s">
+      <c r="I32" s="87" t="s">
         <v>225</v>
       </c>
-      <c r="J32" s="89" t="s">
+      <c r="J32" s="88" t="s">
         <v>164</v>
       </c>
       <c r="K32" s="50"/>
       <c r="L32" s="56" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="M32" s="53" t="s">
         <v>108</v>
@@ -15391,26 +15390,26 @@
         <v>3</v>
       </c>
       <c r="E33" s="53" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="F33" s="13"/>
       <c r="G33" s="13"/>
       <c r="H33" s="13"/>
-      <c r="I33" s="88" t="s">
+      <c r="I33" s="87" t="s">
         <v>313</v>
       </c>
-      <c r="J33" s="89" t="s">
+      <c r="J33" s="88" t="s">
         <v>50</v>
       </c>
       <c r="K33" s="50"/>
       <c r="L33" s="56" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="M33" s="53" t="s">
         <v>329</v>
       </c>
-      <c r="N33" s="87" t="s">
-        <v>474</v>
+      <c r="N33" s="86" t="s">
+        <v>475</v>
       </c>
       <c r="O33" s="56"/>
       <c r="P33" s="29"/>
@@ -15437,15 +15436,15 @@
         <v>3</v>
       </c>
       <c r="E34" s="53" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="F34" s="13"/>
       <c r="G34" s="13"/>
       <c r="H34" s="13"/>
-      <c r="I34" s="88" t="s">
+      <c r="I34" s="87" t="s">
         <v>190</v>
       </c>
-      <c r="J34" s="89" t="s">
+      <c r="J34" s="88" t="s">
         <v>164</v>
       </c>
       <c r="K34" s="50"/>
@@ -15483,20 +15482,20 @@
         <v>3</v>
       </c>
       <c r="E35" s="53" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F35" s="13"/>
       <c r="G35" s="13"/>
       <c r="H35" s="13"/>
-      <c r="I35" s="88" t="s">
+      <c r="I35" s="87" t="s">
         <v>195</v>
       </c>
-      <c r="J35" s="89" t="s">
-        <v>486</v>
+      <c r="J35" s="88" t="s">
+        <v>487</v>
       </c>
       <c r="K35" s="50"/>
       <c r="L35" s="56" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="M35" s="53" t="s">
         <v>108</v>
@@ -15529,20 +15528,20 @@
         <v>3</v>
       </c>
       <c r="E36" s="53" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="F36" s="13"/>
       <c r="G36" s="13"/>
       <c r="H36" s="13"/>
-      <c r="I36" s="88" t="s">
+      <c r="I36" s="87" t="s">
         <v>228</v>
       </c>
-      <c r="J36" s="89" t="s">
+      <c r="J36" s="88" t="s">
         <v>164</v>
       </c>
       <c r="K36" s="50"/>
       <c r="L36" s="56" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="M36" s="53" t="s">
         <v>108</v>
@@ -15575,20 +15574,20 @@
         <v>3</v>
       </c>
       <c r="E37" s="53" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="F37" s="13"/>
       <c r="G37" s="13"/>
       <c r="H37" s="13"/>
-      <c r="I37" s="88" t="s">
+      <c r="I37" s="87" t="s">
         <v>219</v>
       </c>
-      <c r="J37" s="89" t="s">
-        <v>486</v>
+      <c r="J37" s="88" t="s">
+        <v>487</v>
       </c>
       <c r="K37" s="50"/>
       <c r="L37" s="56" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="M37" s="53" t="s">
         <v>108</v>
@@ -15621,15 +15620,15 @@
         <v>3</v>
       </c>
       <c r="E38" s="53" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="F38" s="13"/>
       <c r="G38" s="13"/>
       <c r="H38" s="13"/>
-      <c r="I38" s="88" t="s">
+      <c r="I38" s="87" t="s">
         <v>192</v>
       </c>
-      <c r="J38" s="89" t="s">
+      <c r="J38" s="88" t="s">
         <v>164</v>
       </c>
       <c r="K38" s="50"/>
@@ -15667,26 +15666,26 @@
         <v>3</v>
       </c>
       <c r="E39" s="53" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="F39" s="13"/>
       <c r="G39" s="13"/>
       <c r="H39" s="13"/>
-      <c r="I39" s="88" t="s">
+      <c r="I39" s="87" t="s">
         <v>326</v>
       </c>
-      <c r="J39" s="89" t="s">
+      <c r="J39" s="88" t="s">
         <v>50</v>
       </c>
       <c r="K39" s="50"/>
       <c r="L39" s="56" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="M39" s="53" t="s">
         <v>329</v>
       </c>
-      <c r="N39" s="87" t="s">
-        <v>474</v>
+      <c r="N39" s="86" t="s">
+        <v>475</v>
       </c>
       <c r="O39" s="56"/>
       <c r="P39" s="29"/>
@@ -15713,20 +15712,20 @@
         <v>3</v>
       </c>
       <c r="E40" s="53" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="F40" s="13"/>
       <c r="G40" s="13"/>
       <c r="H40" s="13"/>
-      <c r="I40" s="88" t="s">
+      <c r="I40" s="87" t="s">
         <v>222</v>
       </c>
-      <c r="J40" s="89" t="s">
-        <v>486</v>
+      <c r="J40" s="88" t="s">
+        <v>487</v>
       </c>
       <c r="K40" s="50"/>
       <c r="L40" s="56" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="M40" s="53" t="s">
         <v>108</v>
@@ -15759,20 +15758,20 @@
         <v>3</v>
       </c>
       <c r="E41" s="53" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="F41" s="13"/>
       <c r="G41" s="13"/>
       <c r="H41" s="13"/>
-      <c r="I41" s="88" t="s">
+      <c r="I41" s="87" t="s">
         <v>232</v>
       </c>
-      <c r="J41" s="89" t="s">
+      <c r="J41" s="88" t="s">
         <v>164</v>
       </c>
       <c r="K41" s="50"/>
       <c r="L41" s="56" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="M41" s="53" t="s">
         <v>108</v>
@@ -15805,20 +15804,20 @@
         <v>3</v>
       </c>
       <c r="E42" s="53" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="F42" s="13"/>
       <c r="G42" s="13"/>
       <c r="H42" s="13"/>
-      <c r="I42" s="88" t="s">
+      <c r="I42" s="87" t="s">
         <v>225</v>
       </c>
-      <c r="J42" s="89" t="s">
-        <v>486</v>
+      <c r="J42" s="88" t="s">
+        <v>487</v>
       </c>
       <c r="K42" s="50"/>
       <c r="L42" s="56" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="M42" s="53" t="s">
         <v>108</v>
@@ -15851,20 +15850,20 @@
         <v>3</v>
       </c>
       <c r="E43" s="53" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="F43" s="13"/>
       <c r="G43" s="13"/>
       <c r="H43" s="13"/>
-      <c r="I43" s="88" t="s">
-        <v>526</v>
-      </c>
-      <c r="J43" s="89" t="s">
+      <c r="I43" s="87" t="s">
+        <v>527</v>
+      </c>
+      <c r="J43" s="88" t="s">
         <v>164</v>
       </c>
       <c r="K43" s="50"/>
       <c r="L43" s="56" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="M43" s="53" t="s">
         <v>108</v>
@@ -15897,26 +15896,26 @@
         <v>3</v>
       </c>
       <c r="E44" s="53" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="F44" s="13"/>
       <c r="G44" s="13"/>
       <c r="H44" s="13"/>
-      <c r="I44" s="88" t="s">
+      <c r="I44" s="87" t="s">
         <v>324</v>
       </c>
-      <c r="J44" s="89" t="s">
+      <c r="J44" s="88" t="s">
         <v>50</v>
       </c>
       <c r="K44" s="50"/>
       <c r="L44" s="56" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="M44" s="53" t="s">
         <v>329</v>
       </c>
-      <c r="N44" s="87" t="s">
-        <v>474</v>
+      <c r="N44" s="86" t="s">
+        <v>475</v>
       </c>
       <c r="O44" s="56"/>
       <c r="P44" s="29"/>
@@ -15943,16 +15942,16 @@
         <v>3</v>
       </c>
       <c r="E45" s="53" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="F45" s="13"/>
       <c r="G45" s="13"/>
       <c r="H45" s="13"/>
-      <c r="I45" s="88" t="s">
+      <c r="I45" s="87" t="s">
         <v>190</v>
       </c>
-      <c r="J45" s="89" t="s">
-        <v>486</v>
+      <c r="J45" s="88" t="s">
+        <v>487</v>
       </c>
       <c r="K45" s="50"/>
       <c r="L45" s="56" t="s">
@@ -15989,20 +15988,20 @@
         <v>3</v>
       </c>
       <c r="E46" s="53" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="F46" s="13"/>
       <c r="G46" s="13"/>
       <c r="H46" s="13"/>
-      <c r="I46" s="88" t="s">
-        <v>531</v>
-      </c>
-      <c r="J46" s="89" t="s">
+      <c r="I46" s="87" t="s">
+        <v>532</v>
+      </c>
+      <c r="J46" s="88" t="s">
         <v>164</v>
       </c>
       <c r="K46" s="50"/>
       <c r="L46" s="56" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="M46" s="53" t="s">
         <v>108</v>
@@ -16035,20 +16034,20 @@
         <v>3</v>
       </c>
       <c r="E47" s="53" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="F47" s="13"/>
       <c r="G47" s="13"/>
       <c r="H47" s="13"/>
-      <c r="I47" s="88" t="s">
+      <c r="I47" s="87" t="s">
         <v>228</v>
       </c>
-      <c r="J47" s="89" t="s">
-        <v>486</v>
+      <c r="J47" s="88" t="s">
+        <v>487</v>
       </c>
       <c r="K47" s="50"/>
       <c r="L47" s="56" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="M47" s="53" t="s">
         <v>108</v>
@@ -16081,20 +16080,20 @@
         <v>3</v>
       </c>
       <c r="E48" s="53" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="F48" s="13"/>
       <c r="G48" s="13"/>
       <c r="H48" s="13"/>
-      <c r="I48" s="88" t="s">
-        <v>534</v>
-      </c>
-      <c r="J48" s="89" t="s">
+      <c r="I48" s="87" t="s">
+        <v>535</v>
+      </c>
+      <c r="J48" s="88" t="s">
         <v>164</v>
       </c>
       <c r="K48" s="50"/>
       <c r="L48" s="56" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="M48" s="53" t="s">
         <v>108</v>
@@ -16127,20 +16126,20 @@
         <v>3</v>
       </c>
       <c r="E49" s="53" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="F49" s="13"/>
       <c r="G49" s="13"/>
       <c r="H49" s="13"/>
-      <c r="I49" s="88" t="s">
-        <v>537</v>
-      </c>
-      <c r="J49" s="89" t="s">
+      <c r="I49" s="87" t="s">
+        <v>538</v>
+      </c>
+      <c r="J49" s="88" t="s">
         <v>50</v>
       </c>
       <c r="K49" s="50"/>
       <c r="L49" s="56" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="M49" s="53" t="s">
         <v>108</v>
@@ -16173,16 +16172,16 @@
         <v>3</v>
       </c>
       <c r="E50" s="53" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="F50" s="13"/>
       <c r="G50" s="13"/>
       <c r="H50" s="13"/>
-      <c r="I50" s="88" t="s">
+      <c r="I50" s="87" t="s">
         <v>192</v>
       </c>
-      <c r="J50" s="89" t="s">
-        <v>486</v>
+      <c r="J50" s="88" t="s">
+        <v>487</v>
       </c>
       <c r="K50" s="50"/>
       <c r="L50" s="56" t="s">
@@ -16219,22 +16218,22 @@
         <v>3</v>
       </c>
       <c r="E51" s="53" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="F51" s="13"/>
       <c r="G51" s="13"/>
       <c r="H51" s="13"/>
-      <c r="I51" s="88" t="s">
-        <v>449</v>
-      </c>
-      <c r="J51" s="89" t="s">
+      <c r="I51" s="87" t="s">
+        <v>450</v>
+      </c>
+      <c r="J51" s="88" t="s">
         <v>164</v>
       </c>
       <c r="K51" s="50"/>
       <c r="L51" s="56" t="s">
-        <v>455</v>
-      </c>
-      <c r="M51" s="87" t="s">
+        <v>456</v>
+      </c>
+      <c r="M51" s="86" t="s">
         <v>53</v>
       </c>
       <c r="N51" s="73"/>
@@ -16263,20 +16262,20 @@
         <v>3</v>
       </c>
       <c r="E52" s="53" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="F52" s="13"/>
       <c r="G52" s="13"/>
       <c r="H52" s="13"/>
-      <c r="I52" s="88" t="s">
+      <c r="I52" s="87" t="s">
         <v>232</v>
       </c>
-      <c r="J52" s="89" t="s">
-        <v>486</v>
+      <c r="J52" s="88" t="s">
+        <v>487</v>
       </c>
       <c r="K52" s="50"/>
       <c r="L52" s="56" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="M52" s="53" t="s">
         <v>108</v>
@@ -16299,36 +16298,36 @@
       <c r="AC52" s="63"/>
     </row>
     <row r="53" customFormat="false" ht="20.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B53" s="90" t="n">
+      <c r="B53" s="89" t="n">
         <v>1</v>
       </c>
-      <c r="C53" s="91" t="s">
-        <v>45</v>
-      </c>
-      <c r="D53" s="92" t="s">
+      <c r="C53" s="90" t="s">
+        <v>45</v>
+      </c>
+      <c r="D53" s="91" t="s">
         <v>62</v>
       </c>
-      <c r="E53" s="93" t="s">
-        <v>540</v>
-      </c>
-      <c r="F53" s="90"/>
-      <c r="G53" s="90"/>
-      <c r="H53" s="90"/>
-      <c r="I53" s="94" t="s">
+      <c r="E53" s="92" t="s">
         <v>541</v>
       </c>
-      <c r="J53" s="95" t="s">
+      <c r="F53" s="89"/>
+      <c r="G53" s="89"/>
+      <c r="H53" s="89"/>
+      <c r="I53" s="93" t="s">
+        <v>542</v>
+      </c>
+      <c r="J53" s="94" t="s">
         <v>164</v>
       </c>
-      <c r="K53" s="90"/>
-      <c r="L53" s="96" t="s">
-        <v>542</v>
-      </c>
-      <c r="M53" s="98"/>
-      <c r="N53" s="97"/>
-      <c r="O53" s="96"/>
-      <c r="P53" s="98"/>
-      <c r="Q53" s="96"/>
+      <c r="K53" s="89"/>
+      <c r="L53" s="95" t="s">
+        <v>543</v>
+      </c>
+      <c r="M53" s="97"/>
+      <c r="N53" s="96"/>
+      <c r="O53" s="95"/>
+      <c r="P53" s="97"/>
+      <c r="Q53" s="95"/>
       <c r="R53" s="58"/>
       <c r="U53" s="12"/>
       <c r="V53" s="59"/>
@@ -16351,20 +16350,20 @@
         <v>3</v>
       </c>
       <c r="E54" s="53" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="F54" s="13"/>
       <c r="G54" s="13"/>
       <c r="H54" s="13"/>
-      <c r="I54" s="88" t="s">
-        <v>544</v>
-      </c>
-      <c r="J54" s="89" t="s">
+      <c r="I54" s="87" t="s">
+        <v>545</v>
+      </c>
+      <c r="J54" s="88" t="s">
         <v>50</v>
       </c>
       <c r="K54" s="50"/>
       <c r="L54" s="56" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="M54" s="53" t="s">
         <v>108</v>
@@ -16387,36 +16386,36 @@
       <c r="AC54" s="63"/>
     </row>
     <row r="55" customFormat="false" ht="20.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B55" s="90" t="n">
+      <c r="B55" s="89" t="n">
         <v>1</v>
       </c>
-      <c r="C55" s="91" t="s">
-        <v>45</v>
-      </c>
-      <c r="D55" s="92" t="s">
+      <c r="C55" s="90" t="s">
+        <v>45</v>
+      </c>
+      <c r="D55" s="91" t="s">
         <v>62</v>
       </c>
-      <c r="E55" s="93" t="s">
-        <v>546</v>
-      </c>
-      <c r="F55" s="99"/>
-      <c r="G55" s="99"/>
-      <c r="H55" s="99"/>
-      <c r="I55" s="94" t="s">
+      <c r="E55" s="92" t="s">
         <v>547</v>
       </c>
-      <c r="J55" s="95" t="s">
+      <c r="F55" s="98"/>
+      <c r="G55" s="98"/>
+      <c r="H55" s="98"/>
+      <c r="I55" s="93" t="s">
+        <v>548</v>
+      </c>
+      <c r="J55" s="94" t="s">
         <v>164</v>
       </c>
-      <c r="K55" s="99"/>
-      <c r="L55" s="99" t="s">
-        <v>548</v>
-      </c>
-      <c r="M55" s="99"/>
-      <c r="N55" s="100"/>
-      <c r="O55" s="99"/>
-      <c r="P55" s="99"/>
-      <c r="Q55" s="99"/>
+      <c r="K55" s="98"/>
+      <c r="L55" s="98" t="s">
+        <v>549</v>
+      </c>
+      <c r="M55" s="98"/>
+      <c r="N55" s="99"/>
+      <c r="O55" s="98"/>
+      <c r="P55" s="98"/>
+      <c r="Q55" s="98"/>
     </row>
     <row r="56" customFormat="false" ht="32.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B56" s="50" t="n">
@@ -16429,16 +16428,16 @@
         <v>3</v>
       </c>
       <c r="E56" s="53" t="s">
-        <v>525</v>
-      </c>
-      <c r="I56" s="88" t="s">
         <v>526</v>
       </c>
-      <c r="J56" s="89" t="s">
-        <v>486</v>
+      <c r="I56" s="87" t="s">
+        <v>527</v>
+      </c>
+      <c r="J56" s="88" t="s">
+        <v>487</v>
       </c>
       <c r="L56" s="56" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="M56" s="53" t="s">
         <v>108</v>
@@ -16458,22 +16457,22 @@
         <v>3</v>
       </c>
       <c r="E57" s="53" t="s">
-        <v>549</v>
-      </c>
-      <c r="I57" s="88" t="s">
-        <v>435</v>
-      </c>
-      <c r="J57" s="89" t="s">
+        <v>550</v>
+      </c>
+      <c r="I57" s="87" t="s">
+        <v>436</v>
+      </c>
+      <c r="J57" s="88" t="s">
         <v>164</v>
       </c>
       <c r="L57" s="0" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="M57" s="53" t="s">
         <v>329</v>
       </c>
-      <c r="N57" s="87" t="s">
-        <v>474</v>
+      <c r="N57" s="86" t="s">
+        <v>475</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="32.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16487,16 +16486,16 @@
         <v>3</v>
       </c>
       <c r="E58" s="53" t="s">
-        <v>530</v>
-      </c>
-      <c r="I58" s="88" t="s">
         <v>531</v>
       </c>
-      <c r="J58" s="89" t="s">
-        <v>486</v>
+      <c r="I58" s="87" t="s">
+        <v>532</v>
+      </c>
+      <c r="J58" s="88" t="s">
+        <v>487</v>
       </c>
       <c r="L58" s="56" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="M58" s="53" t="s">
         <v>108</v>
@@ -16516,21 +16515,21 @@
         <v>3</v>
       </c>
       <c r="E59" s="53" t="s">
-        <v>355</v>
-      </c>
-      <c r="I59" s="88" t="s">
-        <v>351</v>
-      </c>
-      <c r="J59" s="89" t="s">
+        <v>356</v>
+      </c>
+      <c r="I59" s="87" t="s">
+        <v>352</v>
+      </c>
+      <c r="J59" s="88" t="s">
         <v>50</v>
       </c>
       <c r="L59" s="0" t="s">
-        <v>356</v>
-      </c>
-      <c r="M59" s="87" t="s">
+        <v>357</v>
+      </c>
+      <c r="M59" s="86" t="s">
         <v>53</v>
       </c>
-      <c r="N59" s="87"/>
+      <c r="N59" s="86"/>
     </row>
     <row r="60" customFormat="false" ht="20.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B60" s="50" t="n">
@@ -16543,22 +16542,22 @@
         <v>3</v>
       </c>
       <c r="E60" s="53" t="s">
-        <v>551</v>
-      </c>
-      <c r="I60" s="88" t="s">
-        <v>458</v>
-      </c>
-      <c r="J60" s="89" t="s">
+        <v>552</v>
+      </c>
+      <c r="I60" s="87" t="s">
+        <v>459</v>
+      </c>
+      <c r="J60" s="88" t="s">
         <v>164</v>
       </c>
       <c r="L60" s="0" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="M60" s="53" t="s">
         <v>329</v>
       </c>
-      <c r="N60" s="87" t="s">
-        <v>474</v>
+      <c r="N60" s="86" t="s">
+        <v>475</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="32.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16572,16 +16571,16 @@
         <v>3</v>
       </c>
       <c r="E61" s="53" t="s">
-        <v>533</v>
-      </c>
-      <c r="I61" s="88" t="s">
         <v>534</v>
       </c>
-      <c r="J61" s="89" t="s">
-        <v>486</v>
+      <c r="I61" s="87" t="s">
+        <v>535</v>
+      </c>
+      <c r="J61" s="88" t="s">
+        <v>487</v>
       </c>
       <c r="L61" s="56" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="M61" s="53" t="s">
         <v>108</v>
@@ -16601,21 +16600,21 @@
         <v>3</v>
       </c>
       <c r="E62" s="53" t="s">
-        <v>539</v>
-      </c>
-      <c r="I62" s="88" t="s">
-        <v>449</v>
-      </c>
-      <c r="J62" s="89" t="s">
-        <v>486</v>
+        <v>540</v>
+      </c>
+      <c r="I62" s="87" t="s">
+        <v>450</v>
+      </c>
+      <c r="J62" s="88" t="s">
+        <v>487</v>
       </c>
       <c r="L62" s="56" t="s">
-        <v>455</v>
-      </c>
-      <c r="M62" s="87" t="s">
+        <v>456</v>
+      </c>
+      <c r="M62" s="86" t="s">
         <v>53</v>
       </c>
-      <c r="N62" s="87"/>
+      <c r="N62" s="86"/>
     </row>
     <row r="63" customFormat="false" ht="32.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B63" s="50" t="n">
@@ -16628,16 +16627,16 @@
         <v>3</v>
       </c>
       <c r="E63" s="53" t="s">
-        <v>553</v>
-      </c>
-      <c r="I63" s="88" t="s">
-        <v>375</v>
-      </c>
-      <c r="J63" s="89" t="s">
+        <v>554</v>
+      </c>
+      <c r="I63" s="87" t="s">
+        <v>376</v>
+      </c>
+      <c r="J63" s="88" t="s">
         <v>50</v>
       </c>
       <c r="L63" s="0" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="M63" s="53" t="s">
         <v>108</v>
@@ -16647,36 +16646,36 @@
       </c>
     </row>
     <row r="64" customFormat="false" ht="20.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B64" s="90" t="n">
+      <c r="B64" s="89" t="n">
         <v>1</v>
       </c>
-      <c r="C64" s="91" t="s">
-        <v>45</v>
-      </c>
-      <c r="D64" s="92" t="s">
+      <c r="C64" s="90" t="s">
+        <v>45</v>
+      </c>
+      <c r="D64" s="91" t="s">
         <v>62</v>
       </c>
-      <c r="E64" s="93" t="s">
-        <v>540</v>
-      </c>
-      <c r="F64" s="99"/>
-      <c r="G64" s="99"/>
-      <c r="H64" s="99"/>
-      <c r="I64" s="94" t="s">
+      <c r="E64" s="92" t="s">
         <v>541</v>
       </c>
-      <c r="J64" s="95" t="s">
-        <v>486</v>
-      </c>
-      <c r="K64" s="99"/>
-      <c r="L64" s="96" t="s">
+      <c r="F64" s="98"/>
+      <c r="G64" s="98"/>
+      <c r="H64" s="98"/>
+      <c r="I64" s="93" t="s">
         <v>542</v>
       </c>
-      <c r="M64" s="99"/>
-      <c r="N64" s="100"/>
-      <c r="O64" s="99"/>
-      <c r="P64" s="99"/>
-      <c r="Q64" s="99"/>
+      <c r="J64" s="94" t="s">
+        <v>487</v>
+      </c>
+      <c r="K64" s="98"/>
+      <c r="L64" s="95" t="s">
+        <v>543</v>
+      </c>
+      <c r="M64" s="98"/>
+      <c r="N64" s="99"/>
+      <c r="O64" s="98"/>
+      <c r="P64" s="98"/>
+      <c r="Q64" s="98"/>
     </row>
     <row r="65" customFormat="false" ht="20.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B65" s="50" t="n">
@@ -16689,22 +16688,22 @@
         <v>3</v>
       </c>
       <c r="E65" s="53" t="s">
-        <v>555</v>
-      </c>
-      <c r="I65" s="88" t="s">
-        <v>421</v>
-      </c>
-      <c r="J65" s="89" t="s">
+        <v>556</v>
+      </c>
+      <c r="I65" s="87" t="s">
+        <v>422</v>
+      </c>
+      <c r="J65" s="88" t="s">
         <v>164</v>
       </c>
       <c r="L65" s="0" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="M65" s="53" t="s">
         <v>329</v>
       </c>
-      <c r="N65" s="87" t="s">
-        <v>474</v>
+      <c r="N65" s="86" t="s">
+        <v>475</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="20.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16718,52 +16717,52 @@
         <v>3</v>
       </c>
       <c r="E66" s="53" t="s">
-        <v>557</v>
-      </c>
-      <c r="I66" s="88" t="s">
-        <v>445</v>
-      </c>
-      <c r="J66" s="89" t="s">
+        <v>558</v>
+      </c>
+      <c r="I66" s="87" t="s">
+        <v>446</v>
+      </c>
+      <c r="J66" s="88" t="s">
         <v>164</v>
       </c>
       <c r="L66" s="0" t="s">
-        <v>558</v>
-      </c>
-      <c r="M66" s="87" t="s">
+        <v>559</v>
+      </c>
+      <c r="M66" s="86" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="20.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B67" s="90" t="n">
+      <c r="B67" s="89" t="n">
         <v>1</v>
       </c>
-      <c r="C67" s="91" t="s">
-        <v>45</v>
-      </c>
-      <c r="D67" s="92" t="s">
+      <c r="C67" s="90" t="s">
+        <v>45</v>
+      </c>
+      <c r="D67" s="91" t="s">
         <v>62</v>
       </c>
-      <c r="E67" s="93" t="s">
-        <v>546</v>
-      </c>
-      <c r="F67" s="99"/>
-      <c r="G67" s="99"/>
-      <c r="H67" s="99"/>
-      <c r="I67" s="94" t="s">
+      <c r="E67" s="92" t="s">
         <v>547</v>
       </c>
-      <c r="J67" s="95" t="s">
-        <v>486</v>
-      </c>
-      <c r="K67" s="99"/>
-      <c r="L67" s="99" t="s">
+      <c r="F67" s="98"/>
+      <c r="G67" s="98"/>
+      <c r="H67" s="98"/>
+      <c r="I67" s="93" t="s">
         <v>548</v>
       </c>
-      <c r="M67" s="99"/>
-      <c r="N67" s="100"/>
-      <c r="O67" s="99"/>
-      <c r="P67" s="99"/>
-      <c r="Q67" s="99"/>
+      <c r="J67" s="94" t="s">
+        <v>487</v>
+      </c>
+      <c r="K67" s="98"/>
+      <c r="L67" s="98" t="s">
+        <v>549</v>
+      </c>
+      <c r="M67" s="98"/>
+      <c r="N67" s="99"/>
+      <c r="O67" s="98"/>
+      <c r="P67" s="98"/>
+      <c r="Q67" s="98"/>
     </row>
     <row r="68" customFormat="false" ht="32.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B68" s="50" t="n">
@@ -16776,22 +16775,22 @@
         <v>3</v>
       </c>
       <c r="E68" s="53" t="s">
-        <v>559</v>
-      </c>
-      <c r="I68" s="88" t="s">
-        <v>377</v>
-      </c>
-      <c r="J68" s="89" t="s">
+        <v>560</v>
+      </c>
+      <c r="I68" s="87" t="s">
+        <v>378</v>
+      </c>
+      <c r="J68" s="88" t="s">
         <v>50</v>
       </c>
       <c r="L68" s="0" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="M68" s="0" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="N68" s="73" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="20.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16805,21 +16804,21 @@
         <v>3</v>
       </c>
       <c r="E69" s="53" t="s">
-        <v>549</v>
-      </c>
-      <c r="I69" s="88" t="s">
-        <v>435</v>
-      </c>
-      <c r="J69" s="89" t="s">
-        <v>486</v>
+        <v>550</v>
+      </c>
+      <c r="I69" s="87" t="s">
+        <v>436</v>
+      </c>
+      <c r="J69" s="88" t="s">
+        <v>487</v>
       </c>
       <c r="L69" s="0" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="M69" s="53" t="s">
         <v>329</v>
       </c>
-      <c r="N69" s="87"/>
+      <c r="N69" s="86"/>
     </row>
     <row r="70" customFormat="false" ht="20.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B70" s="50" t="n">
@@ -16832,21 +16831,21 @@
         <v>3</v>
       </c>
       <c r="E70" s="53" t="s">
-        <v>551</v>
-      </c>
-      <c r="I70" s="88" t="s">
-        <v>458</v>
-      </c>
-      <c r="J70" s="89" t="s">
-        <v>486</v>
+        <v>552</v>
+      </c>
+      <c r="I70" s="87" t="s">
+        <v>459</v>
+      </c>
+      <c r="J70" s="88" t="s">
+        <v>487</v>
       </c>
       <c r="L70" s="0" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="M70" s="53" t="s">
         <v>329</v>
       </c>
-      <c r="N70" s="87"/>
+      <c r="N70" s="86"/>
     </row>
     <row r="71" customFormat="false" ht="32.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B71" s="50" t="n">
@@ -16859,16 +16858,16 @@
         <v>3</v>
       </c>
       <c r="E71" s="53" t="s">
-        <v>563</v>
-      </c>
-      <c r="I71" s="88" t="s">
         <v>564</v>
       </c>
-      <c r="J71" s="89" t="s">
+      <c r="I71" s="87" t="s">
+        <v>565</v>
+      </c>
+      <c r="J71" s="88" t="s">
         <v>50</v>
       </c>
       <c r="L71" s="0" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="M71" s="53" t="s">
         <v>108</v>
@@ -16888,22 +16887,22 @@
         <v>3</v>
       </c>
       <c r="E72" s="53" t="s">
-        <v>555</v>
-      </c>
-      <c r="I72" s="88" t="s">
-        <v>421</v>
-      </c>
-      <c r="J72" s="89" t="s">
-        <v>486</v>
+        <v>556</v>
+      </c>
+      <c r="I72" s="87" t="s">
+        <v>422</v>
+      </c>
+      <c r="J72" s="88" t="s">
+        <v>487</v>
       </c>
       <c r="L72" s="0" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="M72" s="53" t="s">
         <v>329</v>
       </c>
-      <c r="N72" s="87" t="s">
-        <v>474</v>
+      <c r="N72" s="86" t="s">
+        <v>475</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="32.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16917,12 +16916,12 @@
         <v>3</v>
       </c>
       <c r="E73" s="53" t="s">
-        <v>566</v>
-      </c>
-      <c r="I73" s="88" t="s">
+        <v>567</v>
+      </c>
+      <c r="I73" s="87" t="s">
         <v>260</v>
       </c>
-      <c r="J73" s="89" t="s">
+      <c r="J73" s="88" t="s">
         <v>50</v>
       </c>
       <c r="L73" s="0" t="s">
@@ -16946,21 +16945,21 @@
         <v>3</v>
       </c>
       <c r="E74" s="53" t="s">
-        <v>557</v>
-      </c>
-      <c r="I74" s="88" t="s">
-        <v>445</v>
-      </c>
-      <c r="J74" s="89" t="s">
-        <v>486</v>
+        <v>558</v>
+      </c>
+      <c r="I74" s="87" t="s">
+        <v>446</v>
+      </c>
+      <c r="J74" s="88" t="s">
+        <v>487</v>
       </c>
       <c r="L74" s="0" t="s">
-        <v>567</v>
-      </c>
-      <c r="M74" s="87" t="s">
+        <v>568</v>
+      </c>
+      <c r="M74" s="86" t="s">
         <v>53</v>
       </c>
-      <c r="N74" s="87"/>
+      <c r="N74" s="86"/>
     </row>
     <row r="75" customFormat="false" ht="32.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B75" s="50" t="n">
@@ -16973,16 +16972,16 @@
         <v>3</v>
       </c>
       <c r="E75" s="53" t="s">
-        <v>568</v>
-      </c>
-      <c r="I75" s="88" t="s">
-        <v>406</v>
-      </c>
-      <c r="J75" s="89" t="s">
+        <v>569</v>
+      </c>
+      <c r="I75" s="87" t="s">
+        <v>407</v>
+      </c>
+      <c r="J75" s="88" t="s">
         <v>50</v>
       </c>
       <c r="L75" s="0" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="M75" s="53" t="s">
         <v>108</v>
@@ -17002,22 +17001,22 @@
         <v>3</v>
       </c>
       <c r="E76" s="53" t="s">
-        <v>569</v>
-      </c>
-      <c r="I76" s="88" t="s">
-        <v>383</v>
-      </c>
-      <c r="J76" s="89" t="s">
+        <v>570</v>
+      </c>
+      <c r="I76" s="87" t="s">
+        <v>384</v>
+      </c>
+      <c r="J76" s="88" t="s">
         <v>50</v>
       </c>
       <c r="L76" s="0" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="M76" s="53" t="s">
         <v>329</v>
       </c>
-      <c r="N76" s="87" t="s">
-        <v>474</v>
+      <c r="N76" s="86" t="s">
+        <v>475</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="20.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17031,22 +17030,22 @@
         <v>3</v>
       </c>
       <c r="E77" s="53" t="s">
-        <v>571</v>
-      </c>
-      <c r="I77" s="88" t="s">
-        <v>410</v>
-      </c>
-      <c r="J77" s="89" t="s">
+        <v>572</v>
+      </c>
+      <c r="I77" s="87" t="s">
+        <v>411</v>
+      </c>
+      <c r="J77" s="88" t="s">
         <v>50</v>
       </c>
       <c r="L77" s="0" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="M77" s="53" t="s">
         <v>329</v>
       </c>
-      <c r="N77" s="87" t="s">
-        <v>474</v>
+      <c r="N77" s="86" t="s">
+        <v>475</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="20.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17060,57 +17059,57 @@
         <v>3</v>
       </c>
       <c r="E78" s="53" t="s">
-        <v>573</v>
-      </c>
-      <c r="I78" s="88" t="s">
-        <v>395</v>
-      </c>
-      <c r="J78" s="89" t="s">
+        <v>574</v>
+      </c>
+      <c r="I78" s="87" t="s">
+        <v>396</v>
+      </c>
+      <c r="J78" s="88" t="s">
         <v>50</v>
       </c>
       <c r="L78" s="0" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="M78" s="53" t="s">
         <v>329</v>
       </c>
-      <c r="N78" s="87" t="s">
-        <v>474</v>
+      <c r="N78" s="86" t="s">
+        <v>475</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="20.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B79" s="101" t="n">
+      <c r="B79" s="100" t="n">
         <v>1</v>
       </c>
-      <c r="C79" s="102" t="s">
-        <v>45</v>
-      </c>
-      <c r="D79" s="103" t="s">
+      <c r="C79" s="101" t="s">
+        <v>45</v>
+      </c>
+      <c r="D79" s="102" t="s">
         <v>62</v>
       </c>
-      <c r="E79" s="104" t="s">
-        <v>575</v>
-      </c>
-      <c r="F79" s="105"/>
-      <c r="G79" s="105"/>
-      <c r="H79" s="105"/>
-      <c r="I79" s="106" t="s">
+      <c r="E79" s="103" t="s">
         <v>576</v>
       </c>
-      <c r="J79" s="107" t="s">
+      <c r="F79" s="104"/>
+      <c r="G79" s="104"/>
+      <c r="H79" s="104"/>
+      <c r="I79" s="105" t="s">
+        <v>577</v>
+      </c>
+      <c r="J79" s="106" t="s">
         <v>50</v>
       </c>
-      <c r="K79" s="105"/>
-      <c r="L79" s="105" t="s">
-        <v>577</v>
-      </c>
-      <c r="M79" s="108" t="s">
+      <c r="K79" s="104"/>
+      <c r="L79" s="104" t="s">
+        <v>578</v>
+      </c>
+      <c r="M79" s="107" t="s">
         <v>108</v>
       </c>
-      <c r="N79" s="109"/>
-      <c r="O79" s="105"/>
-      <c r="P79" s="105"/>
-      <c r="Q79" s="105"/>
+      <c r="N79" s="108"/>
+      <c r="O79" s="104"/>
+      <c r="P79" s="104"/>
+      <c r="Q79" s="104"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -17229,39 +17228,39 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B19"/>
-  <sheetFormatPr defaultColWidth="12.01953125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.0390625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11.52"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="115.2"/>
   </cols>
   <sheetData>
-    <row r="1" s="110" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" s="109" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="28" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="28" t="s">
-        <v>579</v>
-      </c>
-      <c r="B2" s="110"/>
+        <v>580</v>
+      </c>
+      <c r="B2" s="109"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="28" t="n">
         <v>14</v>
       </c>
-      <c r="B3" s="110"/>
+      <c r="B3" s="109"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="28"/>
-      <c r="B4" s="110"/>
+      <c r="B4" s="109"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="28" t="s">
-        <v>579</v>
-      </c>
-      <c r="B5" s="110" t="s">
         <v>580</v>
+      </c>
+      <c r="B5" s="109" t="s">
+        <v>581</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17269,7 +17268,7 @@
         <v>1</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17277,7 +17276,7 @@
         <v>2</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17285,7 +17284,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17293,7 +17292,7 @@
         <v>4</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17301,7 +17300,7 @@
         <v>5</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17309,7 +17308,7 @@
         <v>6</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17317,7 +17316,7 @@
         <v>7</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17325,7 +17324,7 @@
         <v>8</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17333,7 +17332,7 @@
         <v>9</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17341,7 +17340,7 @@
         <v>10</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17349,7 +17348,7 @@
         <v>11</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17357,15 +17356,15 @@
         <v>12</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="24.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="B18" s="87" t="s">
-        <v>593</v>
+      <c r="B18" s="86" t="s">
+        <v>594</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17373,7 +17372,7 @@
         <v>14</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
   </sheetData>
@@ -17393,7 +17392,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B1:AE54"/>
-  <sheetFormatPr defaultColWidth="9.01953125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.03125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="1" min="1" style="0" width="11.52"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="10.01"/>
@@ -19750,7 +19749,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B1:AE54"/>
-  <sheetFormatPr defaultColWidth="9.01953125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.03125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="1" min="1" style="0" width="11.52"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="10.01"/>
@@ -21921,7 +21920,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B1:AE54"/>
-  <sheetFormatPr defaultColWidth="9.01953125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.03125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="1" min="1" style="0" width="11.52"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="10.01"/>
@@ -23042,7 +23041,7 @@
       <c r="D27" s="52" t="s">
         <v>3</v>
       </c>
-      <c r="E27" s="77" t="s">
+      <c r="E27" s="76" t="s">
         <v>204</v>
       </c>
       <c r="F27" s="13"/>
@@ -24098,7 +24097,7 @@
       <c r="D51" s="52" t="s">
         <v>3</v>
       </c>
-      <c r="E51" s="77" t="s">
+      <c r="E51" s="76" t="s">
         <v>238</v>
       </c>
       <c r="F51" s="13"/>
@@ -24389,7 +24388,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B1:AE30"/>
-  <sheetFormatPr defaultColWidth="9.01953125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.03125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="1" min="1" style="0" width="11.52"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="10.01"/>
@@ -24742,7 +24741,7 @@
       <c r="F7" s="13"/>
       <c r="G7" s="13"/>
       <c r="H7" s="13"/>
-      <c r="I7" s="78" t="s">
+      <c r="I7" s="77" t="s">
         <v>243</v>
       </c>
       <c r="J7" s="55"/>
@@ -24788,7 +24787,7 @@
       <c r="F8" s="13"/>
       <c r="G8" s="13"/>
       <c r="H8" s="13"/>
-      <c r="I8" s="78" t="s">
+      <c r="I8" s="77" t="s">
         <v>243</v>
       </c>
       <c r="J8" s="55"/>
@@ -24834,7 +24833,7 @@
       <c r="F9" s="13"/>
       <c r="G9" s="13"/>
       <c r="H9" s="13"/>
-      <c r="I9" s="78" t="s">
+      <c r="I9" s="77" t="s">
         <v>243</v>
       </c>
       <c r="J9" s="55"/>
@@ -24880,7 +24879,7 @@
       <c r="F10" s="13"/>
       <c r="G10" s="13"/>
       <c r="H10" s="13"/>
-      <c r="I10" s="78" t="s">
+      <c r="I10" s="77" t="s">
         <v>243</v>
       </c>
       <c r="J10" s="55"/>
@@ -24928,7 +24927,7 @@
       <c r="H11" s="13" t="s">
         <v>255</v>
       </c>
-      <c r="I11" s="78" t="s">
+      <c r="I11" s="77" t="s">
         <v>243</v>
       </c>
       <c r="J11" s="55"/>
@@ -24972,7 +24971,7 @@
       <c r="F12" s="13"/>
       <c r="G12" s="13"/>
       <c r="H12" s="13"/>
-      <c r="I12" s="78"/>
+      <c r="I12" s="77"/>
       <c r="J12" s="55"/>
       <c r="K12" s="50"/>
       <c r="L12" s="56"/>
@@ -25006,7 +25005,7 @@
       <c r="F13" s="13"/>
       <c r="G13" s="13"/>
       <c r="H13" s="13"/>
-      <c r="I13" s="78"/>
+      <c r="I13" s="77"/>
       <c r="J13" s="55"/>
       <c r="K13" s="50"/>
       <c r="L13" s="56"/>
@@ -25040,7 +25039,7 @@
       <c r="F14" s="13"/>
       <c r="G14" s="13"/>
       <c r="H14" s="13"/>
-      <c r="I14" s="78"/>
+      <c r="I14" s="77"/>
       <c r="J14" s="55"/>
       <c r="K14" s="50"/>
       <c r="L14" s="56"/>
@@ -25074,7 +25073,7 @@
       <c r="F15" s="13"/>
       <c r="G15" s="13"/>
       <c r="H15" s="13"/>
-      <c r="I15" s="78"/>
+      <c r="I15" s="77"/>
       <c r="J15" s="55"/>
       <c r="K15" s="50"/>
       <c r="L15" s="56"/>
@@ -25108,7 +25107,7 @@
       <c r="F16" s="13"/>
       <c r="G16" s="13"/>
       <c r="H16" s="13"/>
-      <c r="I16" s="78"/>
+      <c r="I16" s="77"/>
       <c r="J16" s="55"/>
       <c r="K16" s="50"/>
       <c r="L16" s="56"/>
@@ -25142,7 +25141,7 @@
       <c r="F17" s="13"/>
       <c r="G17" s="13"/>
       <c r="H17" s="13"/>
-      <c r="I17" s="78"/>
+      <c r="I17" s="77"/>
       <c r="J17" s="55"/>
       <c r="K17" s="50"/>
       <c r="L17" s="56"/>
@@ -25176,7 +25175,7 @@
       <c r="F18" s="13"/>
       <c r="G18" s="13"/>
       <c r="H18" s="13"/>
-      <c r="I18" s="78"/>
+      <c r="I18" s="77"/>
       <c r="J18" s="55"/>
       <c r="K18" s="50"/>
       <c r="L18" s="56"/>
@@ -25212,7 +25211,7 @@
       <c r="F19" s="13"/>
       <c r="G19" s="13"/>
       <c r="H19" s="13"/>
-      <c r="I19" s="78" t="s">
+      <c r="I19" s="77" t="s">
         <v>260</v>
       </c>
       <c r="J19" s="55"/>
@@ -25256,7 +25255,7 @@
       <c r="F20" s="13"/>
       <c r="G20" s="13"/>
       <c r="H20" s="13"/>
-      <c r="I20" s="78" t="s">
+      <c r="I20" s="77" t="s">
         <v>260</v>
       </c>
       <c r="J20" s="55"/>
@@ -25300,7 +25299,7 @@
       <c r="F21" s="13"/>
       <c r="G21" s="13"/>
       <c r="H21" s="13"/>
-      <c r="I21" s="78" t="s">
+      <c r="I21" s="77" t="s">
         <v>260</v>
       </c>
       <c r="J21" s="55"/>
@@ -25344,7 +25343,7 @@
       <c r="F22" s="13"/>
       <c r="G22" s="13"/>
       <c r="H22" s="13"/>
-      <c r="I22" s="78" t="s">
+      <c r="I22" s="77" t="s">
         <v>260</v>
       </c>
       <c r="J22" s="55"/>
@@ -25774,7 +25773,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B1:AE54"/>
-  <sheetFormatPr defaultColWidth="9.01953125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.03125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="1" min="1" style="0" width="11.52"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="10.01"/>
@@ -26116,10 +26115,10 @@
       <c r="B7" s="69" t="n">
         <v>1</v>
       </c>
-      <c r="C7" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D7" s="80" t="s">
+      <c r="C7" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D7" s="79" t="s">
         <v>62</v>
       </c>
       <c r="E7" s="71" t="s">
@@ -26140,7 +26139,7 @@
       <c r="N7" s="72"/>
       <c r="O7" s="70"/>
       <c r="P7" s="65"/>
-      <c r="Q7" s="81"/>
+      <c r="Q7" s="80"/>
       <c r="R7" s="58"/>
       <c r="U7" s="12"/>
       <c r="V7" s="59"/>
@@ -26156,10 +26155,10 @@
       <c r="B8" s="69" t="n">
         <v>2</v>
       </c>
-      <c r="C8" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D8" s="80" t="s">
+      <c r="C8" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D8" s="79" t="s">
         <v>62</v>
       </c>
       <c r="E8" s="71" t="s">
@@ -26180,7 +26179,7 @@
       <c r="N8" s="72"/>
       <c r="O8" s="70"/>
       <c r="P8" s="65"/>
-      <c r="Q8" s="81"/>
+      <c r="Q8" s="80"/>
       <c r="R8" s="58"/>
       <c r="U8" s="12"/>
       <c r="V8" s="59"/>
@@ -26196,10 +26195,10 @@
       <c r="B9" s="69" t="n">
         <v>3</v>
       </c>
-      <c r="C9" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D9" s="80" t="s">
+      <c r="C9" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D9" s="79" t="s">
         <v>62</v>
       </c>
       <c r="E9" s="65" t="s">
@@ -26218,7 +26217,7 @@
       <c r="N9" s="72"/>
       <c r="O9" s="70"/>
       <c r="P9" s="65"/>
-      <c r="Q9" s="81"/>
+      <c r="Q9" s="80"/>
       <c r="R9" s="58"/>
       <c r="U9" s="12"/>
       <c r="V9" s="59"/>
@@ -26234,10 +26233,10 @@
       <c r="B10" s="69" t="n">
         <v>4</v>
       </c>
-      <c r="C10" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D10" s="80" t="s">
+      <c r="C10" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D10" s="79" t="s">
         <v>62</v>
       </c>
       <c r="E10" s="65" t="s">
@@ -26258,7 +26257,7 @@
       <c r="N10" s="72"/>
       <c r="O10" s="70"/>
       <c r="P10" s="65"/>
-      <c r="Q10" s="81"/>
+      <c r="Q10" s="80"/>
       <c r="R10" s="58"/>
       <c r="U10" s="12"/>
       <c r="V10" s="59"/>
@@ -26274,31 +26273,31 @@
       <c r="B11" s="69" t="n">
         <v>5</v>
       </c>
-      <c r="C11" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D11" s="80" t="s">
+      <c r="C11" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D11" s="79" t="s">
         <v>62</v>
       </c>
-      <c r="E11" s="82" t="s">
+      <c r="E11" s="81" t="s">
         <v>280</v>
       </c>
-      <c r="F11" s="82"/>
-      <c r="G11" s="82"/>
-      <c r="H11" s="82"/>
-      <c r="I11" s="82"/>
-      <c r="J11" s="82"/>
-      <c r="K11" s="82"/>
-      <c r="L11" s="82" t="s">
+      <c r="F11" s="81"/>
+      <c r="G11" s="81"/>
+      <c r="H11" s="81"/>
+      <c r="I11" s="81"/>
+      <c r="J11" s="81"/>
+      <c r="K11" s="81"/>
+      <c r="L11" s="81" t="s">
         <v>281</v>
       </c>
       <c r="M11" s="71" t="s">
         <v>108</v>
       </c>
-      <c r="N11" s="82"/>
+      <c r="N11" s="81"/>
       <c r="O11" s="70"/>
       <c r="P11" s="65"/>
-      <c r="Q11" s="81"/>
+      <c r="Q11" s="80"/>
       <c r="R11" s="58"/>
       <c r="U11" s="12"/>
       <c r="V11" s="59"/>
@@ -26314,10 +26313,10 @@
       <c r="B12" s="69" t="n">
         <v>6</v>
       </c>
-      <c r="C12" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D12" s="80" t="s">
+      <c r="C12" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D12" s="79" t="s">
         <v>62</v>
       </c>
       <c r="E12" s="65" t="s">
@@ -26340,7 +26339,7 @@
       </c>
       <c r="O12" s="70"/>
       <c r="P12" s="65"/>
-      <c r="Q12" s="81"/>
+      <c r="Q12" s="80"/>
       <c r="R12" s="58"/>
       <c r="U12" s="12"/>
       <c r="V12" s="59"/>
@@ -26356,10 +26355,10 @@
       <c r="B13" s="69" t="n">
         <v>7</v>
       </c>
-      <c r="C13" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D13" s="80" t="s">
+      <c r="C13" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D13" s="79" t="s">
         <v>62</v>
       </c>
       <c r="E13" s="65" t="s">
@@ -26382,7 +26381,7 @@
       </c>
       <c r="O13" s="70"/>
       <c r="P13" s="65"/>
-      <c r="Q13" s="81"/>
+      <c r="Q13" s="80"/>
       <c r="R13" s="58"/>
       <c r="U13" s="12"/>
       <c r="V13" s="59"/>
@@ -26398,10 +26397,10 @@
       <c r="B14" s="69" t="n">
         <v>8</v>
       </c>
-      <c r="C14" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D14" s="80" t="s">
+      <c r="C14" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D14" s="79" t="s">
         <v>62</v>
       </c>
       <c r="E14" s="65" t="s">
@@ -26424,7 +26423,7 @@
       </c>
       <c r="O14" s="70"/>
       <c r="P14" s="65"/>
-      <c r="Q14" s="81"/>
+      <c r="Q14" s="80"/>
       <c r="R14" s="58"/>
       <c r="U14" s="12"/>
       <c r="V14" s="59"/>
@@ -26440,13 +26439,13 @@
       <c r="B15" s="69" t="n">
         <v>9</v>
       </c>
-      <c r="C15" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D15" s="80" t="s">
-        <v>3</v>
-      </c>
-      <c r="E15" s="83" t="s">
+      <c r="C15" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D15" s="79" t="s">
+        <v>3</v>
+      </c>
+      <c r="E15" s="82" t="s">
         <v>291</v>
       </c>
       <c r="F15" s="66"/>
@@ -26470,7 +26469,7 @@
         <v>295</v>
       </c>
       <c r="P15" s="65"/>
-      <c r="Q15" s="81" t="s">
+      <c r="Q15" s="80" t="s">
         <v>296</v>
       </c>
       <c r="R15" s="58"/>
@@ -26488,10 +26487,10 @@
       <c r="B16" s="69" t="n">
         <v>10</v>
       </c>
-      <c r="C16" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D16" s="80" t="s">
+      <c r="C16" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D16" s="79" t="s">
         <v>62</v>
       </c>
       <c r="E16" s="65" t="s">
@@ -26509,12 +26508,12 @@
       <c r="M16" s="71" t="s">
         <v>108</v>
       </c>
-      <c r="N16" s="84" t="s">
+      <c r="N16" s="83" t="s">
         <v>299</v>
       </c>
       <c r="O16" s="70"/>
       <c r="P16" s="65"/>
-      <c r="Q16" s="81"/>
+      <c r="Q16" s="80"/>
       <c r="R16" s="58"/>
       <c r="U16" s="12"/>
       <c r="V16" s="59"/>
@@ -26530,10 +26529,10 @@
       <c r="B17" s="69" t="n">
         <v>2</v>
       </c>
-      <c r="C17" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D17" s="80" t="s">
+      <c r="C17" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D17" s="79" t="s">
         <v>62</v>
       </c>
       <c r="E17" s="65" t="s">
@@ -26558,7 +26557,7 @@
       </c>
       <c r="O17" s="70"/>
       <c r="P17" s="65"/>
-      <c r="Q17" s="81"/>
+      <c r="Q17" s="80"/>
       <c r="R17" s="58"/>
       <c r="U17" s="12"/>
       <c r="V17" s="59"/>
@@ -26574,10 +26573,10 @@
       <c r="B18" s="69" t="n">
         <v>11</v>
       </c>
-      <c r="C18" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D18" s="80" t="s">
+      <c r="C18" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D18" s="79" t="s">
         <v>62</v>
       </c>
       <c r="E18" s="65" t="s">
@@ -26600,7 +26599,7 @@
       </c>
       <c r="O18" s="70"/>
       <c r="P18" s="65"/>
-      <c r="Q18" s="81"/>
+      <c r="Q18" s="80"/>
       <c r="R18" s="58"/>
       <c r="U18" s="12"/>
       <c r="V18" s="59"/>
@@ -26616,10 +26615,10 @@
       <c r="B19" s="69" t="n">
         <v>12</v>
       </c>
-      <c r="C19" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D19" s="80" t="s">
+      <c r="C19" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D19" s="79" t="s">
         <v>62</v>
       </c>
       <c r="E19" s="65"/>
@@ -26634,7 +26633,7 @@
       <c r="N19" s="72"/>
       <c r="O19" s="70"/>
       <c r="P19" s="65"/>
-      <c r="Q19" s="81"/>
+      <c r="Q19" s="80"/>
       <c r="R19" s="58"/>
       <c r="U19" s="12"/>
       <c r="V19" s="59"/>
@@ -27950,7 +27949,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B1:AE30"/>
-  <sheetFormatPr defaultColWidth="9.01953125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.03125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="1" min="1" style="0" width="11.52"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="10.01"/>
@@ -28291,10 +28290,10 @@
       <c r="B7" s="69" t="n">
         <v>1</v>
       </c>
-      <c r="C7" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D7" s="80" t="s">
+      <c r="C7" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D7" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E7" s="71"/>
@@ -28325,10 +28324,10 @@
       <c r="B8" s="69" t="n">
         <v>2</v>
       </c>
-      <c r="C8" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D8" s="80" t="s">
+      <c r="C8" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D8" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E8" s="71" t="s">
@@ -28363,10 +28362,10 @@
       <c r="B9" s="69" t="n">
         <v>3</v>
       </c>
-      <c r="C9" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D9" s="80" t="s">
+      <c r="C9" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D9" s="79" t="s">
         <v>62</v>
       </c>
       <c r="E9" s="65" t="s">
@@ -28401,10 +28400,10 @@
       <c r="B10" s="69" t="n">
         <v>4</v>
       </c>
-      <c r="C10" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D10" s="80" t="s">
+      <c r="C10" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D10" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E10" s="65" t="s">
@@ -28439,26 +28438,26 @@
       <c r="B11" s="69" t="n">
         <v>5</v>
       </c>
-      <c r="C11" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D11" s="80" t="s">
-        <v>3</v>
-      </c>
-      <c r="E11" s="82" t="s">
+      <c r="C11" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D11" s="79" t="s">
+        <v>3</v>
+      </c>
+      <c r="E11" s="81" t="s">
         <v>310</v>
       </c>
-      <c r="F11" s="82"/>
-      <c r="G11" s="82"/>
-      <c r="H11" s="82"/>
-      <c r="I11" s="82"/>
-      <c r="J11" s="82"/>
-      <c r="K11" s="82"/>
-      <c r="L11" s="82" t="s">
+      <c r="F11" s="81"/>
+      <c r="G11" s="81"/>
+      <c r="H11" s="81"/>
+      <c r="I11" s="81"/>
+      <c r="J11" s="81"/>
+      <c r="K11" s="81"/>
+      <c r="L11" s="81" t="s">
         <v>311</v>
       </c>
       <c r="M11" s="71"/>
-      <c r="N11" s="82"/>
+      <c r="N11" s="81"/>
       <c r="O11" s="56"/>
       <c r="P11" s="29"/>
       <c r="Q11" s="57"/>
@@ -28477,10 +28476,10 @@
       <c r="B12" s="69" t="n">
         <v>6</v>
       </c>
-      <c r="C12" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D12" s="80" t="s">
+      <c r="C12" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D12" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E12" s="65" t="s">
@@ -28529,7 +28528,7 @@
       <c r="F13" s="13"/>
       <c r="G13" s="13"/>
       <c r="H13" s="13"/>
-      <c r="I13" s="78"/>
+      <c r="I13" s="77"/>
       <c r="J13" s="55"/>
       <c r="K13" s="50"/>
       <c r="L13" s="56"/>
@@ -28563,7 +28562,7 @@
       <c r="F14" s="13"/>
       <c r="G14" s="13"/>
       <c r="H14" s="13"/>
-      <c r="I14" s="78"/>
+      <c r="I14" s="77"/>
       <c r="J14" s="55"/>
       <c r="K14" s="50"/>
       <c r="L14" s="56"/>
@@ -28597,7 +28596,7 @@
       <c r="F15" s="13"/>
       <c r="G15" s="13"/>
       <c r="H15" s="13"/>
-      <c r="I15" s="78"/>
+      <c r="I15" s="77"/>
       <c r="J15" s="55"/>
       <c r="K15" s="50"/>
       <c r="L15" s="56"/>
@@ -28631,7 +28630,7 @@
       <c r="F16" s="13"/>
       <c r="G16" s="13"/>
       <c r="H16" s="13"/>
-      <c r="I16" s="78"/>
+      <c r="I16" s="77"/>
       <c r="J16" s="55"/>
       <c r="K16" s="50"/>
       <c r="L16" s="56"/>
@@ -28665,7 +28664,7 @@
       <c r="F17" s="13"/>
       <c r="G17" s="13"/>
       <c r="H17" s="13"/>
-      <c r="I17" s="78"/>
+      <c r="I17" s="77"/>
       <c r="J17" s="55"/>
       <c r="K17" s="50"/>
       <c r="L17" s="56"/>
@@ -28699,7 +28698,7 @@
       <c r="F18" s="13"/>
       <c r="G18" s="13"/>
       <c r="H18" s="13"/>
-      <c r="I18" s="78"/>
+      <c r="I18" s="77"/>
       <c r="J18" s="55"/>
       <c r="K18" s="50"/>
       <c r="L18" s="56"/>
@@ -28733,7 +28732,7 @@
       <c r="F19" s="13"/>
       <c r="G19" s="13"/>
       <c r="H19" s="13"/>
-      <c r="I19" s="78"/>
+      <c r="I19" s="77"/>
       <c r="J19" s="55"/>
       <c r="K19" s="50"/>
       <c r="L19" s="53"/>
@@ -28767,7 +28766,7 @@
       <c r="F20" s="13"/>
       <c r="G20" s="13"/>
       <c r="H20" s="13"/>
-      <c r="I20" s="78"/>
+      <c r="I20" s="77"/>
       <c r="J20" s="55"/>
       <c r="K20" s="50"/>
       <c r="L20" s="53"/>
@@ -28801,7 +28800,7 @@
       <c r="F21" s="13"/>
       <c r="G21" s="13"/>
       <c r="H21" s="13"/>
-      <c r="I21" s="78"/>
+      <c r="I21" s="77"/>
       <c r="J21" s="55"/>
       <c r="K21" s="50"/>
       <c r="L21" s="29"/>
@@ -28835,7 +28834,7 @@
       <c r="F22" s="13"/>
       <c r="G22" s="13"/>
       <c r="H22" s="13"/>
-      <c r="I22" s="78"/>
+      <c r="I22" s="77"/>
       <c r="J22" s="55"/>
       <c r="K22" s="50"/>
       <c r="L22" s="29"/>
@@ -29277,7 +29276,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B1:AE30"/>
-  <sheetFormatPr defaultColWidth="9.01953125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.03125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="1" min="1" style="0" width="11.52"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="10.01"/>
@@ -29619,10 +29618,10 @@
       <c r="B7" s="69" t="n">
         <v>11</v>
       </c>
-      <c r="C7" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D7" s="80" t="s">
+      <c r="C7" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D7" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E7" s="65" t="s">
@@ -29657,10 +29656,10 @@
       <c r="B8" s="69" t="n">
         <v>12</v>
       </c>
-      <c r="C8" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D8" s="80" t="s">
+      <c r="C8" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D8" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E8" s="65" t="s">
@@ -29695,10 +29694,10 @@
       <c r="B9" s="69" t="n">
         <v>13</v>
       </c>
-      <c r="C9" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D9" s="80" t="s">
+      <c r="C9" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D9" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E9" s="65" t="s">
@@ -29733,10 +29732,10 @@
       <c r="B10" s="69" t="n">
         <v>14</v>
       </c>
-      <c r="C10" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D10" s="80" t="s">
+      <c r="C10" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D10" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E10" s="65" t="s">
@@ -29771,10 +29770,10 @@
       <c r="B11" s="69" t="n">
         <v>15</v>
       </c>
-      <c r="C11" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D11" s="80" t="s">
+      <c r="C11" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D11" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E11" s="65" t="s">
@@ -29809,10 +29808,10 @@
       <c r="B12" s="69" t="n">
         <v>16</v>
       </c>
-      <c r="C12" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D12" s="80" t="s">
+      <c r="C12" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D12" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E12" s="29"/>
@@ -29843,10 +29842,10 @@
       <c r="B13" s="69" t="n">
         <v>17</v>
       </c>
-      <c r="C13" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D13" s="80" t="s">
+      <c r="C13" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D13" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E13" s="29"/>
@@ -29877,10 +29876,10 @@
       <c r="B14" s="69" t="n">
         <v>18</v>
       </c>
-      <c r="C14" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D14" s="80" t="s">
+      <c r="C14" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D14" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E14" s="29"/>
@@ -29911,10 +29910,10 @@
       <c r="B15" s="69" t="n">
         <v>19</v>
       </c>
-      <c r="C15" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D15" s="80" t="s">
+      <c r="C15" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D15" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E15" s="29"/>
@@ -29945,10 +29944,10 @@
       <c r="B16" s="69" t="n">
         <v>20</v>
       </c>
-      <c r="C16" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D16" s="80" t="s">
+      <c r="C16" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D16" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E16" s="29"/>
@@ -29979,10 +29978,10 @@
       <c r="B17" s="69" t="n">
         <v>21</v>
       </c>
-      <c r="C17" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D17" s="80" t="s">
+      <c r="C17" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D17" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E17" s="29"/>
@@ -30013,10 +30012,10 @@
       <c r="B18" s="69" t="n">
         <v>22</v>
       </c>
-      <c r="C18" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D18" s="80" t="s">
+      <c r="C18" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D18" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E18" s="29"/>
@@ -30047,10 +30046,10 @@
       <c r="B19" s="69" t="n">
         <v>11</v>
       </c>
-      <c r="C19" s="79" t="s">
+      <c r="C19" s="78" t="s">
         <v>86</v>
       </c>
-      <c r="D19" s="80" t="s">
+      <c r="D19" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E19" s="29"/>
@@ -30081,10 +30080,10 @@
       <c r="B20" s="69" t="n">
         <v>12</v>
       </c>
-      <c r="C20" s="79" t="s">
+      <c r="C20" s="78" t="s">
         <v>86</v>
       </c>
-      <c r="D20" s="80" t="s">
+      <c r="D20" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E20" s="29"/>
@@ -30115,10 +30114,10 @@
       <c r="B21" s="69" t="n">
         <v>13</v>
       </c>
-      <c r="C21" s="79" t="s">
+      <c r="C21" s="78" t="s">
         <v>86</v>
       </c>
-      <c r="D21" s="80" t="s">
+      <c r="D21" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E21" s="29"/>
@@ -30149,10 +30148,10 @@
       <c r="B22" s="69" t="n">
         <v>14</v>
       </c>
-      <c r="C22" s="79" t="s">
+      <c r="C22" s="78" t="s">
         <v>86</v>
       </c>
-      <c r="D22" s="80" t="s">
+      <c r="D22" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E22" s="29"/>
@@ -30182,10 +30181,10 @@
       <c r="B23" s="69" t="n">
         <v>15</v>
       </c>
-      <c r="C23" s="79" t="s">
+      <c r="C23" s="78" t="s">
         <v>86</v>
       </c>
-      <c r="D23" s="80" t="s">
+      <c r="D23" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E23" s="29"/>
@@ -30216,10 +30215,10 @@
       <c r="B24" s="69" t="n">
         <v>16</v>
       </c>
-      <c r="C24" s="79" t="s">
+      <c r="C24" s="78" t="s">
         <v>86</v>
       </c>
-      <c r="D24" s="80" t="s">
+      <c r="D24" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E24" s="29"/>
@@ -30250,10 +30249,10 @@
       <c r="B25" s="69" t="n">
         <v>17</v>
       </c>
-      <c r="C25" s="79" t="s">
+      <c r="C25" s="78" t="s">
         <v>86</v>
       </c>
-      <c r="D25" s="80" t="s">
+      <c r="D25" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E25" s="29"/>
@@ -30284,10 +30283,10 @@
       <c r="B26" s="69" t="n">
         <v>18</v>
       </c>
-      <c r="C26" s="79" t="s">
+      <c r="C26" s="78" t="s">
         <v>86</v>
       </c>
-      <c r="D26" s="80" t="s">
+      <c r="D26" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E26" s="29"/>
@@ -30318,10 +30317,10 @@
       <c r="B27" s="69" t="n">
         <v>19</v>
       </c>
-      <c r="C27" s="79" t="s">
+      <c r="C27" s="78" t="s">
         <v>86</v>
       </c>
-      <c r="D27" s="80" t="s">
+      <c r="D27" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E27" s="29"/>
@@ -30352,10 +30351,10 @@
       <c r="B28" s="69" t="n">
         <v>20</v>
       </c>
-      <c r="C28" s="79" t="s">
+      <c r="C28" s="78" t="s">
         <v>86</v>
       </c>
-      <c r="D28" s="80" t="s">
+      <c r="D28" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E28" s="29"/>
@@ -30386,10 +30385,10 @@
       <c r="B29" s="69" t="n">
         <v>21</v>
       </c>
-      <c r="C29" s="79" t="s">
+      <c r="C29" s="78" t="s">
         <v>86</v>
       </c>
-      <c r="D29" s="80" t="s">
+      <c r="D29" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E29" s="29"/>
@@ -30420,10 +30419,10 @@
       <c r="B30" s="69" t="n">
         <v>22</v>
       </c>
-      <c r="C30" s="79" t="s">
+      <c r="C30" s="78" t="s">
         <v>86</v>
       </c>
-      <c r="D30" s="80" t="s">
+      <c r="D30" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E30" s="29"/>
@@ -30567,7 +30566,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B1:AE54"/>
-  <sheetFormatPr defaultColWidth="9.01953125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.03125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="1" min="1" style="0" width="11.52"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="10.01"/>
@@ -30909,10 +30908,10 @@
       <c r="B7" s="69" t="n">
         <v>1</v>
       </c>
-      <c r="C7" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D7" s="80" t="s">
+      <c r="C7" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D7" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E7" s="71" t="s">
@@ -30939,7 +30938,7 @@
       </c>
       <c r="O7" s="70"/>
       <c r="P7" s="65"/>
-      <c r="Q7" s="81"/>
+      <c r="Q7" s="80"/>
       <c r="R7" s="58"/>
       <c r="U7" s="12"/>
       <c r="V7" s="59"/>
@@ -30955,10 +30954,10 @@
       <c r="B8" s="69" t="n">
         <v>2</v>
       </c>
-      <c r="C8" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D8" s="80" t="s">
+      <c r="C8" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D8" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E8" s="71" t="s">
@@ -30981,7 +30980,7 @@
       </c>
       <c r="O8" s="70"/>
       <c r="P8" s="65"/>
-      <c r="Q8" s="81"/>
+      <c r="Q8" s="80"/>
       <c r="R8" s="58"/>
       <c r="U8" s="12"/>
       <c r="V8" s="59"/>
@@ -30997,10 +30996,10 @@
       <c r="B9" s="69" t="n">
         <v>3</v>
       </c>
-      <c r="C9" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D9" s="80" t="s">
+      <c r="C9" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D9" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E9" s="65" t="s">
@@ -31023,7 +31022,7 @@
       </c>
       <c r="O9" s="70"/>
       <c r="P9" s="65"/>
-      <c r="Q9" s="81"/>
+      <c r="Q9" s="80"/>
       <c r="R9" s="58"/>
       <c r="U9" s="12"/>
       <c r="V9" s="59"/>
@@ -31039,10 +31038,10 @@
       <c r="B10" s="69" t="n">
         <v>4</v>
       </c>
-      <c r="C10" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D10" s="80" t="s">
+      <c r="C10" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D10" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E10" s="65" t="s">
@@ -31065,7 +31064,7 @@
       </c>
       <c r="O10" s="70"/>
       <c r="P10" s="65"/>
-      <c r="Q10" s="81"/>
+      <c r="Q10" s="80"/>
       <c r="R10" s="58"/>
       <c r="U10" s="12"/>
       <c r="V10" s="59"/>
@@ -31081,10 +31080,10 @@
       <c r="B11" s="69" t="n">
         <v>5</v>
       </c>
-      <c r="C11" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D11" s="80" t="s">
+      <c r="C11" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D11" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E11" s="0" t="s">
@@ -31101,7 +31100,7 @@
       </c>
       <c r="O11" s="70"/>
       <c r="P11" s="65"/>
-      <c r="Q11" s="81"/>
+      <c r="Q11" s="80"/>
       <c r="R11" s="58"/>
       <c r="U11" s="12"/>
       <c r="V11" s="59"/>
@@ -31117,10 +31116,10 @@
       <c r="B12" s="69" t="n">
         <v>6</v>
       </c>
-      <c r="C12" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D12" s="80" t="s">
+      <c r="C12" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D12" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E12" s="65" t="s">
@@ -31145,7 +31144,7 @@
       </c>
       <c r="O12" s="70"/>
       <c r="P12" s="65"/>
-      <c r="Q12" s="81"/>
+      <c r="Q12" s="80"/>
       <c r="R12" s="58"/>
       <c r="U12" s="12"/>
       <c r="V12" s="59"/>
@@ -31161,10 +31160,10 @@
       <c r="B13" s="69" t="n">
         <v>7</v>
       </c>
-      <c r="C13" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D13" s="80" t="s">
+      <c r="C13" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D13" s="79" t="s">
         <v>62</v>
       </c>
       <c r="E13" s="65"/>
@@ -31179,7 +31178,7 @@
       <c r="N13" s="72"/>
       <c r="O13" s="70"/>
       <c r="P13" s="65"/>
-      <c r="Q13" s="81"/>
+      <c r="Q13" s="80"/>
       <c r="R13" s="58"/>
       <c r="U13" s="12"/>
       <c r="V13" s="59"/>
@@ -31195,10 +31194,10 @@
       <c r="B14" s="69" t="n">
         <v>8</v>
       </c>
-      <c r="C14" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D14" s="80" t="s">
+      <c r="C14" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D14" s="79" t="s">
         <v>62</v>
       </c>
       <c r="E14" s="65"/>
@@ -31213,7 +31212,7 @@
       <c r="N14" s="72"/>
       <c r="O14" s="70"/>
       <c r="P14" s="65"/>
-      <c r="Q14" s="81"/>
+      <c r="Q14" s="80"/>
       <c r="R14" s="58"/>
       <c r="U14" s="12"/>
       <c r="V14" s="59"/>
@@ -31229,13 +31228,13 @@
       <c r="B15" s="69" t="n">
         <v>9</v>
       </c>
-      <c r="C15" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D15" s="80" t="s">
+      <c r="C15" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D15" s="79" t="s">
         <v>62</v>
       </c>
-      <c r="E15" s="85"/>
+      <c r="E15" s="84"/>
       <c r="F15" s="66"/>
       <c r="G15" s="66"/>
       <c r="H15" s="66"/>
@@ -31247,7 +31246,7 @@
       <c r="N15" s="72"/>
       <c r="O15" s="70"/>
       <c r="P15" s="65"/>
-      <c r="Q15" s="81"/>
+      <c r="Q15" s="80"/>
       <c r="R15" s="58"/>
       <c r="U15" s="12"/>
       <c r="V15" s="59"/>
@@ -31263,10 +31262,10 @@
       <c r="B16" s="69" t="n">
         <v>10</v>
       </c>
-      <c r="C16" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D16" s="80" t="s">
+      <c r="C16" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D16" s="79" t="s">
         <v>62</v>
       </c>
       <c r="E16" s="65"/>
@@ -31278,10 +31277,10 @@
       <c r="K16" s="69"/>
       <c r="L16" s="70"/>
       <c r="M16" s="71"/>
-      <c r="N16" s="86"/>
+      <c r="N16" s="85"/>
       <c r="O16" s="70"/>
       <c r="P16" s="65"/>
-      <c r="Q16" s="81"/>
+      <c r="Q16" s="80"/>
       <c r="R16" s="58"/>
       <c r="U16" s="12"/>
       <c r="V16" s="59"/>
@@ -31297,10 +31296,10 @@
       <c r="B17" s="69" t="n">
         <v>11</v>
       </c>
-      <c r="C17" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D17" s="80" t="s">
+      <c r="C17" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D17" s="79" t="s">
         <v>62</v>
       </c>
       <c r="E17" s="65"/>
@@ -31315,7 +31314,7 @@
       <c r="N17" s="72"/>
       <c r="O17" s="70"/>
       <c r="P17" s="65"/>
-      <c r="Q17" s="81"/>
+      <c r="Q17" s="80"/>
       <c r="R17" s="58"/>
       <c r="U17" s="12"/>
       <c r="V17" s="59"/>
@@ -31331,10 +31330,10 @@
       <c r="B18" s="69" t="n">
         <v>12</v>
       </c>
-      <c r="C18" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D18" s="80" t="s">
+      <c r="C18" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D18" s="79" t="s">
         <v>62</v>
       </c>
       <c r="E18" s="65"/>
@@ -31349,7 +31348,7 @@
       <c r="N18" s="72"/>
       <c r="O18" s="70"/>
       <c r="P18" s="65"/>
-      <c r="Q18" s="81"/>
+      <c r="Q18" s="80"/>
       <c r="R18" s="58"/>
       <c r="U18" s="12"/>
       <c r="V18" s="59"/>
@@ -31365,10 +31364,10 @@
       <c r="B19" s="69" t="n">
         <v>13</v>
       </c>
-      <c r="C19" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D19" s="80" t="s">
+      <c r="C19" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D19" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E19" s="65" t="s">
@@ -31395,7 +31394,7 @@
       </c>
       <c r="O19" s="70"/>
       <c r="P19" s="65"/>
-      <c r="Q19" s="81"/>
+      <c r="Q19" s="80"/>
       <c r="R19" s="58"/>
       <c r="U19" s="12"/>
       <c r="V19" s="59"/>
@@ -31411,10 +31410,10 @@
       <c r="B20" s="69" t="n">
         <v>14</v>
       </c>
-      <c r="C20" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D20" s="80" t="s">
+      <c r="C20" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D20" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E20" s="0" t="s">
@@ -31431,7 +31430,7 @@
       </c>
       <c r="O20" s="70"/>
       <c r="P20" s="65"/>
-      <c r="Q20" s="81"/>
+      <c r="Q20" s="80"/>
       <c r="R20" s="58"/>
       <c r="U20" s="12"/>
       <c r="V20" s="59"/>
@@ -31447,10 +31446,10 @@
       <c r="B21" s="69" t="n">
         <v>15</v>
       </c>
-      <c r="C21" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D21" s="80" t="s">
+      <c r="C21" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D21" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E21" s="0" t="s">
@@ -31459,7 +31458,7 @@
       <c r="I21" s="67" t="s">
         <v>324</v>
       </c>
-      <c r="L21" s="87" t="s">
+      <c r="L21" s="86" t="s">
         <v>343</v>
       </c>
       <c r="N21" s="73" t="s">
@@ -31467,7 +31466,7 @@
       </c>
       <c r="O21" s="70"/>
       <c r="P21" s="65"/>
-      <c r="Q21" s="81"/>
+      <c r="Q21" s="80"/>
       <c r="R21" s="58"/>
       <c r="U21" s="12"/>
       <c r="V21" s="59"/>
@@ -31483,10 +31482,10 @@
       <c r="B22" s="69" t="n">
         <v>16</v>
       </c>
-      <c r="C22" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D22" s="80" t="s">
+      <c r="C22" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D22" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E22" s="0" t="s">
@@ -31495,7 +31494,7 @@
       <c r="I22" s="67" t="s">
         <v>324</v>
       </c>
-      <c r="L22" s="87" t="s">
+      <c r="L22" s="86" t="s">
         <v>345</v>
       </c>
       <c r="N22" s="73" t="s">
@@ -31503,7 +31502,7 @@
       </c>
       <c r="O22" s="70"/>
       <c r="P22" s="65"/>
-      <c r="Q22" s="81"/>
+      <c r="Q22" s="80"/>
       <c r="R22" s="58"/>
       <c r="U22" s="12"/>
       <c r="V22" s="59"/>
@@ -31519,10 +31518,10 @@
       <c r="B23" s="69" t="n">
         <v>17</v>
       </c>
-      <c r="C23" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D23" s="80" t="s">
+      <c r="C23" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D23" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E23" s="0" t="s">
@@ -31539,7 +31538,7 @@
       </c>
       <c r="O23" s="70"/>
       <c r="P23" s="65"/>
-      <c r="Q23" s="81"/>
+      <c r="Q23" s="80"/>
       <c r="R23" s="58"/>
       <c r="U23" s="12"/>
       <c r="V23" s="59"/>
@@ -31555,10 +31554,10 @@
       <c r="B24" s="69" t="n">
         <v>18</v>
       </c>
-      <c r="C24" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D24" s="80" t="s">
+      <c r="C24" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D24" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E24" s="65" t="s">
@@ -31567,7 +31566,7 @@
       <c r="F24" s="66"/>
       <c r="G24" s="66"/>
       <c r="H24" s="66" t="s">
-        <v>292</v>
+        <v>348</v>
       </c>
       <c r="I24" s="67" t="s">
         <v>324</v>
@@ -31575,7 +31574,7 @@
       <c r="J24" s="68"/>
       <c r="K24" s="69"/>
       <c r="L24" s="70" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="M24" s="71"/>
       <c r="N24" s="73" t="s">
@@ -31583,7 +31582,7 @@
       </c>
       <c r="O24" s="70"/>
       <c r="P24" s="65"/>
-      <c r="Q24" s="81" t="s">
+      <c r="Q24" s="80" t="s">
         <v>296</v>
       </c>
       <c r="R24" s="58"/>
@@ -31601,14 +31600,14 @@
       <c r="B25" s="69" t="n">
         <v>19</v>
       </c>
-      <c r="C25" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D25" s="80" t="s">
+      <c r="C25" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D25" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E25" s="65" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="F25" s="66"/>
       <c r="G25" s="66"/>
@@ -31618,8 +31617,8 @@
       </c>
       <c r="J25" s="68"/>
       <c r="K25" s="69"/>
-      <c r="L25" s="87" t="s">
-        <v>350</v>
+      <c r="L25" s="86" t="s">
+        <v>351</v>
       </c>
       <c r="M25" s="71"/>
       <c r="N25" s="73" t="s">
@@ -31627,7 +31626,7 @@
       </c>
       <c r="O25" s="70"/>
       <c r="P25" s="65"/>
-      <c r="Q25" s="81"/>
+      <c r="Q25" s="80"/>
       <c r="R25" s="58"/>
       <c r="U25" s="12"/>
       <c r="V25" s="59"/>
@@ -31643,10 +31642,10 @@
       <c r="B26" s="69" t="n">
         <v>20</v>
       </c>
-      <c r="C26" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D26" s="80" t="s">
+      <c r="C26" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D26" s="79" t="s">
         <v>3</v>
       </c>
       <c r="E26" s="65" t="s">
@@ -31669,7 +31668,7 @@
       </c>
       <c r="O26" s="70"/>
       <c r="P26" s="65"/>
-      <c r="Q26" s="81"/>
+      <c r="Q26" s="80"/>
       <c r="R26" s="58"/>
       <c r="U26" s="12"/>
       <c r="V26" s="59"/>
@@ -31685,10 +31684,10 @@
       <c r="B27" s="69" t="n">
         <v>21</v>
       </c>
-      <c r="C27" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D27" s="80" t="s">
+      <c r="C27" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D27" s="79" t="s">
         <v>62</v>
       </c>
       <c r="E27" s="65"/>
@@ -31703,7 +31702,7 @@
       <c r="N27" s="72"/>
       <c r="O27" s="70"/>
       <c r="P27" s="65"/>
-      <c r="Q27" s="81"/>
+      <c r="Q27" s="80"/>
       <c r="R27" s="58"/>
       <c r="U27" s="12"/>
       <c r="V27" s="59"/>
@@ -31719,10 +31718,10 @@
       <c r="B28" s="69" t="n">
         <v>22</v>
       </c>
-      <c r="C28" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D28" s="80" t="s">
+      <c r="C28" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D28" s="79" t="s">
         <v>62</v>
       </c>
       <c r="E28" s="65"/>
@@ -31737,7 +31736,7 @@
       <c r="N28" s="72"/>
       <c r="O28" s="70"/>
       <c r="P28" s="65"/>
-      <c r="Q28" s="81"/>
+      <c r="Q28" s="80"/>
       <c r="R28" s="58"/>
       <c r="U28" s="12"/>
       <c r="V28" s="59"/>
@@ -31753,10 +31752,10 @@
       <c r="B29" s="69" t="n">
         <v>23</v>
       </c>
-      <c r="C29" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D29" s="80" t="s">
+      <c r="C29" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D29" s="79" t="s">
         <v>62</v>
       </c>
       <c r="E29" s="65"/>
@@ -31771,7 +31770,7 @@
       <c r="N29" s="72"/>
       <c r="O29" s="70"/>
       <c r="P29" s="65"/>
-      <c r="Q29" s="81"/>
+      <c r="Q29" s="80"/>
       <c r="R29" s="58"/>
       <c r="U29" s="12"/>
       <c r="V29" s="59"/>
@@ -31787,10 +31786,10 @@
       <c r="B30" s="69" t="n">
         <v>24</v>
       </c>
-      <c r="C30" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D30" s="80" t="s">
+      <c r="C30" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D30" s="79" t="s">
         <v>62</v>
       </c>
       <c r="E30" s="65"/>
@@ -31805,7 +31804,7 @@
       <c r="N30" s="72"/>
       <c r="O30" s="70"/>
       <c r="P30" s="65"/>
-      <c r="Q30" s="81"/>
+      <c r="Q30" s="80"/>
       <c r="R30" s="58"/>
       <c r="U30" s="12"/>
       <c r="V30" s="59"/>
@@ -31821,10 +31820,10 @@
       <c r="B31" s="69" t="n">
         <v>1</v>
       </c>
-      <c r="C31" s="79" t="s">
+      <c r="C31" s="78" t="s">
         <v>86</v>
       </c>
-      <c r="D31" s="80" t="s">
+      <c r="D31" s="79" t="s">
         <v>62</v>
       </c>
       <c r="E31" s="71"/>
@@ -31839,7 +31838,7 @@
       <c r="N31" s="72"/>
       <c r="O31" s="70"/>
       <c r="P31" s="65"/>
-      <c r="Q31" s="81"/>
+      <c r="Q31" s="80"/>
       <c r="R31" s="58"/>
       <c r="U31" s="12"/>
       <c r="V31" s="59"/>
@@ -31855,10 +31854,10 @@
       <c r="B32" s="69" t="n">
         <v>2</v>
       </c>
-      <c r="C32" s="79" t="s">
+      <c r="C32" s="78" t="s">
         <v>86</v>
       </c>
-      <c r="D32" s="80" t="s">
+      <c r="D32" s="79" t="s">
         <v>62</v>
       </c>
       <c r="E32" s="71"/>
@@ -31873,7 +31872,7 @@
       <c r="N32" s="72"/>
       <c r="O32" s="70"/>
       <c r="P32" s="65"/>
-      <c r="Q32" s="81"/>
+      <c r="Q32" s="80"/>
       <c r="R32" s="58"/>
       <c r="U32" s="12"/>
       <c r="V32" s="59"/>
@@ -31889,10 +31888,10 @@
       <c r="B33" s="69" t="n">
         <v>3</v>
       </c>
-      <c r="C33" s="79" t="s">
+      <c r="C33" s="78" t="s">
         <v>86</v>
       </c>
-      <c r="D33" s="80" t="s">
+      <c r="D33" s="79" t="s">
         <v>62</v>
       </c>
       <c r="E33" s="65"/>
@@ -31907,7 +31906,7 @@
       <c r="N33" s="72"/>
       <c r="O33" s="70"/>
       <c r="P33" s="65"/>
-      <c r="Q33" s="81"/>
+      <c r="Q33" s="80"/>
       <c r="R33" s="58"/>
       <c r="U33" s="12"/>
       <c r="V33" s="59"/>
@@ -31923,10 +31922,10 @@
       <c r="B34" s="69" t="n">
         <v>4</v>
       </c>
-      <c r="C34" s="79" t="s">
+      <c r="C34" s="78" t="s">
         <v>86</v>
       </c>
-      <c r="D34" s="80" t="s">
+      <c r="D34" s="79" t="s">
         <v>62</v>
       </c>
       <c r="E34" s="65"/>
@@ -31941,7 +31940,7 @@
       <c r="N34" s="72"/>
       <c r="O34" s="70"/>
       <c r="P34" s="65"/>
-      <c r="Q34" s="81"/>
+      <c r="Q34" s="80"/>
       <c r="R34" s="58"/>
       <c r="U34" s="12"/>
       <c r="V34" s="59"/>
@@ -31957,10 +31956,10 @@
       <c r="B35" s="69" t="n">
         <v>5</v>
       </c>
-      <c r="C35" s="79" t="s">
+      <c r="C35" s="78" t="s">
         <v>86</v>
       </c>
-      <c r="D35" s="80" t="s">
+      <c r="D35" s="79" t="s">
         <v>62</v>
       </c>
       <c r="E35" s="65"/>
@@ -31975,7 +31974,7 @@
       <c r="N35" s="72"/>
       <c r="O35" s="70"/>
       <c r="P35" s="65"/>
-      <c r="Q35" s="81"/>
+      <c r="Q35" s="80"/>
       <c r="R35" s="58"/>
       <c r="U35" s="12"/>
       <c r="V35" s="59"/>
@@ -31991,10 +31990,10 @@
       <c r="B36" s="69" t="n">
         <v>6</v>
       </c>
-      <c r="C36" s="79" t="s">
+      <c r="C36" s="78" t="s">
         <v>86</v>
       </c>
-      <c r="D36" s="80" t="s">
+      <c r="D36" s="79" t="s">
         <v>62</v>
       </c>
       <c r="E36" s="65"/>
@@ -32009,7 +32008,7 @@
       <c r="N36" s="72"/>
       <c r="O36" s="70"/>
       <c r="P36" s="65"/>
-      <c r="Q36" s="81"/>
+      <c r="Q36" s="80"/>
       <c r="R36" s="58"/>
       <c r="U36" s="12"/>
       <c r="V36" s="59"/>
@@ -32025,10 +32024,10 @@
       <c r="B37" s="69" t="n">
         <v>7</v>
       </c>
-      <c r="C37" s="79" t="s">
+      <c r="C37" s="78" t="s">
         <v>86</v>
       </c>
-      <c r="D37" s="80" t="s">
+      <c r="D37" s="79" t="s">
         <v>62</v>
       </c>
       <c r="E37" s="65"/>
@@ -32043,7 +32042,7 @@
       <c r="N37" s="72"/>
       <c r="O37" s="70"/>
       <c r="P37" s="65"/>
-      <c r="Q37" s="81"/>
+      <c r="Q37" s="80"/>
       <c r="R37" s="58"/>
       <c r="U37" s="12"/>
       <c r="V37" s="59"/>
@@ -32059,13 +32058,13 @@
       <c r="B38" s="69" t="n">
         <v>8</v>
       </c>
-      <c r="C38" s="79" t="s">
+      <c r="C38" s="78" t="s">
         <v>86</v>
       </c>
-      <c r="D38" s="80" t="s">
+      <c r="D38" s="79" t="s">
         <v>62</v>
       </c>
-      <c r="E38" s="82"/>
+      <c r="E38" s="81"/>
       <c r="F38" s="66"/>
       <c r="G38" s="66"/>
       <c r="H38" s="66"/>
@@ -32077,7 +32076,7 @@
       <c r="N38" s="72"/>
       <c r="O38" s="70"/>
       <c r="P38" s="65"/>
-      <c r="Q38" s="81"/>
+      <c r="Q38" s="80"/>
       <c r="R38" s="58"/>
       <c r="U38" s="12"/>
       <c r="V38" s="59"/>
@@ -32093,10 +32092,10 @@
       <c r="B39" s="69" t="n">
         <v>9</v>
       </c>
-      <c r="C39" s="79" t="s">
+      <c r="C39" s="78" t="s">
         <v>86</v>
       </c>
-      <c r="D39" s="80" t="s">
+      <c r="D39" s="79" t="s">
         <v>62</v>
       </c>
       <c r="E39" s="65"/>
@@ -32111,7 +32110,7 @@
       <c r="N39" s="72"/>
       <c r="O39" s="70"/>
       <c r="P39" s="65"/>
-      <c r="Q39" s="81"/>
+      <c r="Q39" s="80"/>
       <c r="R39" s="58"/>
       <c r="U39" s="12"/>
       <c r="V39" s="59"/>
@@ -32127,10 +32126,10 @@
       <c r="B40" s="69" t="n">
         <v>10</v>
       </c>
-      <c r="C40" s="79" t="s">
+      <c r="C40" s="78" t="s">
         <v>86</v>
       </c>
-      <c r="D40" s="80" t="s">
+      <c r="D40" s="79" t="s">
         <v>62</v>
       </c>
       <c r="E40" s="65"/>
@@ -32145,7 +32144,7 @@
       <c r="N40" s="72"/>
       <c r="O40" s="70"/>
       <c r="P40" s="65"/>
-      <c r="Q40" s="81"/>
+      <c r="Q40" s="80"/>
       <c r="R40" s="58"/>
       <c r="U40" s="12"/>
       <c r="V40" s="59"/>
@@ -32161,10 +32160,10 @@
       <c r="B41" s="69" t="n">
         <v>11</v>
       </c>
-      <c r="C41" s="79" t="s">
+      <c r="C41" s="78" t="s">
         <v>86</v>
       </c>
-      <c r="D41" s="80" t="s">
+      <c r="D41" s="79" t="s">
         <v>62</v>
       </c>
       <c r="E41" s="65"/>
@@ -32179,7 +32178,7 @@
       <c r="N41" s="72"/>
       <c r="O41" s="70"/>
       <c r="P41" s="65"/>
-      <c r="Q41" s="81"/>
+      <c r="Q41" s="80"/>
       <c r="R41" s="58"/>
       <c r="U41" s="12"/>
       <c r="V41" s="59"/>
@@ -32195,13 +32194,13 @@
       <c r="B42" s="69" t="n">
         <v>12</v>
       </c>
-      <c r="C42" s="79" t="s">
+      <c r="C42" s="78" t="s">
         <v>86</v>
       </c>
-      <c r="D42" s="80" t="s">
+      <c r="D42" s="79" t="s">
         <v>62</v>
       </c>
-      <c r="E42" s="82"/>
+      <c r="E42" s="81"/>
       <c r="F42" s="66"/>
       <c r="G42" s="66"/>
       <c r="H42" s="66"/>
@@ -32213,7 +32212,7 @@
       <c r="N42" s="72"/>
       <c r="O42" s="70"/>
       <c r="P42" s="65"/>
-      <c r="Q42" s="81"/>
+      <c r="Q42" s="80"/>
       <c r="R42" s="58"/>
       <c r="U42" s="12"/>
       <c r="V42" s="59"/>
@@ -32229,10 +32228,10 @@
       <c r="B43" s="69" t="n">
         <v>13</v>
       </c>
-      <c r="C43" s="79" t="s">
+      <c r="C43" s="78" t="s">
         <v>86</v>
       </c>
-      <c r="D43" s="80" t="s">
+      <c r="D43" s="79" t="s">
         <v>62</v>
       </c>
       <c r="E43" s="65"/>
@@ -32247,7 +32246,7 @@
       <c r="N43" s="72"/>
       <c r="O43" s="70"/>
       <c r="P43" s="65"/>
-      <c r="Q43" s="81"/>
+      <c r="Q43" s="80"/>
       <c r="R43" s="58"/>
       <c r="U43" s="12"/>
       <c r="V43" s="59"/>
@@ -32263,10 +32262,10 @@
       <c r="B44" s="69" t="n">
         <v>14</v>
       </c>
-      <c r="C44" s="79" t="s">
+      <c r="C44" s="78" t="s">
         <v>86</v>
       </c>
-      <c r="D44" s="80" t="s">
+      <c r="D44" s="79" t="s">
         <v>62</v>
       </c>
       <c r="E44" s="65"/>
@@ -32281,7 +32280,7 @@
       <c r="N44" s="72"/>
       <c r="O44" s="70"/>
       <c r="P44" s="65"/>
-      <c r="Q44" s="81"/>
+      <c r="Q44" s="80"/>
       <c r="R44" s="58"/>
       <c r="U44" s="12"/>
       <c r="V44" s="59"/>
@@ -32297,10 +32296,10 @@
       <c r="B45" s="69" t="n">
         <v>15</v>
       </c>
-      <c r="C45" s="79" t="s">
+      <c r="C45" s="78" t="s">
         <v>86</v>
       </c>
-      <c r="D45" s="80" t="s">
+      <c r="D45" s="79" t="s">
         <v>62</v>
       </c>
       <c r="E45" s="65"/>
@@ -32315,7 +32314,7 @@
       <c r="N45" s="72"/>
       <c r="O45" s="70"/>
       <c r="P45" s="65"/>
-      <c r="Q45" s="81"/>
+      <c r="Q45" s="80"/>
       <c r="R45" s="58"/>
       <c r="U45" s="12"/>
       <c r="V45" s="59"/>
@@ -32331,10 +32330,10 @@
       <c r="B46" s="69" t="n">
         <v>16</v>
       </c>
-      <c r="C46" s="79" t="s">
+      <c r="C46" s="78" t="s">
         <v>86</v>
       </c>
-      <c r="D46" s="80" t="s">
+      <c r="D46" s="79" t="s">
         <v>62</v>
       </c>
       <c r="E46" s="65"/>
@@ -32349,7 +32348,7 @@
       <c r="N46" s="72"/>
       <c r="O46" s="70"/>
       <c r="P46" s="65"/>
-      <c r="Q46" s="81"/>
+      <c r="Q46" s="80"/>
       <c r="R46" s="58"/>
       <c r="U46" s="12"/>
       <c r="V46" s="59"/>
@@ -32365,10 +32364,10 @@
       <c r="B47" s="69" t="n">
         <v>17</v>
       </c>
-      <c r="C47" s="79" t="s">
+      <c r="C47" s="78" t="s">
         <v>86</v>
       </c>
-      <c r="D47" s="80" t="s">
+      <c r="D47" s="79" t="s">
         <v>62</v>
       </c>
       <c r="E47" s="65"/>
@@ -32383,7 +32382,7 @@
       <c r="N47" s="72"/>
       <c r="O47" s="70"/>
       <c r="P47" s="65"/>
-      <c r="Q47" s="81"/>
+      <c r="Q47" s="80"/>
       <c r="R47" s="58"/>
       <c r="U47" s="12"/>
       <c r="V47" s="59"/>
@@ -32399,10 +32398,10 @@
       <c r="B48" s="69" t="n">
         <v>18</v>
       </c>
-      <c r="C48" s="79" t="s">
+      <c r="C48" s="78" t="s">
         <v>86</v>
       </c>
-      <c r="D48" s="80" t="s">
+      <c r="D48" s="79" t="s">
         <v>62</v>
       </c>
       <c r="E48" s="65"/>
@@ -32417,7 +32416,7 @@
       <c r="N48" s="72"/>
       <c r="O48" s="70"/>
       <c r="P48" s="65"/>
-      <c r="Q48" s="81"/>
+      <c r="Q48" s="80"/>
       <c r="R48" s="58"/>
       <c r="U48" s="12"/>
       <c r="V48" s="59"/>
@@ -32433,10 +32432,10 @@
       <c r="B49" s="69" t="n">
         <v>19</v>
       </c>
-      <c r="C49" s="79" t="s">
+      <c r="C49" s="78" t="s">
         <v>86</v>
       </c>
-      <c r="D49" s="80" t="s">
+      <c r="D49" s="79" t="s">
         <v>62</v>
       </c>
       <c r="E49" s="65"/>
@@ -32451,7 +32450,7 @@
       <c r="N49" s="72"/>
       <c r="O49" s="70"/>
       <c r="P49" s="65"/>
-      <c r="Q49" s="81"/>
+      <c r="Q49" s="80"/>
       <c r="R49" s="58"/>
       <c r="U49" s="12"/>
       <c r="V49" s="59"/>
@@ -32467,10 +32466,10 @@
       <c r="B50" s="69" t="n">
         <v>20</v>
       </c>
-      <c r="C50" s="79" t="s">
+      <c r="C50" s="78" t="s">
         <v>86</v>
       </c>
-      <c r="D50" s="80" t="s">
+      <c r="D50" s="79" t="s">
         <v>62</v>
       </c>
       <c r="E50" s="65"/>
@@ -32485,7 +32484,7 @@
       <c r="N50" s="72"/>
       <c r="O50" s="70"/>
       <c r="P50" s="65"/>
-      <c r="Q50" s="81"/>
+      <c r="Q50" s="80"/>
       <c r="R50" s="58"/>
       <c r="U50" s="12"/>
       <c r="V50" s="59"/>
@@ -32501,10 +32500,10 @@
       <c r="B51" s="69" t="n">
         <v>21</v>
       </c>
-      <c r="C51" s="79" t="s">
+      <c r="C51" s="78" t="s">
         <v>86</v>
       </c>
-      <c r="D51" s="80" t="s">
+      <c r="D51" s="79" t="s">
         <v>62</v>
       </c>
       <c r="E51" s="65"/>
@@ -32519,7 +32518,7 @@
       <c r="N51" s="72"/>
       <c r="O51" s="70"/>
       <c r="P51" s="65"/>
-      <c r="Q51" s="81"/>
+      <c r="Q51" s="80"/>
       <c r="R51" s="58"/>
       <c r="U51" s="12"/>
       <c r="V51" s="59"/>
@@ -32535,10 +32534,10 @@
       <c r="B52" s="69" t="n">
         <v>22</v>
       </c>
-      <c r="C52" s="79" t="s">
+      <c r="C52" s="78" t="s">
         <v>86</v>
       </c>
-      <c r="D52" s="80" t="s">
+      <c r="D52" s="79" t="s">
         <v>62</v>
       </c>
       <c r="E52" s="65"/>
@@ -32553,7 +32552,7 @@
       <c r="N52" s="72"/>
       <c r="O52" s="70"/>
       <c r="P52" s="65"/>
-      <c r="Q52" s="81"/>
+      <c r="Q52" s="80"/>
       <c r="R52" s="58"/>
       <c r="U52" s="12"/>
       <c r="V52" s="59"/>
@@ -32569,10 +32568,10 @@
       <c r="B53" s="69" t="n">
         <v>23</v>
       </c>
-      <c r="C53" s="79" t="s">
+      <c r="C53" s="78" t="s">
         <v>86</v>
       </c>
-      <c r="D53" s="80" t="s">
+      <c r="D53" s="79" t="s">
         <v>62</v>
       </c>
       <c r="E53" s="65"/>
@@ -32587,7 +32586,7 @@
       <c r="N53" s="72"/>
       <c r="O53" s="70"/>
       <c r="P53" s="65"/>
-      <c r="Q53" s="81"/>
+      <c r="Q53" s="80"/>
       <c r="R53" s="58"/>
       <c r="U53" s="12"/>
       <c r="V53" s="59"/>
@@ -32603,10 +32602,10 @@
       <c r="B54" s="69" t="n">
         <v>24</v>
       </c>
-      <c r="C54" s="79" t="s">
+      <c r="C54" s="78" t="s">
         <v>86</v>
       </c>
-      <c r="D54" s="80" t="s">
+      <c r="D54" s="79" t="s">
         <v>62</v>
       </c>
       <c r="F54" s="66"/>
@@ -32620,7 +32619,7 @@
       <c r="N54" s="72"/>
       <c r="O54" s="70"/>
       <c r="P54" s="65"/>
-      <c r="Q54" s="81"/>
+      <c r="Q54" s="80"/>
       <c r="R54" s="58"/>
       <c r="U54" s="12"/>
       <c r="V54" s="59"/>

--- a/startup/standards/standards.xlsx
+++ b/startup/standards/standards.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="12"/>
   </bookViews>
   <sheets>
     <sheet name="Ti" sheetId="1" state="visible" r:id="rId2"/>
@@ -1700,7 +1700,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3282" uniqueCount="596">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3288" uniqueCount="600">
   <si>
     <t xml:space="preserve">Double wheel</t>
   </si>
@@ -3007,10 +3007,22 @@
     <t xml:space="preserve">PbCl, lead chloride</t>
   </si>
   <si>
+    <t xml:space="preserve">PtACAC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pt(C5H7O2)2, Platinum acetylacetonate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">powder on tape 18 layers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAS#15170=57=7. STREM Chemicals Inc., Cat#78-1400-1G, Lot#L00102507, Sample courtesy Elaine Flynn, Washington University</t>
+  </si>
+  <si>
     <t xml:space="preserve">PtRu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pt</t>
   </si>
   <si>
     <t xml:space="preserve">PtRu powder</t>
@@ -3850,7 +3862,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="110">
+  <cellXfs count="111">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -4199,6 +4211,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -4374,9 +4390,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>40320</xdr:colOff>
+      <xdr:colOff>39960</xdr:colOff>
       <xdr:row>65</xdr:row>
-      <xdr:rowOff>66600</xdr:rowOff>
+      <xdr:rowOff>66240</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4389,8 +4405,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1656360" y="11943000"/>
-          <a:ext cx="3207240" cy="1822320"/>
+          <a:off x="1657080" y="11943000"/>
+          <a:ext cx="3206880" cy="1821960"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4416,9 +4432,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>855720</xdr:colOff>
+      <xdr:colOff>855360</xdr:colOff>
       <xdr:row>43</xdr:row>
-      <xdr:rowOff>162000</xdr:rowOff>
+      <xdr:rowOff>161640</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4431,8 +4447,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2073600" y="7088040"/>
-          <a:ext cx="3605400" cy="2246400"/>
+          <a:off x="2074320" y="7088040"/>
+          <a:ext cx="3605040" cy="2246040"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4458,9 +4474,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>855720</xdr:colOff>
+      <xdr:colOff>855360</xdr:colOff>
       <xdr:row>43</xdr:row>
-      <xdr:rowOff>162360</xdr:rowOff>
+      <xdr:rowOff>162000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4473,8 +4489,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2073600" y="5591880"/>
-          <a:ext cx="3605400" cy="2246760"/>
+          <a:off x="2074320" y="5591880"/>
+          <a:ext cx="3605040" cy="2246400"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4495,7 +4511,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B1:AE54"/>
-  <sheetFormatPr defaultColWidth="9.03125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.0390625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="1" min="1" style="0" width="11.52"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="10.01"/>
@@ -6709,7 +6725,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B1:AE30"/>
-  <sheetFormatPr defaultColWidth="9.03125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.0390625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="1" min="1" style="0" width="11.52"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="10.01"/>
@@ -8053,7 +8069,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B1:AE30"/>
-  <sheetFormatPr defaultColWidth="9.03125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.0390625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="1" min="1" style="0" width="11.52"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="10.01"/>
@@ -9379,7 +9395,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B1:AE54"/>
-  <sheetFormatPr defaultColWidth="9.03125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.0390625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="1" min="1" style="0" width="11.52"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="10.01"/>
@@ -11569,7 +11585,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B1:AE54"/>
-  <sheetFormatPr defaultColWidth="9.03125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.0390625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="1" min="1" style="0" width="11.52"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="10.01"/>
@@ -12555,7 +12571,7 @@
       <c r="AB24" s="62"/>
       <c r="AC24" s="63"/>
     </row>
-    <row r="25" customFormat="false" ht="20.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="43.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="69" t="n">
         <v>19</v>
       </c>
@@ -12565,16 +12581,28 @@
       <c r="D25" s="79" t="s">
         <v>3</v>
       </c>
-      <c r="E25" s="65"/>
+      <c r="E25" s="65" t="s">
+        <v>435</v>
+      </c>
       <c r="F25" s="66"/>
       <c r="G25" s="66"/>
       <c r="H25" s="66"/>
-      <c r="I25" s="67"/>
-      <c r="J25" s="68"/>
+      <c r="I25" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="J25" s="68" t="s">
+        <v>164</v>
+      </c>
       <c r="K25" s="69"/>
-      <c r="L25" s="86"/>
-      <c r="M25" s="71"/>
-      <c r="N25" s="73"/>
+      <c r="L25" s="87" t="s">
+        <v>437</v>
+      </c>
+      <c r="M25" s="53" t="s">
+        <v>438</v>
+      </c>
+      <c r="N25" s="73" t="s">
+        <v>439</v>
+      </c>
       <c r="O25" s="64"/>
       <c r="P25" s="29"/>
       <c r="Q25" s="57"/>
@@ -12624,7 +12652,7 @@
         <v>3</v>
       </c>
       <c r="E27" s="0" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="I27" s="67" t="s">
         <v>436</v>
@@ -12633,7 +12661,7 @@
         <v>164</v>
       </c>
       <c r="L27" s="0" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="M27" s="71" t="s">
         <v>53</v>
@@ -12666,7 +12694,7 @@
         <v>3</v>
       </c>
       <c r="E28" s="65" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="F28" s="66"/>
       <c r="G28" s="66"/>
@@ -12679,13 +12707,13 @@
       </c>
       <c r="K28" s="69"/>
       <c r="L28" s="86" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="M28" s="71" t="s">
         <v>53</v>
       </c>
       <c r="N28" s="72" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="O28" s="64"/>
       <c r="P28" s="29"/>
@@ -12712,7 +12740,7 @@
         <v>3</v>
       </c>
       <c r="E29" s="65" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="F29" s="66"/>
       <c r="G29" s="66"/>
@@ -12725,13 +12753,13 @@
       </c>
       <c r="K29" s="69"/>
       <c r="L29" s="70" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="M29" s="71" t="s">
         <v>53</v>
       </c>
       <c r="N29" s="72" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="O29" s="64"/>
       <c r="P29" s="29"/>
@@ -12758,7 +12786,7 @@
         <v>3</v>
       </c>
       <c r="E30" s="65" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="F30" s="66"/>
       <c r="G30" s="66"/>
@@ -12771,13 +12799,13 @@
       </c>
       <c r="K30" s="69"/>
       <c r="L30" s="65" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="M30" s="71" t="s">
         <v>53</v>
       </c>
       <c r="N30" s="72" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="O30" s="64"/>
       <c r="P30" s="29"/>
@@ -12838,20 +12866,20 @@
         <v>3</v>
       </c>
       <c r="E32" s="71" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="F32" s="66"/>
       <c r="G32" s="66"/>
       <c r="H32" s="66"/>
       <c r="I32" s="67" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="J32" s="68" t="s">
         <v>164</v>
       </c>
       <c r="K32" s="69"/>
       <c r="L32" s="70" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="M32" s="71"/>
       <c r="N32" s="73" t="s">
@@ -12882,20 +12910,20 @@
         <v>3</v>
       </c>
       <c r="E33" s="65" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="F33" s="66"/>
       <c r="G33" s="66"/>
       <c r="H33" s="66"/>
       <c r="I33" s="67" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="J33" s="68" t="s">
         <v>164</v>
       </c>
       <c r="K33" s="69"/>
       <c r="L33" s="70" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="M33" s="71" t="s">
         <v>53</v>
@@ -13132,20 +13160,20 @@
         <v>3</v>
       </c>
       <c r="E40" s="65" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="F40" s="66"/>
       <c r="G40" s="66"/>
       <c r="H40" s="66"/>
       <c r="I40" s="67" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="J40" s="68" t="s">
         <v>164</v>
       </c>
       <c r="K40" s="69"/>
       <c r="L40" s="70" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="M40" s="71" t="s">
         <v>53</v>
@@ -13176,20 +13204,20 @@
         <v>3</v>
       </c>
       <c r="E41" s="65" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="F41" s="66"/>
       <c r="G41" s="66"/>
       <c r="H41" s="66"/>
       <c r="I41" s="67" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="J41" s="68" t="s">
         <v>164</v>
       </c>
       <c r="K41" s="69"/>
       <c r="L41" s="70" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="M41" s="71" t="s">
         <v>53</v>
@@ -13220,20 +13248,20 @@
         <v>3</v>
       </c>
       <c r="E42" s="65" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="F42" s="66"/>
       <c r="G42" s="66"/>
       <c r="H42" s="66"/>
       <c r="I42" s="67" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="J42" s="68" t="s">
         <v>164</v>
       </c>
       <c r="K42" s="69"/>
       <c r="L42" s="70" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="M42" s="71" t="s">
         <v>53</v>
@@ -13264,20 +13292,20 @@
         <v>3</v>
       </c>
       <c r="E43" s="65" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="F43" s="66"/>
       <c r="G43" s="66"/>
       <c r="H43" s="66"/>
       <c r="I43" s="67" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="J43" s="68" t="s">
         <v>164</v>
       </c>
       <c r="K43" s="69"/>
       <c r="L43" s="70" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="M43" s="71" t="s">
         <v>53</v>
@@ -13383,20 +13411,20 @@
         <v>3</v>
       </c>
       <c r="E47" s="65" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="F47" s="66"/>
       <c r="G47" s="66"/>
       <c r="H47" s="66"/>
       <c r="I47" s="67" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="J47" s="68" t="s">
         <v>164</v>
       </c>
       <c r="K47" s="69"/>
       <c r="L47" s="70" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="M47" s="71" t="s">
         <v>53</v>
@@ -13427,20 +13455,20 @@
         <v>3</v>
       </c>
       <c r="E48" s="65" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="F48" s="66"/>
       <c r="G48" s="66"/>
       <c r="H48" s="66"/>
       <c r="I48" s="67" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="J48" s="68" t="s">
         <v>164</v>
       </c>
       <c r="K48" s="69"/>
       <c r="L48" s="86" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="M48" s="71" t="s">
         <v>393</v>
@@ -13505,20 +13533,20 @@
         <v>3</v>
       </c>
       <c r="E50" s="65" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="F50" s="66"/>
       <c r="G50" s="66"/>
       <c r="H50" s="66"/>
       <c r="I50" s="67" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="J50" s="68" t="s">
         <v>164</v>
       </c>
       <c r="K50" s="69"/>
       <c r="L50" s="70" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="M50" s="71" t="s">
         <v>393</v>
@@ -13549,20 +13577,20 @@
         <v>3</v>
       </c>
       <c r="E51" s="65" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="F51" s="66"/>
       <c r="G51" s="66"/>
       <c r="H51" s="66"/>
       <c r="I51" s="67" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="J51" s="68" t="s">
         <v>164</v>
       </c>
       <c r="K51" s="69"/>
       <c r="L51" s="70" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="M51" s="71" t="s">
         <v>393</v>
@@ -13593,24 +13621,24 @@
         <v>3</v>
       </c>
       <c r="E52" s="65" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="F52" s="66"/>
       <c r="G52" s="66"/>
       <c r="H52" s="66"/>
       <c r="I52" s="67" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="J52" s="68" t="s">
         <v>164</v>
       </c>
       <c r="K52" s="69"/>
       <c r="L52" s="65" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="M52" s="71"/>
       <c r="N52" s="73" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="O52" s="64"/>
       <c r="P52" s="29"/>
@@ -13637,20 +13665,20 @@
         <v>3</v>
       </c>
       <c r="E53" s="65" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="F53" s="66"/>
       <c r="G53" s="66"/>
       <c r="H53" s="66"/>
       <c r="I53" s="67" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="J53" s="68" t="s">
         <v>164</v>
       </c>
       <c r="K53" s="69"/>
       <c r="L53" s="70" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="M53" s="65"/>
       <c r="N53" s="73" t="s">
@@ -13681,20 +13709,20 @@
         <v>3</v>
       </c>
       <c r="E54" s="65" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="F54" s="66"/>
       <c r="G54" s="66"/>
       <c r="H54" s="66"/>
       <c r="I54" s="67" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="J54" s="68" t="s">
         <v>164</v>
       </c>
       <c r="K54" s="69"/>
       <c r="L54" s="70" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="M54" s="71"/>
       <c r="N54" s="73" t="s">
@@ -13831,7 +13859,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B1:AE79"/>
-  <sheetFormatPr defaultColWidth="9.03125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.0390625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="1" min="1" style="0" width="11.52"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="10.01"/>
@@ -14180,26 +14208,26 @@
         <v>3</v>
       </c>
       <c r="E7" s="53" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="F7" s="13"/>
       <c r="G7" s="13"/>
       <c r="H7" s="13"/>
-      <c r="I7" s="87" t="s">
+      <c r="I7" s="88" t="s">
         <v>49</v>
       </c>
-      <c r="J7" s="88" t="s">
+      <c r="J7" s="89" t="s">
         <v>50</v>
       </c>
       <c r="K7" s="50"/>
       <c r="L7" s="56" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="M7" s="53" t="s">
         <v>329</v>
       </c>
       <c r="N7" s="86" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="O7" s="56"/>
       <c r="P7" s="29"/>
@@ -14226,20 +14254,20 @@
         <v>3</v>
       </c>
       <c r="E8" s="53" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="F8" s="13"/>
       <c r="G8" s="13"/>
       <c r="H8" s="13"/>
-      <c r="I8" s="87" t="s">
-        <v>477</v>
-      </c>
-      <c r="J8" s="88" t="s">
+      <c r="I8" s="88" t="s">
+        <v>481</v>
+      </c>
+      <c r="J8" s="89" t="s">
         <v>164</v>
       </c>
       <c r="K8" s="50"/>
       <c r="L8" s="56" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="M8" s="53" t="s">
         <v>108</v>
@@ -14248,7 +14276,7 @@
         <v>167</v>
       </c>
       <c r="O8" s="75" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="P8" s="29"/>
       <c r="Q8" s="57"/>
@@ -14264,36 +14292,36 @@
       <c r="AC8" s="63"/>
     </row>
     <row r="9" customFormat="false" ht="20.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="89" t="n">
+      <c r="B9" s="90" t="n">
         <v>1</v>
       </c>
-      <c r="C9" s="90" t="s">
-        <v>45</v>
-      </c>
-      <c r="D9" s="91" t="s">
+      <c r="C9" s="91" t="s">
+        <v>45</v>
+      </c>
+      <c r="D9" s="92" t="s">
         <v>62</v>
       </c>
-      <c r="E9" s="92" t="s">
-        <v>480</v>
-      </c>
-      <c r="F9" s="89"/>
-      <c r="G9" s="89"/>
-      <c r="H9" s="89"/>
-      <c r="I9" s="93" t="s">
-        <v>481</v>
-      </c>
-      <c r="J9" s="94" t="s">
+      <c r="E9" s="93" t="s">
+        <v>484</v>
+      </c>
+      <c r="F9" s="90"/>
+      <c r="G9" s="90"/>
+      <c r="H9" s="90"/>
+      <c r="I9" s="94" t="s">
+        <v>485</v>
+      </c>
+      <c r="J9" s="95" t="s">
         <v>164</v>
       </c>
-      <c r="K9" s="89"/>
-      <c r="L9" s="95" t="s">
-        <v>482</v>
-      </c>
-      <c r="M9" s="92"/>
-      <c r="N9" s="96"/>
-      <c r="O9" s="95"/>
-      <c r="P9" s="97"/>
-      <c r="Q9" s="95"/>
+      <c r="K9" s="90"/>
+      <c r="L9" s="96" t="s">
+        <v>486</v>
+      </c>
+      <c r="M9" s="93"/>
+      <c r="N9" s="97"/>
+      <c r="O9" s="96"/>
+      <c r="P9" s="98"/>
+      <c r="Q9" s="96"/>
       <c r="R9" s="58"/>
       <c r="U9" s="12"/>
       <c r="V9" s="59"/>
@@ -14316,15 +14344,15 @@
         <v>3</v>
       </c>
       <c r="E10" s="53" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="F10" s="13"/>
       <c r="G10" s="13"/>
       <c r="H10" s="13"/>
-      <c r="I10" s="87" t="s">
+      <c r="I10" s="88" t="s">
         <v>243</v>
       </c>
-      <c r="J10" s="88" t="s">
+      <c r="J10" s="89" t="s">
         <v>50</v>
       </c>
       <c r="K10" s="50"/>
@@ -14335,7 +14363,7 @@
         <v>329</v>
       </c>
       <c r="N10" s="86" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="O10" s="56"/>
       <c r="P10" s="29"/>
@@ -14362,20 +14390,20 @@
         <v>3</v>
       </c>
       <c r="E11" s="53" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="F11" s="13"/>
       <c r="G11" s="13"/>
       <c r="H11" s="13"/>
-      <c r="I11" s="87" t="s">
+      <c r="I11" s="88" t="s">
         <v>176</v>
       </c>
-      <c r="J11" s="88" t="s">
+      <c r="J11" s="89" t="s">
         <v>164</v>
       </c>
       <c r="K11" s="50"/>
       <c r="L11" s="56" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="M11" s="53" t="s">
         <v>108</v>
@@ -14384,7 +14412,7 @@
         <v>167</v>
       </c>
       <c r="O11" s="75" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="P11" s="29"/>
       <c r="Q11" s="57"/>
@@ -14410,20 +14438,20 @@
         <v>3</v>
       </c>
       <c r="E12" s="53" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="F12" s="13"/>
       <c r="G12" s="13"/>
       <c r="H12" s="13"/>
-      <c r="I12" s="87" t="s">
-        <v>477</v>
-      </c>
-      <c r="J12" s="88" t="s">
-        <v>487</v>
+      <c r="I12" s="88" t="s">
+        <v>481</v>
+      </c>
+      <c r="J12" s="89" t="s">
+        <v>491</v>
       </c>
       <c r="K12" s="50"/>
       <c r="L12" s="56" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="M12" s="53" t="s">
         <v>108</v>
@@ -14456,15 +14484,15 @@
         <v>3</v>
       </c>
       <c r="E13" s="53" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="F13" s="13"/>
       <c r="G13" s="13"/>
       <c r="H13" s="13"/>
-      <c r="I13" s="87" t="s">
+      <c r="I13" s="88" t="s">
         <v>163</v>
       </c>
-      <c r="J13" s="88" t="s">
+      <c r="J13" s="89" t="s">
         <v>164</v>
       </c>
       <c r="K13" s="50"/>
@@ -14478,7 +14506,7 @@
         <v>167</v>
       </c>
       <c r="O13" s="75" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="P13" s="29"/>
       <c r="Q13" s="57"/>
@@ -14504,20 +14532,20 @@
         <v>3</v>
       </c>
       <c r="E14" s="53" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="F14" s="13"/>
       <c r="G14" s="13"/>
       <c r="H14" s="13"/>
-      <c r="I14" s="87" t="s">
+      <c r="I14" s="88" t="s">
         <v>200</v>
       </c>
-      <c r="J14" s="88" t="s">
+      <c r="J14" s="89" t="s">
         <v>164</v>
       </c>
       <c r="K14" s="50"/>
       <c r="L14" s="56" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="M14" s="53" t="s">
         <v>108</v>
@@ -14552,26 +14580,26 @@
         <v>3</v>
       </c>
       <c r="E15" s="53" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="F15" s="13"/>
       <c r="G15" s="13"/>
       <c r="H15" s="13"/>
-      <c r="I15" s="87" t="s">
-        <v>493</v>
-      </c>
-      <c r="J15" s="88" t="s">
+      <c r="I15" s="88" t="s">
+        <v>497</v>
+      </c>
+      <c r="J15" s="89" t="s">
         <v>50</v>
       </c>
       <c r="K15" s="50"/>
       <c r="L15" s="56" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="M15" s="53" t="s">
         <v>329</v>
       </c>
       <c r="N15" s="86" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="O15" s="56"/>
       <c r="P15" s="29"/>
@@ -14588,36 +14616,36 @@
       <c r="AC15" s="63"/>
     </row>
     <row r="16" customFormat="false" ht="20.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="89" t="n">
+      <c r="B16" s="90" t="n">
         <v>1</v>
       </c>
-      <c r="C16" s="90" t="s">
-        <v>45</v>
-      </c>
-      <c r="D16" s="91" t="s">
+      <c r="C16" s="91" t="s">
+        <v>45</v>
+      </c>
+      <c r="D16" s="92" t="s">
         <v>62</v>
       </c>
-      <c r="E16" s="92" t="s">
-        <v>480</v>
-      </c>
-      <c r="F16" s="89"/>
-      <c r="G16" s="89"/>
-      <c r="H16" s="89"/>
-      <c r="I16" s="93" t="s">
-        <v>481</v>
-      </c>
-      <c r="J16" s="94" t="s">
-        <v>487</v>
-      </c>
-      <c r="K16" s="89"/>
-      <c r="L16" s="95" t="s">
-        <v>482</v>
-      </c>
-      <c r="M16" s="92"/>
-      <c r="N16" s="96"/>
-      <c r="O16" s="95"/>
-      <c r="P16" s="97"/>
-      <c r="Q16" s="95"/>
+      <c r="E16" s="93" t="s">
+        <v>484</v>
+      </c>
+      <c r="F16" s="90"/>
+      <c r="G16" s="90"/>
+      <c r="H16" s="90"/>
+      <c r="I16" s="94" t="s">
+        <v>485</v>
+      </c>
+      <c r="J16" s="95" t="s">
+        <v>491</v>
+      </c>
+      <c r="K16" s="90"/>
+      <c r="L16" s="96" t="s">
+        <v>486</v>
+      </c>
+      <c r="M16" s="93"/>
+      <c r="N16" s="97"/>
+      <c r="O16" s="96"/>
+      <c r="P16" s="98"/>
+      <c r="Q16" s="96"/>
       <c r="R16" s="58"/>
       <c r="U16" s="12"/>
       <c r="V16" s="59"/>
@@ -14640,20 +14668,20 @@
         <v>3</v>
       </c>
       <c r="E17" s="53" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="F17" s="13"/>
       <c r="G17" s="13"/>
       <c r="H17" s="13"/>
-      <c r="I17" s="87" t="s">
+      <c r="I17" s="88" t="s">
         <v>205</v>
       </c>
-      <c r="J17" s="88" t="s">
+      <c r="J17" s="89" t="s">
         <v>164</v>
       </c>
       <c r="K17" s="50"/>
       <c r="L17" s="56" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="M17" s="53" t="s">
         <v>108</v>
@@ -14688,20 +14716,20 @@
         <v>3</v>
       </c>
       <c r="E18" s="53" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="F18" s="13"/>
       <c r="G18" s="13"/>
       <c r="H18" s="13"/>
-      <c r="I18" s="87" t="s">
+      <c r="I18" s="88" t="s">
         <v>176</v>
       </c>
-      <c r="J18" s="88" t="s">
-        <v>487</v>
+      <c r="J18" s="89" t="s">
+        <v>491</v>
       </c>
       <c r="K18" s="50"/>
       <c r="L18" s="56" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="M18" s="53" t="s">
         <v>108</v>
@@ -14734,26 +14762,26 @@
         <v>3</v>
       </c>
       <c r="E19" s="53" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="F19" s="13"/>
       <c r="G19" s="13"/>
       <c r="H19" s="13"/>
-      <c r="I19" s="87" t="s">
+      <c r="I19" s="88" t="s">
         <v>271</v>
       </c>
-      <c r="J19" s="88" t="s">
+      <c r="J19" s="89" t="s">
         <v>50</v>
       </c>
       <c r="K19" s="50"/>
       <c r="L19" s="56" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="M19" s="53" t="s">
         <v>255</v>
       </c>
       <c r="N19" s="86" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="O19" s="56"/>
       <c r="P19" s="29"/>
@@ -14780,16 +14808,16 @@
         <v>3</v>
       </c>
       <c r="E20" s="53" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="F20" s="13"/>
       <c r="G20" s="13"/>
       <c r="H20" s="13"/>
-      <c r="I20" s="87" t="s">
+      <c r="I20" s="88" t="s">
         <v>163</v>
       </c>
-      <c r="J20" s="88" t="s">
-        <v>487</v>
+      <c r="J20" s="89" t="s">
+        <v>491</v>
       </c>
       <c r="K20" s="50"/>
       <c r="L20" s="56" t="s">
@@ -14826,20 +14854,20 @@
         <v>3</v>
       </c>
       <c r="E21" s="53" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="F21" s="13"/>
       <c r="G21" s="13"/>
       <c r="H21" s="13"/>
-      <c r="I21" s="87" t="s">
+      <c r="I21" s="88" t="s">
         <v>179</v>
       </c>
-      <c r="J21" s="88" t="s">
+      <c r="J21" s="89" t="s">
         <v>164</v>
       </c>
       <c r="K21" s="50"/>
       <c r="L21" s="56" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="M21" s="53" t="s">
         <v>108</v>
@@ -14874,20 +14902,20 @@
         <v>3</v>
       </c>
       <c r="E22" s="53" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="F22" s="13"/>
       <c r="G22" s="13"/>
       <c r="H22" s="13"/>
-      <c r="I22" s="87" t="s">
+      <c r="I22" s="88" t="s">
         <v>200</v>
       </c>
-      <c r="J22" s="88" t="s">
-        <v>487</v>
+      <c r="J22" s="89" t="s">
+        <v>491</v>
       </c>
       <c r="K22" s="50"/>
       <c r="L22" s="56" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="M22" s="53" t="s">
         <v>108</v>
@@ -14920,20 +14948,20 @@
         <v>3</v>
       </c>
       <c r="E23" s="53" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="F23" s="13"/>
       <c r="G23" s="13"/>
       <c r="H23" s="13"/>
-      <c r="I23" s="87" t="s">
+      <c r="I23" s="88" t="s">
         <v>183</v>
       </c>
-      <c r="J23" s="88" t="s">
+      <c r="J23" s="89" t="s">
         <v>164</v>
       </c>
       <c r="K23" s="50"/>
       <c r="L23" s="56" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="M23" s="53" t="s">
         <v>108</v>
@@ -14968,26 +14996,26 @@
         <v>3</v>
       </c>
       <c r="E24" s="53" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="F24" s="13"/>
       <c r="G24" s="13"/>
       <c r="H24" s="13"/>
-      <c r="I24" s="87" t="s">
+      <c r="I24" s="88" t="s">
         <v>89</v>
       </c>
-      <c r="J24" s="88" t="s">
+      <c r="J24" s="89" t="s">
         <v>50</v>
       </c>
       <c r="K24" s="50"/>
       <c r="L24" s="56" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="M24" s="53" t="s">
         <v>329</v>
       </c>
       <c r="N24" s="86" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="O24" s="56"/>
       <c r="P24" s="29"/>
@@ -15014,20 +15042,20 @@
         <v>3</v>
       </c>
       <c r="E25" s="53" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="F25" s="13"/>
       <c r="G25" s="13"/>
       <c r="H25" s="13"/>
-      <c r="I25" s="87" t="s">
+      <c r="I25" s="88" t="s">
         <v>205</v>
       </c>
-      <c r="J25" s="88" t="s">
-        <v>487</v>
+      <c r="J25" s="89" t="s">
+        <v>491</v>
       </c>
       <c r="K25" s="50"/>
       <c r="L25" s="56" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="M25" s="53" t="s">
         <v>108</v>
@@ -15060,20 +15088,20 @@
         <v>3</v>
       </c>
       <c r="E26" s="53" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="F26" s="13"/>
       <c r="G26" s="13"/>
       <c r="H26" s="13"/>
-      <c r="I26" s="87" t="s">
+      <c r="I26" s="88" t="s">
         <v>195</v>
       </c>
-      <c r="J26" s="88" t="s">
+      <c r="J26" s="89" t="s">
         <v>164</v>
       </c>
       <c r="K26" s="50"/>
       <c r="L26" s="56" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="M26" s="53" t="s">
         <v>108</v>
@@ -15108,20 +15136,20 @@
         <v>3</v>
       </c>
       <c r="E27" s="53" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="F27" s="13"/>
       <c r="G27" s="13"/>
       <c r="H27" s="13"/>
-      <c r="I27" s="87" t="s">
+      <c r="I27" s="88" t="s">
         <v>219</v>
       </c>
-      <c r="J27" s="88" t="s">
+      <c r="J27" s="89" t="s">
         <v>164</v>
       </c>
       <c r="K27" s="50"/>
       <c r="L27" s="56" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="M27" s="53" t="s">
         <v>108</v>
@@ -15156,26 +15184,26 @@
         <v>3</v>
       </c>
       <c r="E28" s="53" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="F28" s="13"/>
       <c r="G28" s="13"/>
       <c r="H28" s="13"/>
-      <c r="I28" s="87" t="s">
+      <c r="I28" s="88" t="s">
         <v>305</v>
       </c>
-      <c r="J28" s="88" t="s">
+      <c r="J28" s="89" t="s">
         <v>50</v>
       </c>
       <c r="K28" s="50"/>
       <c r="L28" s="56" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="M28" s="53" t="s">
         <v>329</v>
       </c>
       <c r="N28" s="86" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="O28" s="56"/>
       <c r="P28" s="29"/>
@@ -15202,20 +15230,20 @@
         <v>3</v>
       </c>
       <c r="E29" s="53" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="F29" s="13"/>
       <c r="G29" s="13"/>
       <c r="H29" s="13"/>
-      <c r="I29" s="87" t="s">
+      <c r="I29" s="88" t="s">
         <v>179</v>
       </c>
-      <c r="J29" s="88" t="s">
-        <v>487</v>
+      <c r="J29" s="89" t="s">
+        <v>491</v>
       </c>
       <c r="K29" s="50"/>
       <c r="L29" s="56" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="M29" s="53" t="s">
         <v>108</v>
@@ -15248,20 +15276,20 @@
         <v>3</v>
       </c>
       <c r="E30" s="53" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="F30" s="13"/>
       <c r="G30" s="13"/>
       <c r="H30" s="13"/>
-      <c r="I30" s="87" t="s">
+      <c r="I30" s="88" t="s">
         <v>222</v>
       </c>
-      <c r="J30" s="88" t="s">
+      <c r="J30" s="89" t="s">
         <v>164</v>
       </c>
       <c r="K30" s="50"/>
       <c r="L30" s="56" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="M30" s="53" t="s">
         <v>108</v>
@@ -15296,20 +15324,20 @@
         <v>3</v>
       </c>
       <c r="E31" s="53" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="F31" s="13"/>
       <c r="G31" s="13"/>
       <c r="H31" s="13"/>
-      <c r="I31" s="87" t="s">
+      <c r="I31" s="88" t="s">
         <v>183</v>
       </c>
-      <c r="J31" s="88" t="s">
-        <v>487</v>
+      <c r="J31" s="89" t="s">
+        <v>491</v>
       </c>
       <c r="K31" s="50"/>
       <c r="L31" s="56" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="M31" s="53" t="s">
         <v>108</v>
@@ -15342,20 +15370,20 @@
         <v>3</v>
       </c>
       <c r="E32" s="53" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="F32" s="13"/>
       <c r="G32" s="13"/>
       <c r="H32" s="13"/>
-      <c r="I32" s="87" t="s">
+      <c r="I32" s="88" t="s">
         <v>225</v>
       </c>
-      <c r="J32" s="88" t="s">
+      <c r="J32" s="89" t="s">
         <v>164</v>
       </c>
       <c r="K32" s="50"/>
       <c r="L32" s="56" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="M32" s="53" t="s">
         <v>108</v>
@@ -15390,26 +15418,26 @@
         <v>3</v>
       </c>
       <c r="E33" s="53" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="F33" s="13"/>
       <c r="G33" s="13"/>
       <c r="H33" s="13"/>
-      <c r="I33" s="87" t="s">
+      <c r="I33" s="88" t="s">
         <v>313</v>
       </c>
-      <c r="J33" s="88" t="s">
+      <c r="J33" s="89" t="s">
         <v>50</v>
       </c>
       <c r="K33" s="50"/>
       <c r="L33" s="56" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="M33" s="53" t="s">
         <v>329</v>
       </c>
       <c r="N33" s="86" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="O33" s="56"/>
       <c r="P33" s="29"/>
@@ -15436,15 +15464,15 @@
         <v>3</v>
       </c>
       <c r="E34" s="53" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="F34" s="13"/>
       <c r="G34" s="13"/>
       <c r="H34" s="13"/>
-      <c r="I34" s="87" t="s">
+      <c r="I34" s="88" t="s">
         <v>190</v>
       </c>
-      <c r="J34" s="88" t="s">
+      <c r="J34" s="89" t="s">
         <v>164</v>
       </c>
       <c r="K34" s="50"/>
@@ -15482,20 +15510,20 @@
         <v>3</v>
       </c>
       <c r="E35" s="53" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="F35" s="13"/>
       <c r="G35" s="13"/>
       <c r="H35" s="13"/>
-      <c r="I35" s="87" t="s">
+      <c r="I35" s="88" t="s">
         <v>195</v>
       </c>
-      <c r="J35" s="88" t="s">
-        <v>487</v>
+      <c r="J35" s="89" t="s">
+        <v>491</v>
       </c>
       <c r="K35" s="50"/>
       <c r="L35" s="56" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="M35" s="53" t="s">
         <v>108</v>
@@ -15528,20 +15556,20 @@
         <v>3</v>
       </c>
       <c r="E36" s="53" t="s">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="F36" s="13"/>
       <c r="G36" s="13"/>
       <c r="H36" s="13"/>
-      <c r="I36" s="87" t="s">
+      <c r="I36" s="88" t="s">
         <v>228</v>
       </c>
-      <c r="J36" s="88" t="s">
+      <c r="J36" s="89" t="s">
         <v>164</v>
       </c>
       <c r="K36" s="50"/>
       <c r="L36" s="56" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="M36" s="53" t="s">
         <v>108</v>
@@ -15574,20 +15602,20 @@
         <v>3</v>
       </c>
       <c r="E37" s="53" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="F37" s="13"/>
       <c r="G37" s="13"/>
       <c r="H37" s="13"/>
-      <c r="I37" s="87" t="s">
+      <c r="I37" s="88" t="s">
         <v>219</v>
       </c>
-      <c r="J37" s="88" t="s">
-        <v>487</v>
+      <c r="J37" s="89" t="s">
+        <v>491</v>
       </c>
       <c r="K37" s="50"/>
       <c r="L37" s="56" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="M37" s="53" t="s">
         <v>108</v>
@@ -15620,15 +15648,15 @@
         <v>3</v>
       </c>
       <c r="E38" s="53" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="F38" s="13"/>
       <c r="G38" s="13"/>
       <c r="H38" s="13"/>
-      <c r="I38" s="87" t="s">
+      <c r="I38" s="88" t="s">
         <v>192</v>
       </c>
-      <c r="J38" s="88" t="s">
+      <c r="J38" s="89" t="s">
         <v>164</v>
       </c>
       <c r="K38" s="50"/>
@@ -15666,26 +15694,26 @@
         <v>3</v>
       </c>
       <c r="E39" s="53" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="F39" s="13"/>
       <c r="G39" s="13"/>
       <c r="H39" s="13"/>
-      <c r="I39" s="87" t="s">
+      <c r="I39" s="88" t="s">
         <v>326</v>
       </c>
-      <c r="J39" s="88" t="s">
+      <c r="J39" s="89" t="s">
         <v>50</v>
       </c>
       <c r="K39" s="50"/>
       <c r="L39" s="56" t="s">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="M39" s="53" t="s">
         <v>329</v>
       </c>
       <c r="N39" s="86" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="O39" s="56"/>
       <c r="P39" s="29"/>
@@ -15712,20 +15740,20 @@
         <v>3</v>
       </c>
       <c r="E40" s="53" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="F40" s="13"/>
       <c r="G40" s="13"/>
       <c r="H40" s="13"/>
-      <c r="I40" s="87" t="s">
+      <c r="I40" s="88" t="s">
         <v>222</v>
       </c>
-      <c r="J40" s="88" t="s">
-        <v>487</v>
+      <c r="J40" s="89" t="s">
+        <v>491</v>
       </c>
       <c r="K40" s="50"/>
       <c r="L40" s="56" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="M40" s="53" t="s">
         <v>108</v>
@@ -15758,20 +15786,20 @@
         <v>3</v>
       </c>
       <c r="E41" s="53" t="s">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="F41" s="13"/>
       <c r="G41" s="13"/>
       <c r="H41" s="13"/>
-      <c r="I41" s="87" t="s">
+      <c r="I41" s="88" t="s">
         <v>232</v>
       </c>
-      <c r="J41" s="88" t="s">
+      <c r="J41" s="89" t="s">
         <v>164</v>
       </c>
       <c r="K41" s="50"/>
       <c r="L41" s="56" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="M41" s="53" t="s">
         <v>108</v>
@@ -15804,20 +15832,20 @@
         <v>3</v>
       </c>
       <c r="E42" s="53" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="F42" s="13"/>
       <c r="G42" s="13"/>
       <c r="H42" s="13"/>
-      <c r="I42" s="87" t="s">
+      <c r="I42" s="88" t="s">
         <v>225</v>
       </c>
-      <c r="J42" s="88" t="s">
-        <v>487</v>
+      <c r="J42" s="89" t="s">
+        <v>491</v>
       </c>
       <c r="K42" s="50"/>
       <c r="L42" s="56" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="M42" s="53" t="s">
         <v>108</v>
@@ -15850,20 +15878,20 @@
         <v>3</v>
       </c>
       <c r="E43" s="53" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="F43" s="13"/>
       <c r="G43" s="13"/>
       <c r="H43" s="13"/>
-      <c r="I43" s="87" t="s">
-        <v>527</v>
-      </c>
-      <c r="J43" s="88" t="s">
+      <c r="I43" s="88" t="s">
+        <v>531</v>
+      </c>
+      <c r="J43" s="89" t="s">
         <v>164</v>
       </c>
       <c r="K43" s="50"/>
       <c r="L43" s="56" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="M43" s="53" t="s">
         <v>108</v>
@@ -15896,26 +15924,26 @@
         <v>3</v>
       </c>
       <c r="E44" s="53" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="F44" s="13"/>
       <c r="G44" s="13"/>
       <c r="H44" s="13"/>
-      <c r="I44" s="87" t="s">
+      <c r="I44" s="88" t="s">
         <v>324</v>
       </c>
-      <c r="J44" s="88" t="s">
+      <c r="J44" s="89" t="s">
         <v>50</v>
       </c>
       <c r="K44" s="50"/>
       <c r="L44" s="56" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="M44" s="53" t="s">
         <v>329</v>
       </c>
       <c r="N44" s="86" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="O44" s="56"/>
       <c r="P44" s="29"/>
@@ -15942,16 +15970,16 @@
         <v>3</v>
       </c>
       <c r="E45" s="53" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="F45" s="13"/>
       <c r="G45" s="13"/>
       <c r="H45" s="13"/>
-      <c r="I45" s="87" t="s">
+      <c r="I45" s="88" t="s">
         <v>190</v>
       </c>
-      <c r="J45" s="88" t="s">
-        <v>487</v>
+      <c r="J45" s="89" t="s">
+        <v>491</v>
       </c>
       <c r="K45" s="50"/>
       <c r="L45" s="56" t="s">
@@ -15988,20 +16016,20 @@
         <v>3</v>
       </c>
       <c r="E46" s="53" t="s">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="F46" s="13"/>
       <c r="G46" s="13"/>
       <c r="H46" s="13"/>
-      <c r="I46" s="87" t="s">
-        <v>532</v>
-      </c>
-      <c r="J46" s="88" t="s">
+      <c r="I46" s="88" t="s">
+        <v>536</v>
+      </c>
+      <c r="J46" s="89" t="s">
         <v>164</v>
       </c>
       <c r="K46" s="50"/>
       <c r="L46" s="56" t="s">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="M46" s="53" t="s">
         <v>108</v>
@@ -16034,20 +16062,20 @@
         <v>3</v>
       </c>
       <c r="E47" s="53" t="s">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="F47" s="13"/>
       <c r="G47" s="13"/>
       <c r="H47" s="13"/>
-      <c r="I47" s="87" t="s">
+      <c r="I47" s="88" t="s">
         <v>228</v>
       </c>
-      <c r="J47" s="88" t="s">
-        <v>487</v>
+      <c r="J47" s="89" t="s">
+        <v>491</v>
       </c>
       <c r="K47" s="50"/>
       <c r="L47" s="56" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="M47" s="53" t="s">
         <v>108</v>
@@ -16080,20 +16108,20 @@
         <v>3</v>
       </c>
       <c r="E48" s="53" t="s">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="F48" s="13"/>
       <c r="G48" s="13"/>
       <c r="H48" s="13"/>
-      <c r="I48" s="87" t="s">
-        <v>535</v>
-      </c>
-      <c r="J48" s="88" t="s">
+      <c r="I48" s="88" t="s">
+        <v>539</v>
+      </c>
+      <c r="J48" s="89" t="s">
         <v>164</v>
       </c>
       <c r="K48" s="50"/>
       <c r="L48" s="56" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="M48" s="53" t="s">
         <v>108</v>
@@ -16126,20 +16154,20 @@
         <v>3</v>
       </c>
       <c r="E49" s="53" t="s">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="F49" s="13"/>
       <c r="G49" s="13"/>
       <c r="H49" s="13"/>
-      <c r="I49" s="87" t="s">
-        <v>538</v>
-      </c>
-      <c r="J49" s="88" t="s">
+      <c r="I49" s="88" t="s">
+        <v>542</v>
+      </c>
+      <c r="J49" s="89" t="s">
         <v>50</v>
       </c>
       <c r="K49" s="50"/>
       <c r="L49" s="56" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="M49" s="53" t="s">
         <v>108</v>
@@ -16172,16 +16200,16 @@
         <v>3</v>
       </c>
       <c r="E50" s="53" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="F50" s="13"/>
       <c r="G50" s="13"/>
       <c r="H50" s="13"/>
-      <c r="I50" s="87" t="s">
+      <c r="I50" s="88" t="s">
         <v>192</v>
       </c>
-      <c r="J50" s="88" t="s">
-        <v>487</v>
+      <c r="J50" s="89" t="s">
+        <v>491</v>
       </c>
       <c r="K50" s="50"/>
       <c r="L50" s="56" t="s">
@@ -16218,20 +16246,20 @@
         <v>3</v>
       </c>
       <c r="E51" s="53" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="F51" s="13"/>
       <c r="G51" s="13"/>
       <c r="H51" s="13"/>
-      <c r="I51" s="87" t="s">
-        <v>450</v>
-      </c>
-      <c r="J51" s="88" t="s">
+      <c r="I51" s="88" t="s">
+        <v>454</v>
+      </c>
+      <c r="J51" s="89" t="s">
         <v>164</v>
       </c>
       <c r="K51" s="50"/>
       <c r="L51" s="56" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="M51" s="86" t="s">
         <v>53</v>
@@ -16262,20 +16290,20 @@
         <v>3</v>
       </c>
       <c r="E52" s="53" t="s">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="F52" s="13"/>
       <c r="G52" s="13"/>
       <c r="H52" s="13"/>
-      <c r="I52" s="87" t="s">
+      <c r="I52" s="88" t="s">
         <v>232</v>
       </c>
-      <c r="J52" s="88" t="s">
-        <v>487</v>
+      <c r="J52" s="89" t="s">
+        <v>491</v>
       </c>
       <c r="K52" s="50"/>
       <c r="L52" s="56" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="M52" s="53" t="s">
         <v>108</v>
@@ -16298,36 +16326,36 @@
       <c r="AC52" s="63"/>
     </row>
     <row r="53" customFormat="false" ht="20.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B53" s="89" t="n">
+      <c r="B53" s="90" t="n">
         <v>1</v>
       </c>
-      <c r="C53" s="90" t="s">
-        <v>45</v>
-      </c>
-      <c r="D53" s="91" t="s">
+      <c r="C53" s="91" t="s">
+        <v>45</v>
+      </c>
+      <c r="D53" s="92" t="s">
         <v>62</v>
       </c>
-      <c r="E53" s="92" t="s">
-        <v>541</v>
-      </c>
-      <c r="F53" s="89"/>
-      <c r="G53" s="89"/>
-      <c r="H53" s="89"/>
-      <c r="I53" s="93" t="s">
-        <v>542</v>
-      </c>
-      <c r="J53" s="94" t="s">
+      <c r="E53" s="93" t="s">
+        <v>545</v>
+      </c>
+      <c r="F53" s="90"/>
+      <c r="G53" s="90"/>
+      <c r="H53" s="90"/>
+      <c r="I53" s="94" t="s">
+        <v>546</v>
+      </c>
+      <c r="J53" s="95" t="s">
         <v>164</v>
       </c>
-      <c r="K53" s="89"/>
-      <c r="L53" s="95" t="s">
-        <v>543</v>
-      </c>
-      <c r="M53" s="97"/>
-      <c r="N53" s="96"/>
-      <c r="O53" s="95"/>
-      <c r="P53" s="97"/>
-      <c r="Q53" s="95"/>
+      <c r="K53" s="90"/>
+      <c r="L53" s="96" t="s">
+        <v>547</v>
+      </c>
+      <c r="M53" s="98"/>
+      <c r="N53" s="97"/>
+      <c r="O53" s="96"/>
+      <c r="P53" s="98"/>
+      <c r="Q53" s="96"/>
       <c r="R53" s="58"/>
       <c r="U53" s="12"/>
       <c r="V53" s="59"/>
@@ -16350,20 +16378,20 @@
         <v>3</v>
       </c>
       <c r="E54" s="53" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="F54" s="13"/>
       <c r="G54" s="13"/>
       <c r="H54" s="13"/>
-      <c r="I54" s="87" t="s">
-        <v>545</v>
-      </c>
-      <c r="J54" s="88" t="s">
+      <c r="I54" s="88" t="s">
+        <v>549</v>
+      </c>
+      <c r="J54" s="89" t="s">
         <v>50</v>
       </c>
       <c r="K54" s="50"/>
       <c r="L54" s="56" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="M54" s="53" t="s">
         <v>108</v>
@@ -16386,36 +16414,36 @@
       <c r="AC54" s="63"/>
     </row>
     <row r="55" customFormat="false" ht="20.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B55" s="89" t="n">
+      <c r="B55" s="90" t="n">
         <v>1</v>
       </c>
-      <c r="C55" s="90" t="s">
-        <v>45</v>
-      </c>
-      <c r="D55" s="91" t="s">
+      <c r="C55" s="91" t="s">
+        <v>45</v>
+      </c>
+      <c r="D55" s="92" t="s">
         <v>62</v>
       </c>
-      <c r="E55" s="92" t="s">
-        <v>547</v>
-      </c>
-      <c r="F55" s="98"/>
-      <c r="G55" s="98"/>
-      <c r="H55" s="98"/>
-      <c r="I55" s="93" t="s">
-        <v>548</v>
-      </c>
-      <c r="J55" s="94" t="s">
+      <c r="E55" s="93" t="s">
+        <v>551</v>
+      </c>
+      <c r="F55" s="99"/>
+      <c r="G55" s="99"/>
+      <c r="H55" s="99"/>
+      <c r="I55" s="94" t="s">
+        <v>552</v>
+      </c>
+      <c r="J55" s="95" t="s">
         <v>164</v>
       </c>
-      <c r="K55" s="98"/>
-      <c r="L55" s="98" t="s">
-        <v>549</v>
-      </c>
-      <c r="M55" s="98"/>
-      <c r="N55" s="99"/>
-      <c r="O55" s="98"/>
-      <c r="P55" s="98"/>
-      <c r="Q55" s="98"/>
+      <c r="K55" s="99"/>
+      <c r="L55" s="99" t="s">
+        <v>553</v>
+      </c>
+      <c r="M55" s="99"/>
+      <c r="N55" s="100"/>
+      <c r="O55" s="99"/>
+      <c r="P55" s="99"/>
+      <c r="Q55" s="99"/>
     </row>
     <row r="56" customFormat="false" ht="32.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B56" s="50" t="n">
@@ -16428,16 +16456,16 @@
         <v>3</v>
       </c>
       <c r="E56" s="53" t="s">
-        <v>526</v>
-      </c>
-      <c r="I56" s="87" t="s">
-        <v>527</v>
-      </c>
-      <c r="J56" s="88" t="s">
-        <v>487</v>
+        <v>530</v>
+      </c>
+      <c r="I56" s="88" t="s">
+        <v>531</v>
+      </c>
+      <c r="J56" s="89" t="s">
+        <v>491</v>
       </c>
       <c r="L56" s="56" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="M56" s="53" t="s">
         <v>108</v>
@@ -16457,22 +16485,22 @@
         <v>3</v>
       </c>
       <c r="E57" s="53" t="s">
-        <v>550</v>
-      </c>
-      <c r="I57" s="87" t="s">
+        <v>554</v>
+      </c>
+      <c r="I57" s="88" t="s">
         <v>436</v>
       </c>
-      <c r="J57" s="88" t="s">
+      <c r="J57" s="89" t="s">
         <v>164</v>
       </c>
       <c r="L57" s="0" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="M57" s="53" t="s">
         <v>329</v>
       </c>
       <c r="N57" s="86" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="32.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16486,16 +16514,16 @@
         <v>3</v>
       </c>
       <c r="E58" s="53" t="s">
-        <v>531</v>
-      </c>
-      <c r="I58" s="87" t="s">
-        <v>532</v>
-      </c>
-      <c r="J58" s="88" t="s">
-        <v>487</v>
+        <v>535</v>
+      </c>
+      <c r="I58" s="88" t="s">
+        <v>536</v>
+      </c>
+      <c r="J58" s="89" t="s">
+        <v>491</v>
       </c>
       <c r="L58" s="56" t="s">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="M58" s="53" t="s">
         <v>108</v>
@@ -16517,10 +16545,10 @@
       <c r="E59" s="53" t="s">
         <v>356</v>
       </c>
-      <c r="I59" s="87" t="s">
+      <c r="I59" s="88" t="s">
         <v>352</v>
       </c>
-      <c r="J59" s="88" t="s">
+      <c r="J59" s="89" t="s">
         <v>50</v>
       </c>
       <c r="L59" s="0" t="s">
@@ -16542,22 +16570,22 @@
         <v>3</v>
       </c>
       <c r="E60" s="53" t="s">
-        <v>552</v>
-      </c>
-      <c r="I60" s="87" t="s">
-        <v>459</v>
-      </c>
-      <c r="J60" s="88" t="s">
+        <v>556</v>
+      </c>
+      <c r="I60" s="88" t="s">
+        <v>463</v>
+      </c>
+      <c r="J60" s="89" t="s">
         <v>164</v>
       </c>
       <c r="L60" s="0" t="s">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="M60" s="53" t="s">
         <v>329</v>
       </c>
       <c r="N60" s="86" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="32.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16571,16 +16599,16 @@
         <v>3</v>
       </c>
       <c r="E61" s="53" t="s">
-        <v>534</v>
-      </c>
-      <c r="I61" s="87" t="s">
-        <v>535</v>
-      </c>
-      <c r="J61" s="88" t="s">
-        <v>487</v>
+        <v>538</v>
+      </c>
+      <c r="I61" s="88" t="s">
+        <v>539</v>
+      </c>
+      <c r="J61" s="89" t="s">
+        <v>491</v>
       </c>
       <c r="L61" s="56" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="M61" s="53" t="s">
         <v>108</v>
@@ -16600,16 +16628,16 @@
         <v>3</v>
       </c>
       <c r="E62" s="53" t="s">
-        <v>540</v>
-      </c>
-      <c r="I62" s="87" t="s">
-        <v>450</v>
-      </c>
-      <c r="J62" s="88" t="s">
-        <v>487</v>
+        <v>544</v>
+      </c>
+      <c r="I62" s="88" t="s">
+        <v>454</v>
+      </c>
+      <c r="J62" s="89" t="s">
+        <v>491</v>
       </c>
       <c r="L62" s="56" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="M62" s="86" t="s">
         <v>53</v>
@@ -16627,16 +16655,16 @@
         <v>3</v>
       </c>
       <c r="E63" s="53" t="s">
-        <v>554</v>
-      </c>
-      <c r="I63" s="87" t="s">
+        <v>558</v>
+      </c>
+      <c r="I63" s="88" t="s">
         <v>376</v>
       </c>
-      <c r="J63" s="88" t="s">
+      <c r="J63" s="89" t="s">
         <v>50</v>
       </c>
       <c r="L63" s="0" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="M63" s="53" t="s">
         <v>108</v>
@@ -16646,36 +16674,36 @@
       </c>
     </row>
     <row r="64" customFormat="false" ht="20.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B64" s="89" t="n">
+      <c r="B64" s="90" t="n">
         <v>1</v>
       </c>
-      <c r="C64" s="90" t="s">
-        <v>45</v>
-      </c>
-      <c r="D64" s="91" t="s">
+      <c r="C64" s="91" t="s">
+        <v>45</v>
+      </c>
+      <c r="D64" s="92" t="s">
         <v>62</v>
       </c>
-      <c r="E64" s="92" t="s">
-        <v>541</v>
-      </c>
-      <c r="F64" s="98"/>
-      <c r="G64" s="98"/>
-      <c r="H64" s="98"/>
-      <c r="I64" s="93" t="s">
-        <v>542</v>
-      </c>
-      <c r="J64" s="94" t="s">
-        <v>487</v>
-      </c>
-      <c r="K64" s="98"/>
-      <c r="L64" s="95" t="s">
-        <v>543</v>
-      </c>
-      <c r="M64" s="98"/>
-      <c r="N64" s="99"/>
-      <c r="O64" s="98"/>
-      <c r="P64" s="98"/>
-      <c r="Q64" s="98"/>
+      <c r="E64" s="93" t="s">
+        <v>545</v>
+      </c>
+      <c r="F64" s="99"/>
+      <c r="G64" s="99"/>
+      <c r="H64" s="99"/>
+      <c r="I64" s="94" t="s">
+        <v>546</v>
+      </c>
+      <c r="J64" s="95" t="s">
+        <v>491</v>
+      </c>
+      <c r="K64" s="99"/>
+      <c r="L64" s="96" t="s">
+        <v>547</v>
+      </c>
+      <c r="M64" s="99"/>
+      <c r="N64" s="100"/>
+      <c r="O64" s="99"/>
+      <c r="P64" s="99"/>
+      <c r="Q64" s="99"/>
     </row>
     <row r="65" customFormat="false" ht="20.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B65" s="50" t="n">
@@ -16688,22 +16716,22 @@
         <v>3</v>
       </c>
       <c r="E65" s="53" t="s">
-        <v>556</v>
-      </c>
-      <c r="I65" s="87" t="s">
+        <v>560</v>
+      </c>
+      <c r="I65" s="88" t="s">
         <v>422</v>
       </c>
-      <c r="J65" s="88" t="s">
+      <c r="J65" s="89" t="s">
         <v>164</v>
       </c>
       <c r="L65" s="0" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="M65" s="53" t="s">
         <v>329</v>
       </c>
       <c r="N65" s="86" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="20.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16717,52 +16745,52 @@
         <v>3</v>
       </c>
       <c r="E66" s="53" t="s">
-        <v>558</v>
-      </c>
-      <c r="I66" s="87" t="s">
-        <v>446</v>
-      </c>
-      <c r="J66" s="88" t="s">
+        <v>562</v>
+      </c>
+      <c r="I66" s="88" t="s">
+        <v>450</v>
+      </c>
+      <c r="J66" s="89" t="s">
         <v>164</v>
       </c>
       <c r="L66" s="0" t="s">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="M66" s="86" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="20.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B67" s="89" t="n">
+      <c r="B67" s="90" t="n">
         <v>1</v>
       </c>
-      <c r="C67" s="90" t="s">
-        <v>45</v>
-      </c>
-      <c r="D67" s="91" t="s">
+      <c r="C67" s="91" t="s">
+        <v>45</v>
+      </c>
+      <c r="D67" s="92" t="s">
         <v>62</v>
       </c>
-      <c r="E67" s="92" t="s">
-        <v>547</v>
-      </c>
-      <c r="F67" s="98"/>
-      <c r="G67" s="98"/>
-      <c r="H67" s="98"/>
-      <c r="I67" s="93" t="s">
-        <v>548</v>
-      </c>
-      <c r="J67" s="94" t="s">
-        <v>487</v>
-      </c>
-      <c r="K67" s="98"/>
-      <c r="L67" s="98" t="s">
-        <v>549</v>
-      </c>
-      <c r="M67" s="98"/>
-      <c r="N67" s="99"/>
-      <c r="O67" s="98"/>
-      <c r="P67" s="98"/>
-      <c r="Q67" s="98"/>
+      <c r="E67" s="93" t="s">
+        <v>551</v>
+      </c>
+      <c r="F67" s="99"/>
+      <c r="G67" s="99"/>
+      <c r="H67" s="99"/>
+      <c r="I67" s="94" t="s">
+        <v>552</v>
+      </c>
+      <c r="J67" s="95" t="s">
+        <v>491</v>
+      </c>
+      <c r="K67" s="99"/>
+      <c r="L67" s="99" t="s">
+        <v>553</v>
+      </c>
+      <c r="M67" s="99"/>
+      <c r="N67" s="100"/>
+      <c r="O67" s="99"/>
+      <c r="P67" s="99"/>
+      <c r="Q67" s="99"/>
     </row>
     <row r="68" customFormat="false" ht="32.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B68" s="50" t="n">
@@ -16775,22 +16803,22 @@
         <v>3</v>
       </c>
       <c r="E68" s="53" t="s">
-        <v>560</v>
-      </c>
-      <c r="I68" s="87" t="s">
+        <v>564</v>
+      </c>
+      <c r="I68" s="88" t="s">
         <v>378</v>
       </c>
-      <c r="J68" s="88" t="s">
+      <c r="J68" s="89" t="s">
         <v>50</v>
       </c>
       <c r="L68" s="0" t="s">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="M68" s="0" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="N68" s="73" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="20.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16804,16 +16832,16 @@
         <v>3</v>
       </c>
       <c r="E69" s="53" t="s">
-        <v>550</v>
-      </c>
-      <c r="I69" s="87" t="s">
+        <v>554</v>
+      </c>
+      <c r="I69" s="88" t="s">
         <v>436</v>
       </c>
-      <c r="J69" s="88" t="s">
-        <v>487</v>
+      <c r="J69" s="89" t="s">
+        <v>491</v>
       </c>
       <c r="L69" s="0" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="M69" s="53" t="s">
         <v>329</v>
@@ -16831,16 +16859,16 @@
         <v>3</v>
       </c>
       <c r="E70" s="53" t="s">
-        <v>552</v>
-      </c>
-      <c r="I70" s="87" t="s">
-        <v>459</v>
-      </c>
-      <c r="J70" s="88" t="s">
-        <v>487</v>
+        <v>556</v>
+      </c>
+      <c r="I70" s="88" t="s">
+        <v>463</v>
+      </c>
+      <c r="J70" s="89" t="s">
+        <v>491</v>
       </c>
       <c r="L70" s="0" t="s">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="M70" s="53" t="s">
         <v>329</v>
@@ -16858,16 +16886,16 @@
         <v>3</v>
       </c>
       <c r="E71" s="53" t="s">
-        <v>564</v>
-      </c>
-      <c r="I71" s="87" t="s">
-        <v>565</v>
-      </c>
-      <c r="J71" s="88" t="s">
+        <v>568</v>
+      </c>
+      <c r="I71" s="88" t="s">
+        <v>569</v>
+      </c>
+      <c r="J71" s="89" t="s">
         <v>50</v>
       </c>
       <c r="L71" s="0" t="s">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="M71" s="53" t="s">
         <v>108</v>
@@ -16887,22 +16915,22 @@
         <v>3</v>
       </c>
       <c r="E72" s="53" t="s">
-        <v>556</v>
-      </c>
-      <c r="I72" s="87" t="s">
+        <v>560</v>
+      </c>
+      <c r="I72" s="88" t="s">
         <v>422</v>
       </c>
-      <c r="J72" s="88" t="s">
-        <v>487</v>
+      <c r="J72" s="89" t="s">
+        <v>491</v>
       </c>
       <c r="L72" s="0" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="M72" s="53" t="s">
         <v>329</v>
       </c>
       <c r="N72" s="86" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="32.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16916,12 +16944,12 @@
         <v>3</v>
       </c>
       <c r="E73" s="53" t="s">
-        <v>567</v>
-      </c>
-      <c r="I73" s="87" t="s">
+        <v>571</v>
+      </c>
+      <c r="I73" s="88" t="s">
         <v>260</v>
       </c>
-      <c r="J73" s="88" t="s">
+      <c r="J73" s="89" t="s">
         <v>50</v>
       </c>
       <c r="L73" s="0" t="s">
@@ -16945,16 +16973,16 @@
         <v>3</v>
       </c>
       <c r="E74" s="53" t="s">
-        <v>558</v>
-      </c>
-      <c r="I74" s="87" t="s">
-        <v>446</v>
-      </c>
-      <c r="J74" s="88" t="s">
-        <v>487</v>
+        <v>562</v>
+      </c>
+      <c r="I74" s="88" t="s">
+        <v>450</v>
+      </c>
+      <c r="J74" s="89" t="s">
+        <v>491</v>
       </c>
       <c r="L74" s="0" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="M74" s="86" t="s">
         <v>53</v>
@@ -16972,12 +17000,12 @@
         <v>3</v>
       </c>
       <c r="E75" s="53" t="s">
-        <v>569</v>
-      </c>
-      <c r="I75" s="87" t="s">
+        <v>573</v>
+      </c>
+      <c r="I75" s="88" t="s">
         <v>407</v>
       </c>
-      <c r="J75" s="88" t="s">
+      <c r="J75" s="89" t="s">
         <v>50</v>
       </c>
       <c r="L75" s="0" t="s">
@@ -17001,22 +17029,22 @@
         <v>3</v>
       </c>
       <c r="E76" s="53" t="s">
-        <v>570</v>
-      </c>
-      <c r="I76" s="87" t="s">
+        <v>574</v>
+      </c>
+      <c r="I76" s="88" t="s">
         <v>384</v>
       </c>
-      <c r="J76" s="88" t="s">
+      <c r="J76" s="89" t="s">
         <v>50</v>
       </c>
       <c r="L76" s="0" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="M76" s="53" t="s">
         <v>329</v>
       </c>
       <c r="N76" s="86" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="20.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17030,22 +17058,22 @@
         <v>3</v>
       </c>
       <c r="E77" s="53" t="s">
-        <v>572</v>
-      </c>
-      <c r="I77" s="87" t="s">
+        <v>576</v>
+      </c>
+      <c r="I77" s="88" t="s">
         <v>411</v>
       </c>
-      <c r="J77" s="88" t="s">
+      <c r="J77" s="89" t="s">
         <v>50</v>
       </c>
       <c r="L77" s="0" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="M77" s="53" t="s">
         <v>329</v>
       </c>
       <c r="N77" s="86" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="20.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17059,57 +17087,57 @@
         <v>3</v>
       </c>
       <c r="E78" s="53" t="s">
-        <v>574</v>
-      </c>
-      <c r="I78" s="87" t="s">
+        <v>578</v>
+      </c>
+      <c r="I78" s="88" t="s">
         <v>396</v>
       </c>
-      <c r="J78" s="88" t="s">
+      <c r="J78" s="89" t="s">
         <v>50</v>
       </c>
       <c r="L78" s="0" t="s">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="M78" s="53" t="s">
         <v>329</v>
       </c>
       <c r="N78" s="86" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="20.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B79" s="100" t="n">
+      <c r="B79" s="101" t="n">
         <v>1</v>
       </c>
-      <c r="C79" s="101" t="s">
-        <v>45</v>
-      </c>
-      <c r="D79" s="102" t="s">
+      <c r="C79" s="102" t="s">
+        <v>45</v>
+      </c>
+      <c r="D79" s="103" t="s">
         <v>62</v>
       </c>
-      <c r="E79" s="103" t="s">
-        <v>576</v>
-      </c>
-      <c r="F79" s="104"/>
-      <c r="G79" s="104"/>
-      <c r="H79" s="104"/>
-      <c r="I79" s="105" t="s">
-        <v>577</v>
-      </c>
-      <c r="J79" s="106" t="s">
+      <c r="E79" s="104" t="s">
+        <v>580</v>
+      </c>
+      <c r="F79" s="105"/>
+      <c r="G79" s="105"/>
+      <c r="H79" s="105"/>
+      <c r="I79" s="106" t="s">
+        <v>581</v>
+      </c>
+      <c r="J79" s="107" t="s">
         <v>50</v>
       </c>
-      <c r="K79" s="104"/>
-      <c r="L79" s="104" t="s">
-        <v>578</v>
-      </c>
-      <c r="M79" s="107" t="s">
+      <c r="K79" s="105"/>
+      <c r="L79" s="105" t="s">
+        <v>582</v>
+      </c>
+      <c r="M79" s="108" t="s">
         <v>108</v>
       </c>
-      <c r="N79" s="108"/>
-      <c r="O79" s="104"/>
-      <c r="P79" s="104"/>
-      <c r="Q79" s="104"/>
+      <c r="N79" s="109"/>
+      <c r="O79" s="105"/>
+      <c r="P79" s="105"/>
+      <c r="Q79" s="105"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -17228,39 +17256,39 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B19"/>
-  <sheetFormatPr defaultColWidth="12.0390625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.0546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11.52"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="115.2"/>
   </cols>
   <sheetData>
-    <row r="1" s="109" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" s="110" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="28" t="s">
-        <v>579</v>
+        <v>583</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="28" t="s">
-        <v>580</v>
-      </c>
-      <c r="B2" s="109"/>
+        <v>584</v>
+      </c>
+      <c r="B2" s="110"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="28" t="n">
         <v>14</v>
       </c>
-      <c r="B3" s="109"/>
+      <c r="B3" s="110"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="28"/>
-      <c r="B4" s="109"/>
+      <c r="B4" s="110"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="28" t="s">
-        <v>580</v>
-      </c>
-      <c r="B5" s="109" t="s">
-        <v>581</v>
+        <v>584</v>
+      </c>
+      <c r="B5" s="110" t="s">
+        <v>585</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17268,7 +17296,7 @@
         <v>1</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>582</v>
+        <v>586</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17276,7 +17304,7 @@
         <v>2</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>583</v>
+        <v>587</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17284,7 +17312,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17292,7 +17320,7 @@
         <v>4</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>585</v>
+        <v>589</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17300,7 +17328,7 @@
         <v>5</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>586</v>
+        <v>590</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17308,7 +17336,7 @@
         <v>6</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17316,7 +17344,7 @@
         <v>7</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>588</v>
+        <v>592</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17324,7 +17352,7 @@
         <v>8</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>589</v>
+        <v>593</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17332,7 +17360,7 @@
         <v>9</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>590</v>
+        <v>594</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17340,7 +17368,7 @@
         <v>10</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>591</v>
+        <v>595</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17348,7 +17376,7 @@
         <v>11</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>592</v>
+        <v>596</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17356,7 +17384,7 @@
         <v>12</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>593</v>
+        <v>597</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="24.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17364,7 +17392,7 @@
         <v>13</v>
       </c>
       <c r="B18" s="86" t="s">
-        <v>594</v>
+        <v>598</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17372,7 +17400,7 @@
         <v>14</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>595</v>
+        <v>599</v>
       </c>
     </row>
   </sheetData>
@@ -17392,7 +17420,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B1:AE54"/>
-  <sheetFormatPr defaultColWidth="9.03125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.0390625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="1" min="1" style="0" width="11.52"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="10.01"/>
@@ -19749,7 +19777,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B1:AE54"/>
-  <sheetFormatPr defaultColWidth="9.03125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.0390625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="1" min="1" style="0" width="11.52"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="10.01"/>
@@ -21920,7 +21948,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B1:AE54"/>
-  <sheetFormatPr defaultColWidth="9.03125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.0390625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="1" min="1" style="0" width="11.52"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="10.01"/>
@@ -24388,7 +24416,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B1:AE30"/>
-  <sheetFormatPr defaultColWidth="9.03125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.0390625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="1" min="1" style="0" width="11.52"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="10.01"/>
@@ -25773,7 +25801,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B1:AE54"/>
-  <sheetFormatPr defaultColWidth="9.03125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.0390625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="1" min="1" style="0" width="11.52"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="10.01"/>
@@ -27949,7 +27977,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B1:AE30"/>
-  <sheetFormatPr defaultColWidth="9.03125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.0390625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="1" min="1" style="0" width="11.52"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="10.01"/>
@@ -29276,7 +29304,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B1:AE30"/>
-  <sheetFormatPr defaultColWidth="9.03125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.0390625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="1" min="1" style="0" width="11.52"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="10.01"/>
@@ -30566,7 +30594,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B1:AE54"/>
-  <sheetFormatPr defaultColWidth="9.03125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.0390625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="1" min="1" style="0" width="11.52"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="10.01"/>
